--- a/python/scripts/oracle_upload/sectors.xlsx
+++ b/python/scripts/oracle_upload/sectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="scS" sheetId="1" state="visible" r:id="rId2"/>
@@ -14,8 +14,8 @@
     <sheet name="HXR" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">cuH!$A$1:$S$34</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">scS!$A$1:$S$53</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">cuH!$A$1:$S$37</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">scS!$A$1:$S$64</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="392">
   <si>
     <t xml:space="preserve">Lsector=</t>
   </si>
@@ -78,9 +78,6 @@
     <t xml:space="preserve">S01</t>
   </si>
   <si>
-    <t xml:space="preserve">1,7</t>
-  </si>
-  <si>
     <t xml:space="preserve">L0B/HTR/DIAG0/COL0/L1B</t>
   </si>
   <si>
@@ -297,46 +294,43 @@
     <t xml:space="preserve">S28</t>
   </si>
   <si>
-    <t xml:space="preserve">1,6</t>
-  </si>
-  <si>
     <t xml:space="preserve">BYP/SPD1</t>
   </si>
   <si>
     <t xml:space="preserve">S29</t>
   </si>
   <si>
-    <t xml:space="preserve">1,6,7,9</t>
-  </si>
-  <si>
     <t xml:space="preserve">SPD1/SPS</t>
   </si>
   <si>
+    <t xml:space="preserve">ENDSPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDSPD_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEGDASEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">S30</t>
   </si>
   <si>
     <t xml:space="preserve">SPS</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ENDSPS,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ENDSPH,ENDSPS,ENDSPS</t>
-    </r>
+    <t xml:space="preserve">ENDSPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEGSLTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDSLTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEGSLTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDSLTD</t>
   </si>
   <si>
     <t xml:space="preserve">BSY</t>
@@ -345,46 +339,10 @@
     <t xml:space="preserve">SLTS/BSYS</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BEGSLTS,BEGSLTH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">,BEGSLTS,BEGSLTS</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ENDBSYS,ENDSLTH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">,ENDBSYS,ENDBSYS</t>
-    </r>
+    <t xml:space="preserve">BEGSLTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDBSYS</t>
   </si>
   <si>
     <t xml:space="preserve">BSY
@@ -526,7 +484,7 @@
     <t xml:space="preserve">ALINE</t>
   </si>
   <si>
-    <t xml:space="preserve">ENDBSY_2</t>
+    <t xml:space="preserve">ENDBSYA_2</t>
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
@@ -538,7 +496,7 @@
     <t xml:space="preserve">S20</t>
   </si>
   <si>
-    <t xml:space="preserve">10,15</t>
+    <t xml:space="preserve">10</t>
   </si>
   <si>
     <t xml:space="preserve">GUN1/GUN2/L0/HTR/EMIT/BX0</t>
@@ -550,12 +508,12 @@
     <t xml:space="preserve">ENDDL1_2</t>
   </si>
   <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
     <t xml:space="preserve">S21</t>
   </si>
   <si>
-    <t xml:space="preserve">10,16</t>
-  </si>
-  <si>
     <t xml:space="preserve">L1/BC1/L2</t>
   </si>
   <si>
@@ -565,6 +523,9 @@
     <t xml:space="preserve">LI21END</t>
   </si>
   <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
     <t xml:space="preserve">S22</t>
   </si>
   <si>
@@ -649,9 +610,6 @@
     <t xml:space="preserve">ENDCLTH_0</t>
   </si>
   <si>
-    <t xml:space="preserve">10,14</t>
-  </si>
-  <si>
     <t xml:space="preserve">CLTH/BSYH1/BSYH2</t>
   </si>
   <si>
@@ -661,6 +619,9 @@
     <t xml:space="preserve">ENDBSYH_2</t>
   </si>
   <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
     <t xml:space="preserve">71H</t>
   </si>
   <si>
@@ -764,9 +725,6 @@
   </si>
   <si>
     <t xml:space="preserve">BEGBSYA_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENDBSYA_2</t>
   </si>
   <si>
     <t xml:space="preserve">XTESH</t>
@@ -1260,7 +1218,7 @@
     <numFmt numFmtId="167" formatCode="0.000000"/>
     <numFmt numFmtId="168" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1288,12 +1246,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1328,22 +1280,15 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="medium"/>
+      <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="hair"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
+      <left style="hair"/>
       <right/>
-      <top style="medium"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right/>
-      <top style="medium"/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1352,6 +1297,13 @@
       <right style="medium"/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -1387,7 +1339,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1444,7 +1396,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1452,28 +1428,48 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1533,8 +1529,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:S72"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.57"/>
@@ -1543,15 +1539,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="71.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="71.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="5.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="5.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="3" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="6.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="6.71"/>
   </cols>
   <sheetData>
@@ -1640,18 +1636,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
+      <c r="B5" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="n">
         <f aca="false">F4</f>
@@ -1674,26 +1670,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="n">
-        <f aca="false">F5</f>
+        <f aca="false">F4</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <f aca="false">1*B1</f>
         <v>101.6</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <f aca="false">2*B1</f>
-        <v>203.2</v>
       </c>
       <c r="G6" s="2" t="n">
         <f aca="false">F6-E6</f>
@@ -1705,12 +1701,12 @@
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
@@ -1719,15 +1715,15 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="n">
-        <f aca="false">F6</f>
+        <f aca="false">F5</f>
+        <v>101.6</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <f aca="false">2*B1</f>
         <v>203.2</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <f aca="false">3*B1</f>
-        <v>304.8</v>
       </c>
       <c r="G7" s="2" t="n">
         <f aca="false">F7-E7</f>
@@ -1739,12 +1735,12 @@
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="1" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
@@ -1753,15 +1749,15 @@
         <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2" t="n">
         <f aca="false">F7</f>
+        <v>203.2</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <f aca="false">3*B1</f>
         <v>304.8</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <f aca="false">4*B1</f>
-        <v>406.4</v>
       </c>
       <c r="G8" s="2" t="n">
         <f aca="false">F8-E8</f>
@@ -1773,12 +1769,12 @@
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="1" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
@@ -1787,15 +1783,15 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E9" s="2" t="n">
         <f aca="false">F8</f>
+        <v>304.8</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <f aca="false">4*B1</f>
         <v>406.4</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <f aca="false">5*B1</f>
-        <v>508</v>
       </c>
       <c r="G9" s="2" t="n">
         <f aca="false">F9-E9</f>
@@ -1807,12 +1803,12 @@
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="1" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
@@ -1821,15 +1817,15 @@
         <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="n">
         <f aca="false">F9</f>
+        <v>406.4</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <f aca="false">5*B1</f>
         <v>508</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <f aca="false">6*B1</f>
-        <v>609.6</v>
       </c>
       <c r="G10" s="2" t="n">
         <f aca="false">F10-E10</f>
@@ -1841,12 +1837,12 @@
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="1" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>
@@ -1855,15 +1851,15 @@
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="n">
         <f aca="false">F10</f>
+        <v>508</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <f aca="false">6*B1</f>
         <v>609.6</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <f aca="false">7*B1</f>
-        <v>711.2</v>
       </c>
       <c r="G11" s="2" t="n">
         <f aca="false">F11-E11</f>
@@ -1875,12 +1871,12 @@
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1</v>
@@ -1889,15 +1885,15 @@
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2" t="n">
         <f aca="false">F11</f>
+        <v>609.6</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <f aca="false">7*B1</f>
         <v>711.2</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <f aca="false">8*B1</f>
-        <v>812.8</v>
       </c>
       <c r="G12" s="2" t="n">
         <f aca="false">F12-E12</f>
@@ -1909,12 +1905,12 @@
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="1" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>1</v>
@@ -1922,16 +1918,16 @@
       <c r="C13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>31</v>
+      <c r="D13" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">F12</f>
+        <v>711.2</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <f aca="false">8*B1</f>
         <v>812.8</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <f aca="false">9*B1</f>
-        <v>914.4</v>
       </c>
       <c r="G13" s="2" t="n">
         <f aca="false">F13-E13</f>
@@ -1941,20 +1937,14 @@
         <f aca="false">G13/0.3048</f>
         <v>333.333333333333</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>33</v>
-      </c>
       <c r="K13" s="12"/>
       <c r="L13" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>1</v>
@@ -1963,15 +1953,15 @@
         <v>0</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="n">
         <f aca="false">F13</f>
+        <v>812.8</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <f aca="false">9*B1</f>
         <v>914.4</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <f aca="false">10*B1</f>
-        <v>1016</v>
       </c>
       <c r="G14" s="2" t="n">
         <f aca="false">F14-E14</f>
@@ -1982,19 +1972,19 @@
         <v>333.333333333333</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="1" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>1</v>
@@ -2003,15 +1993,15 @@
         <v>0</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="n">
         <f aca="false">F14</f>
+        <v>914.4</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <f aca="false">10*B1</f>
         <v>1016</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <f aca="false">11*B1</f>
-        <v>1117.6</v>
       </c>
       <c r="G15" s="2" t="n">
         <f aca="false">F15-E15</f>
@@ -2022,19 +2012,19 @@
         <v>333.333333333333</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="1" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>1</v>
@@ -2043,15 +2033,15 @@
         <v>0</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="n">
         <f aca="false">F15</f>
+        <v>1016</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <f aca="false">11*B1</f>
         <v>1117.6</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <f aca="false">12*B1</f>
-        <v>1219.2</v>
       </c>
       <c r="G16" s="2" t="n">
         <f aca="false">F16-E16</f>
@@ -2062,19 +2052,19 @@
         <v>333.333333333333</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="1" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>1</v>
@@ -2083,15 +2073,15 @@
         <v>0</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="n">
         <f aca="false">F16</f>
+        <v>1117.6</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <f aca="false">12*B1</f>
         <v>1219.2</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <f aca="false">13*B1</f>
-        <v>1320.8</v>
       </c>
       <c r="G17" s="2" t="n">
         <f aca="false">F17-E17</f>
@@ -2099,22 +2089,22 @@
       </c>
       <c r="H17" s="5" t="n">
         <f aca="false">G17/0.3048</f>
-        <v>333.333333333334</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K17" s="12"/>
       <c r="L17" s="1" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>1</v>
@@ -2123,15 +2113,15 @@
         <v>0</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E18" s="2" t="n">
         <f aca="false">F17</f>
+        <v>1219.2</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <f aca="false">13*B1</f>
         <v>1320.8</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <f aca="false">14*B1</f>
-        <v>1422.4</v>
       </c>
       <c r="G18" s="2" t="n">
         <f aca="false">F18-E18</f>
@@ -2139,22 +2129,22 @@
       </c>
       <c r="H18" s="5" t="n">
         <f aca="false">G18/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K18" s="12"/>
       <c r="L18" s="1" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>1</v>
@@ -2163,15 +2153,15 @@
         <v>0</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="n">
         <f aca="false">F18</f>
+        <v>1320.8</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <f aca="false">14*B1</f>
         <v>1422.4</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <f aca="false">15*B1</f>
-        <v>1524</v>
       </c>
       <c r="G19" s="2" t="n">
         <f aca="false">F19-E19</f>
@@ -2179,22 +2169,22 @@
       </c>
       <c r="H19" s="5" t="n">
         <f aca="false">G19/0.3048</f>
-        <v>333.333333333334</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K19" s="12"/>
       <c r="L19" s="1" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
@@ -2203,15 +2193,15 @@
         <v>0</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="n">
         <f aca="false">F19</f>
+        <v>1422.4</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <f aca="false">15*B1</f>
         <v>1524</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <f aca="false">16*B1</f>
-        <v>1625.6</v>
       </c>
       <c r="G20" s="2" t="n">
         <f aca="false">F20-E20</f>
@@ -2219,22 +2209,22 @@
       </c>
       <c r="H20" s="5" t="n">
         <f aca="false">G20/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K20" s="12"/>
       <c r="L20" s="1" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>1</v>
@@ -2243,15 +2233,15 @@
         <v>0</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="n">
         <f aca="false">F20</f>
+        <v>1524</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <f aca="false">16*B1</f>
         <v>1625.6</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <f aca="false">17*B1</f>
-        <v>1727.2</v>
       </c>
       <c r="G21" s="2" t="n">
         <f aca="false">F21-E21</f>
@@ -2262,19 +2252,19 @@
         <v>333.333333333333</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K21" s="12"/>
       <c r="L21" s="1" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1</v>
@@ -2283,15 +2273,15 @@
         <v>0</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="n">
         <f aca="false">F21</f>
+        <v>1625.6</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <f aca="false">17*B1</f>
         <v>1727.2</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <f aca="false">18*B1</f>
-        <v>1828.8</v>
       </c>
       <c r="G22" s="2" t="n">
         <f aca="false">F22-E22</f>
@@ -2299,22 +2289,22 @@
       </c>
       <c r="H22" s="5" t="n">
         <f aca="false">G22/0.3048</f>
-        <v>333.333333333334</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K22" s="12"/>
       <c r="L22" s="1" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>1</v>
@@ -2323,15 +2313,15 @@
         <v>0</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2" t="n">
         <f aca="false">F22</f>
+        <v>1727.2</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <f aca="false">18*B1</f>
         <v>1828.8</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <f aca="false">19*B1</f>
-        <v>1930.4</v>
       </c>
       <c r="G23" s="2" t="n">
         <f aca="false">F23-E23</f>
@@ -2339,22 +2329,22 @@
       </c>
       <c r="H23" s="5" t="n">
         <f aca="false">G23/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K23" s="12"/>
       <c r="L23" s="1" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>1</v>
@@ -2363,15 +2353,15 @@
         <v>0</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E24" s="2" t="n">
         <f aca="false">F23</f>
+        <v>1828.8</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <f aca="false">19*B1</f>
         <v>1930.4</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <f aca="false">20*B1</f>
-        <v>2032</v>
       </c>
       <c r="G24" s="2" t="n">
         <f aca="false">F24-E24</f>
@@ -2379,22 +2369,22 @@
       </c>
       <c r="H24" s="5" t="n">
         <f aca="false">G24/0.3048</f>
-        <v>333.333333333334</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K24" s="12"/>
       <c r="L24" s="1" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>1</v>
@@ -2403,15 +2393,15 @@
         <v>0</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="n">
         <f aca="false">F24</f>
+        <v>1930.4</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <f aca="false">20*B1</f>
         <v>2032</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <f aca="false">21*B1</f>
-        <v>2133.6</v>
       </c>
       <c r="G25" s="2" t="n">
         <f aca="false">F25-E25</f>
@@ -2419,22 +2409,22 @@
       </c>
       <c r="H25" s="5" t="n">
         <f aca="false">G25/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K25" s="12"/>
       <c r="L25" s="1" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>1</v>
@@ -2443,15 +2433,15 @@
         <v>0</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E26" s="2" t="n">
         <f aca="false">F25</f>
+        <v>2032</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <f aca="false">21*B1</f>
         <v>2133.6</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <f aca="false">22*B1</f>
-        <v>2235.2</v>
       </c>
       <c r="G26" s="2" t="n">
         <f aca="false">F26-E26</f>
@@ -2462,19 +2452,19 @@
         <v>333.333333333333</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K26" s="12"/>
       <c r="L26" s="1" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>1</v>
@@ -2483,15 +2473,15 @@
         <v>0</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="n">
         <f aca="false">F26</f>
+        <v>2133.6</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <f aca="false">22*B1</f>
         <v>2235.2</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <f aca="false">23*B1</f>
-        <v>2336.8</v>
       </c>
       <c r="G27" s="2" t="n">
         <f aca="false">F27-E27</f>
@@ -2502,19 +2492,19 @@
         <v>333.333333333333</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K27" s="12"/>
       <c r="L27" s="1" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
@@ -2523,15 +2513,15 @@
         <v>0</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E28" s="2" t="n">
         <f aca="false">F27</f>
+        <v>2235.2</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <f aca="false">23*B1</f>
         <v>2336.8</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <f aca="false">24*B1</f>
-        <v>2438.4</v>
       </c>
       <c r="G28" s="2" t="n">
         <f aca="false">F28-E28</f>
@@ -2542,19 +2532,19 @@
         <v>333.333333333333</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="1" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>1</v>
@@ -2563,15 +2553,15 @@
         <v>0</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E29" s="2" t="n">
         <f aca="false">F28</f>
+        <v>2336.8</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <f aca="false">24*B1</f>
         <v>2438.4</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <f aca="false">25*B1</f>
-        <v>2540</v>
       </c>
       <c r="G29" s="2" t="n">
         <f aca="false">F29-E29</f>
@@ -2579,22 +2569,22 @@
       </c>
       <c r="H29" s="5" t="n">
         <f aca="false">G29/0.3048</f>
-        <v>333.333333333334</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="1" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>1</v>
@@ -2603,15 +2593,15 @@
         <v>0</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="n">
         <f aca="false">F29</f>
+        <v>2438.4</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <f aca="false">25*B1</f>
         <v>2540</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <f aca="false">26*B1</f>
-        <v>2641.6</v>
       </c>
       <c r="G30" s="2" t="n">
         <f aca="false">F30-E30</f>
@@ -2619,22 +2609,22 @@
       </c>
       <c r="H30" s="5" t="n">
         <f aca="false">G30/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K30" s="12"/>
       <c r="L30" s="1" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>1</v>
@@ -2643,15 +2633,15 @@
         <v>0</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2" t="n">
         <f aca="false">F30</f>
+        <v>2540</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <f aca="false">26*B1</f>
         <v>2641.6</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <f aca="false">27*B1</f>
-        <v>2743.2</v>
       </c>
       <c r="G31" s="2" t="n">
         <f aca="false">F31-E31</f>
@@ -2662,36 +2652,36 @@
         <v>333.333333333333</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K31" s="12"/>
       <c r="L31" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2" t="n">
         <f aca="false">F31</f>
+        <v>2641.6</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <f aca="false">27*B1</f>
         <v>2743.2</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <f aca="false">28*B1</f>
-        <v>2844.8</v>
       </c>
       <c r="G32" s="2" t="n">
         <f aca="false">F32-E32</f>
@@ -2701,31 +2691,37 @@
         <f aca="false">G32/0.3048</f>
         <v>333.333333333333</v>
       </c>
+      <c r="I32" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="K32" s="12"/>
       <c r="L32" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E33" s="2" t="n">
         <f aca="false">F32</f>
+        <v>2743.2</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <f aca="false">28*B1</f>
         <v>2844.8</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <f aca="false">29*B1</f>
-        <v>2946.4</v>
       </c>
       <c r="G33" s="2" t="n">
         <f aca="false">F33-E33</f>
@@ -2733,495 +2729,549 @@
       </c>
       <c r="H33" s="5" t="n">
         <f aca="false">G33/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="K33" s="12"/>
       <c r="L33" s="1" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="14" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <f aca="false">F33</f>
-        <v>2946.4</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>3050.512</v>
-      </c>
-      <c r="G34" s="9" t="n">
+      <c r="D34" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <f aca="false">F32</f>
+        <v>2743.2</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <f aca="false">28*B1</f>
+        <v>2844.8</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <f aca="false">F34-E34</f>
-        <v>104.112000000001</v>
-      </c>
-      <c r="H34" s="10" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <f aca="false">G34/0.3048</f>
-        <v>341.574803149608</v>
-      </c>
-      <c r="I34" s="7"/>
-      <c r="J34" s="15" t="s">
-        <v>96</v>
+        <v>333.333333333333</v>
       </c>
       <c r="K34" s="12"/>
       <c r="L34" s="1" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>2.512</v>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>176.021</v>
-      </c>
-      <c r="G35" s="17" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <f aca="false">F33</f>
+        <v>2844.8</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <f aca="false">29*B1</f>
+        <v>2946.4</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <f aca="false">F35-E35</f>
-        <v>173.509</v>
-      </c>
-      <c r="H35" s="18" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <f aca="false">G35/0.3048</f>
-        <v>569.255249343832</v>
-      </c>
-      <c r="I35" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="J35" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="K35" s="19" t="s">
-        <v>101</v>
-      </c>
+        <v>333.333333333333</v>
+      </c>
+      <c r="K35" s="12"/>
       <c r="L35" s="1" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E36" s="2" t="n">
-        <f aca="false">F35</f>
-        <v>176.021</v>
+        <f aca="false">F33</f>
+        <v>2844.8</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>206.2677</v>
+        <f aca="false">29*B1</f>
+        <v>2946.4</v>
       </c>
       <c r="G36" s="2" t="n">
         <f aca="false">F36-E36</f>
-        <v>30.2467</v>
+        <v>101.599999999999</v>
       </c>
       <c r="H36" s="5" t="n">
         <f aca="false">G36/0.3048</f>
-        <v>99.2345800524934</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="K36" s="19"/>
+        <v>333.333333333332</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K36" s="12"/>
       <c r="L36" s="1" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>105</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E37" s="2" t="n">
-        <f aca="false">F36</f>
-        <v>206.2677</v>
+        <f aca="false">F33</f>
+        <v>2844.8</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>232.228</v>
+        <f aca="false">29*B1</f>
+        <v>2946.4</v>
       </c>
       <c r="G37" s="2" t="n">
         <f aca="false">F37-E37</f>
-        <v>25.9603</v>
+        <v>101.599999999999</v>
       </c>
       <c r="H37" s="5" t="n">
         <f aca="false">G37/0.3048</f>
-        <v>85.1715879265093</v>
-      </c>
-      <c r="K37" s="19"/>
+        <v>333.333333333332</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K37" s="12"/>
       <c r="L37" s="1" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>106</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E38" s="2" t="n">
-        <f aca="false">F37</f>
-        <v>232.228</v>
+        <f aca="false">F33</f>
+        <v>2844.8</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>259.8137</v>
+        <f aca="false">29*B1</f>
+        <v>2946.4</v>
       </c>
       <c r="G38" s="2" t="n">
         <f aca="false">F38-E38</f>
-        <v>27.5857</v>
+        <v>101.599999999999</v>
       </c>
       <c r="H38" s="5" t="n">
         <f aca="false">G38/0.3048</f>
-        <v>90.5042650918634</v>
-      </c>
-      <c r="K38" s="19"/>
+        <v>333.333333333332</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K38" s="12"/>
       <c r="L38" s="1" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <f aca="false">F35</f>
+        <v>2946.4</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>3050.512</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <f aca="false">F39-E39</f>
+        <v>104.112</v>
+      </c>
+      <c r="H39" s="16" t="n">
+        <f aca="false">G39/0.3048</f>
+        <v>341.574803149607</v>
+      </c>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K39" s="12"/>
+      <c r="L39" s="1" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <f aca="false">F35</f>
+        <v>2946.4</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>3050.512</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <f aca="false">F40-E40</f>
+        <v>104.112</v>
+      </c>
+      <c r="H40" s="16" t="n">
+        <f aca="false">G40/0.3048</f>
+        <v>341.574803149607</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="K40" s="12"/>
+      <c r="L40" s="1" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <f aca="false">F35</f>
+        <v>2946.4</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>3050.512</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <f aca="false">F41-E41</f>
+        <v>104.112</v>
+      </c>
+      <c r="H41" s="16" t="n">
+        <f aca="false">G41/0.3048</f>
+        <v>341.574803149607</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="K41" s="12"/>
+      <c r="L41" s="1" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" s="24" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <f aca="false">F35</f>
+        <v>2946.4</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>3050.512</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <f aca="false">F42-E42</f>
+        <v>104.112</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <f aca="false">G42/0.3048</f>
+        <v>341.574803149607</v>
+      </c>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="M42" s="22"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
+      <c r="P42" s="23"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="22"/>
+      <c r="S42" s="22"/>
+    </row>
+    <row r="43" s="30" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>2.512</v>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>176.021</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <f aca="false">F43-E43</f>
+        <v>173.509</v>
+      </c>
+      <c r="H43" s="26" t="n">
+        <f aca="false">G43/0.3048</f>
+        <v>569.255249343832</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="K43" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="L43" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="M43" s="28"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>2.512</v>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>176.021</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <f aca="false">F44-E44</f>
+        <v>173.509</v>
+      </c>
+      <c r="H44" s="26" t="n">
+        <f aca="false">G44/0.3048</f>
+        <v>569.255249343832</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="K44" s="27"/>
+      <c r="L44" s="1" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>2.512</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>176.021</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <f aca="false">F45-E45</f>
+        <v>173.509</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <f aca="false">G45/0.3048</f>
+        <v>569.255249343832</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="K45" s="27"/>
+      <c r="L45" s="1" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>2.512</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>176.021</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <f aca="false">F46-E46</f>
+        <v>173.509</v>
+      </c>
+      <c r="H46" s="26" t="n">
+        <f aca="false">G46/0.3048</f>
+        <v>569.255249343832</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="K46" s="27"/>
+      <c r="L46" s="1" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <f aca="false">F38</f>
-        <v>259.8137</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>290.3484</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <f aca="false">F39-E39</f>
-        <v>30.5347</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <f aca="false">G39/0.3048</f>
-        <v>100.179461942257</v>
-      </c>
-      <c r="K39" s="19"/>
-      <c r="L39" s="1" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <f aca="false">F39</f>
-        <v>290.3484</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>317.5478</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <f aca="false">F40-E40</f>
-        <v>27.1994</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <f aca="false">G40/0.3048</f>
-        <v>89.2368766404198</v>
-      </c>
-      <c r="K40" s="19"/>
-      <c r="L40" s="1" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <f aca="false">F40</f>
-        <v>317.5478</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>345.1276</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <f aca="false">F41-E41</f>
-        <v>27.5798</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <f aca="false">G41/0.3048</f>
-        <v>90.4849081364829</v>
-      </c>
-      <c r="K41" s="19"/>
-      <c r="L41" s="1" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <f aca="false">F41</f>
-        <v>345.1276</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>368.2201</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <f aca="false">F42-E42</f>
-        <v>23.0925</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <f aca="false">G42/0.3048</f>
-        <v>75.7627952755906</v>
-      </c>
-      <c r="K42" s="19"/>
-      <c r="L42" s="1" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <f aca="false">F42</f>
-        <v>368.2201</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>397.2453</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <f aca="false">F43-E43</f>
-        <v>29.0252</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <f aca="false">G43/0.3048</f>
-        <v>95.2270341207349</v>
-      </c>
-      <c r="K43" s="19"/>
-      <c r="L43" s="1" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44" s="2" t="n">
+      <c r="E47" s="2" t="n">
         <f aca="false">F43</f>
-        <v>397.2453</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>427.6908</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <f aca="false">F44-E44</f>
-        <v>30.4455</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <f aca="false">G44/0.3048</f>
-        <v>99.8868110236222</v>
-      </c>
-      <c r="K44" s="19"/>
-      <c r="L44" s="1" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <f aca="false">F44</f>
-        <v>427.6908</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>454.5479</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <f aca="false">F45-E45</f>
-        <v>26.8571</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <f aca="false">G45/0.3048</f>
-        <v>88.113845144357</v>
-      </c>
-      <c r="K45" s="19"/>
-      <c r="L45" s="1" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <f aca="false">F45</f>
-        <v>454.5479</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>483.808</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <f aca="false">F46-E46</f>
-        <v>29.2601</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <f aca="false">G46/0.3048</f>
-        <v>95.9977034120734</v>
-      </c>
-      <c r="K46" s="19"/>
-      <c r="L46" s="1" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <f aca="false">F46</f>
-        <v>483.808</v>
+        <v>176.021</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>517.657</v>
+        <v>206.2677</v>
       </c>
       <c r="G47" s="2" t="n">
         <f aca="false">F47-E47</f>
-        <v>33.849</v>
+        <v>30.2467</v>
       </c>
       <c r="H47" s="5" t="n">
         <f aca="false">G47/0.3048</f>
-        <v>111.053149606299</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="K47" s="19"/>
+        <v>99.2345800524934</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K47" s="27"/>
       <c r="L47" s="1" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="n">
         <v>1</v>
@@ -3229,35 +3279,32 @@
       <c r="C48" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>118</v>
+      <c r="D48" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E48" s="2" t="n">
         <f aca="false">F47</f>
-        <v>517.657</v>
+        <v>206.2677</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>559.586492</v>
+        <v>232.228</v>
       </c>
       <c r="G48" s="2" t="n">
         <f aca="false">F48-E48</f>
-        <v>41.929492</v>
-      </c>
-      <c r="H48" s="2" t="n">
+        <v>25.9603</v>
+      </c>
+      <c r="H48" s="5" t="n">
         <f aca="false">G48/0.3048</f>
-        <v>137.563950131234</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K48" s="19"/>
+        <v>85.1715879265093</v>
+      </c>
+      <c r="K48" s="27"/>
       <c r="L48" s="1" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B49" s="1" t="n">
         <v>1</v>
@@ -3265,32 +3312,32 @@
       <c r="C49" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>118</v>
+      <c r="D49" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E49" s="2" t="n">
         <f aca="false">F48</f>
-        <v>559.586492</v>
+        <v>232.228</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>594.786492</v>
+        <v>259.8137</v>
       </c>
       <c r="G49" s="2" t="n">
         <f aca="false">F49-E49</f>
-        <v>35.1999999999999</v>
-      </c>
-      <c r="H49" s="2" t="n">
+        <v>27.5857</v>
+      </c>
+      <c r="H49" s="5" t="n">
         <f aca="false">G49/0.3048</f>
-        <v>115.485564304462</v>
-      </c>
-      <c r="K49" s="19"/>
+        <v>90.5042650918634</v>
+      </c>
+      <c r="K49" s="27"/>
       <c r="L49" s="1" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B50" s="1" t="n">
         <v>1</v>
@@ -3298,32 +3345,32 @@
       <c r="C50" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>118</v>
+      <c r="D50" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E50" s="2" t="n">
         <f aca="false">F49</f>
-        <v>594.786492</v>
+        <v>259.8137</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>629.986492</v>
+        <v>290.3484</v>
       </c>
       <c r="G50" s="2" t="n">
         <f aca="false">F50-E50</f>
-        <v>35.2</v>
-      </c>
-      <c r="H50" s="2" t="n">
+        <v>30.5347</v>
+      </c>
+      <c r="H50" s="5" t="n">
         <f aca="false">G50/0.3048</f>
-        <v>115.485564304462</v>
-      </c>
-      <c r="K50" s="19"/>
+        <v>100.179461942257</v>
+      </c>
+      <c r="K50" s="27"/>
       <c r="L50" s="1" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B51" s="1" t="n">
         <v>1</v>
@@ -3331,35 +3378,32 @@
       <c r="C51" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>118</v>
+      <c r="D51" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E51" s="2" t="n">
         <f aca="false">F50</f>
-        <v>629.986492</v>
+        <v>290.3484</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>670.486492</v>
+        <v>317.5478</v>
       </c>
       <c r="G51" s="2" t="n">
         <f aca="false">F51-E51</f>
-        <v>40.5</v>
-      </c>
-      <c r="H51" s="2" t="n">
+        <v>27.1994</v>
+      </c>
+      <c r="H51" s="5" t="n">
         <f aca="false">G51/0.3048</f>
-        <v>132.874015748032</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K51" s="19"/>
+        <v>89.2368766404198</v>
+      </c>
+      <c r="K51" s="27"/>
       <c r="L51" s="1" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B52" s="1" t="n">
         <v>1</v>
@@ -3367,38 +3411,32 @@
       <c r="C52" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>125</v>
+      <c r="D52" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E52" s="2" t="n">
         <f aca="false">F51</f>
-        <v>670.486492</v>
+        <v>317.5478</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>686.41</v>
+        <v>345.1276</v>
       </c>
       <c r="G52" s="2" t="n">
         <f aca="false">F52-E52</f>
-        <v>15.923508</v>
+        <v>27.5798</v>
       </c>
       <c r="H52" s="5" t="n">
         <f aca="false">G52/0.3048</f>
-        <v>52.2424803149605</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K52" s="19"/>
+        <v>90.4849081364829</v>
+      </c>
+      <c r="K52" s="27"/>
       <c r="L52" s="1" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B53" s="1" t="n">
         <v>1</v>
@@ -3406,240 +3444,619 @@
       <c r="C53" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>129</v>
+      <c r="D53" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E53" s="2" t="n">
         <f aca="false">F52</f>
-        <v>686.41</v>
+        <v>345.1276</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>717.475</v>
+        <v>368.2201</v>
       </c>
       <c r="G53" s="2" t="n">
         <f aca="false">F53-E53</f>
-        <v>31.0650000000001</v>
+        <v>23.0925</v>
       </c>
       <c r="H53" s="5" t="n">
         <f aca="false">G53/0.3048</f>
-        <v>101.919291338583</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="K53" s="19"/>
+        <v>75.7627952755906</v>
+      </c>
+      <c r="K53" s="27"/>
       <c r="L53" s="1" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>133</v>
+      <c r="D54" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>686.41033</v>
+        <f aca="false">F53</f>
+        <v>368.2201</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>714.0762</v>
+        <v>397.2453</v>
       </c>
       <c r="G54" s="2" t="n">
         <f aca="false">F54-E54</f>
-        <v>27.6658699999999</v>
+        <v>29.0252</v>
       </c>
       <c r="H54" s="5" t="n">
         <f aca="false">G54/0.3048</f>
-        <v>90.7672900262465</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J54" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="K54" s="19"/>
+        <v>95.2270341207349</v>
+      </c>
+      <c r="K54" s="27"/>
       <c r="L54" s="1" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>137</v>
+      <c r="D55" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>700.528</v>
+        <f aca="false">F54</f>
+        <v>397.2453</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>740.280986</v>
+        <v>427.6908</v>
       </c>
       <c r="G55" s="2" t="n">
         <f aca="false">F55-E55</f>
-        <v>39.752986</v>
+        <v>30.4455</v>
       </c>
       <c r="H55" s="5" t="n">
         <f aca="false">G55/0.3048</f>
-        <v>130.423182414698</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J55" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="K55" s="19"/>
+        <v>99.8868110236222</v>
+      </c>
+      <c r="K55" s="27"/>
       <c r="L55" s="1" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>140</v>
+      <c r="D56" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>733.772</v>
+        <f aca="false">F55</f>
+        <v>427.6908</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>756.099561</v>
+        <v>454.5479</v>
       </c>
       <c r="G56" s="2" t="n">
         <f aca="false">F56-E56</f>
-        <v>22.3275609999999</v>
+        <v>26.8571</v>
       </c>
       <c r="H56" s="5" t="n">
         <f aca="false">G56/0.3048</f>
-        <v>73.2531528871389</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J56" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="K56" s="19"/>
+        <v>88.113845144357</v>
+      </c>
+      <c r="K56" s="27"/>
       <c r="L56" s="1" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C57" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>733.772</v>
+      <c r="D57" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <f aca="false">F56</f>
+        <v>454.5479</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>758.29</v>
+        <v>483.808</v>
       </c>
       <c r="G57" s="2" t="n">
         <f aca="false">F57-E57</f>
-        <v>24.5179999999999</v>
+        <v>29.2601</v>
       </c>
       <c r="H57" s="5" t="n">
         <f aca="false">G57/0.3048</f>
+        <v>95.9977034120734</v>
+      </c>
+      <c r="K57" s="27"/>
+      <c r="L57" s="1" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <f aca="false">F57</f>
+        <v>483.808</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>517.657</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <f aca="false">F58-E58</f>
+        <v>33.849</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <f aca="false">G58/0.3048</f>
+        <v>111.053149606299</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K58" s="27"/>
+      <c r="L58" s="1" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <f aca="false">F58</f>
+        <v>517.657</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>559.586492</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <f aca="false">F59-E59</f>
+        <v>41.929492</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <f aca="false">G59/0.3048</f>
+        <v>137.563950131234</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K59" s="27"/>
+      <c r="L59" s="1" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <f aca="false">F59</f>
+        <v>559.586492</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>594.786492</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <f aca="false">F60-E60</f>
+        <v>35.1999999999999</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <f aca="false">G60/0.3048</f>
+        <v>115.485564304462</v>
+      </c>
+      <c r="K60" s="27"/>
+      <c r="L60" s="1" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <f aca="false">F60</f>
+        <v>594.786492</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>629.986492</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <f aca="false">F61-E61</f>
+        <v>35.2</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <f aca="false">G61/0.3048</f>
+        <v>115.485564304462</v>
+      </c>
+      <c r="K61" s="27"/>
+      <c r="L61" s="1" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <f aca="false">F61</f>
+        <v>629.986492</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>670.486492</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <f aca="false">F62-E62</f>
+        <v>40.5</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <f aca="false">G62/0.3048</f>
+        <v>132.874015748032</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K62" s="27"/>
+      <c r="L62" s="1" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <f aca="false">F62</f>
+        <v>670.486492</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>686.41</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <f aca="false">F63-E63</f>
+        <v>15.923508</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <f aca="false">G63/0.3048</f>
+        <v>52.2424803149605</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K63" s="27"/>
+      <c r="L63" s="1" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <f aca="false">F63</f>
+        <v>686.41</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>717.475</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <f aca="false">F64-E64</f>
+        <v>31.0650000000001</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <f aca="false">G64/0.3048</f>
+        <v>101.919291338583</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K64" s="27"/>
+      <c r="L64" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>686.41033</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>714.0762</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <f aca="false">F65-E65</f>
+        <v>27.6658699999999</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <f aca="false">G65/0.3048</f>
+        <v>90.7672900262465</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J65" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="K65" s="27"/>
+      <c r="L65" s="1" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>700.528</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>740.280986</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <f aca="false">F66-E66</f>
+        <v>39.752986</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <f aca="false">G66/0.3048</f>
+        <v>130.423182414698</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J66" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="K66" s="27"/>
+      <c r="L66" s="1" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>733.772</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>756.099561</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <f aca="false">F67-E67</f>
+        <v>22.3275609999999</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <f aca="false">G67/0.3048</f>
+        <v>73.2531528871389</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J67" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="K67" s="27"/>
+      <c r="L67" s="1" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>733.772</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>758.29</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <f aca="false">F68-E68</f>
+        <v>24.5179999999999</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <f aca="false">G68/0.3048</f>
         <v>80.4396325459315</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J57" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="K57" s="19"/>
-      <c r="L57" s="1" t="n">
+      <c r="I68" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J68" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="K68" s="27"/>
+      <c r="L68" s="1" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B58" s="7" t="n">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E58" s="7" t="n">
+      <c r="C69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E69" s="7" t="n">
         <v>176.021</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F69" s="9" t="n">
         <v>313.056</v>
       </c>
-      <c r="G58" s="9" t="n">
-        <f aca="false">F58-E58</f>
+      <c r="G69" s="9" t="n">
+        <f aca="false">F69-E69</f>
         <v>137.035</v>
       </c>
-      <c r="H58" s="10" t="n">
-        <f aca="false">G58/0.3048</f>
+      <c r="H69" s="10" t="n">
+        <f aca="false">G69/0.3048</f>
         <v>449.589895013123</v>
       </c>
-      <c r="I58" s="7"/>
-      <c r="J58" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="K58" s="21"/>
-      <c r="L58" s="1" t="n">
+      <c r="I69" s="7"/>
+      <c r="J69" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="K69" s="27"/>
+      <c r="L69" s="1" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>149</v>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" s="33" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="K4:K34"/>
-    <mergeCell ref="K35:K57"/>
+    <mergeCell ref="K4:K42"/>
+    <mergeCell ref="K43:K69"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3656,16 +4073,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L59"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="23" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="17.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="17.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="5.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.57"/>
@@ -3677,24 +4094,24 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="n">
+      <c r="B1" s="36" t="n">
         <v>101.6</v>
       </c>
       <c r="C1" s="4"/>
-      <c r="F1" s="26"/>
+      <c r="F1" s="37"/>
       <c r="G1" s="2"/>
       <c r="H1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
-      <c r="B2" s="27"/>
+      <c r="B2" s="38"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="26"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="37"/>
       <c r="G2" s="2"/>
       <c r="H2" s="5"/>
     </row>
@@ -3702,7 +4119,7 @@
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="40" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -3733,16 +4150,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>151</v>
+        <v>154</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>155</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2017.911482</v>
@@ -3759,10 +4176,10 @@
         <v>56.1799475065617</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>14</v>
@@ -3771,52 +4188,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>159</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E5" s="2" t="n">
-        <f aca="false">F4</f>
+        <v>2017.911482</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>2035.03513</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <f aca="false">21*B1</f>
-        <v>2133.6</v>
       </c>
       <c r="G5" s="2" t="n">
         <f aca="false">F5-E5</f>
-        <v>98.5648699999999</v>
+        <v>17.123648</v>
       </c>
       <c r="H5" s="5" t="n">
         <f aca="false">G5/0.3048</f>
-        <v>323.375557742782</v>
+        <v>56.1799475065617</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="K5" s="12"/>
       <c r="L5" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>10</v>
+      <c r="B6" s="38" t="s">
+        <v>155</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -3825,92 +4240,92 @@
         <v>161</v>
       </c>
       <c r="E6" s="2" t="n">
-        <f aca="false">F5</f>
+        <f aca="false">F4</f>
+        <v>2035.03513</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <f aca="false">21*B1</f>
         <v>2133.6</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
+        <f aca="false">F6-E6</f>
+        <v>98.5648699999999</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <f aca="false">G6/0.3048</f>
+        <v>323.375557742782</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <f aca="false">F4</f>
+        <v>2035.03513</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <f aca="false">21*B1</f>
+        <v>2133.6</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <f aca="false">F7-E7</f>
+        <v>98.5648699999999</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <f aca="false">G7/0.3048</f>
+        <v>323.375557742782</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <f aca="false">F6</f>
+        <v>2133.6</v>
+      </c>
+      <c r="F8" s="2" t="n">
         <f aca="false">22*B1</f>
         <v>2235.2</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <f aca="false">F6-E6</f>
-        <v>101.6</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <f aca="false">G6/0.3048</f>
-        <v>333.333333333333</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <f aca="false">F6</f>
-        <v>2235.2</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <f aca="false">23*B1</f>
-        <v>2336.8</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <f aca="false">F7-E7</f>
-        <v>101.6</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <f aca="false">G7/0.3048</f>
-        <v>333.333333333333</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="1" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <f aca="false">F7</f>
-        <v>2336.8</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <f aca="false">24*B1</f>
-        <v>2438.4</v>
       </c>
       <c r="G8" s="2" t="n">
         <f aca="false">F8-E8</f>
@@ -3921,36 +4336,36 @@
         <v>333.333333333333</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B9" s="27" t="n">
+        <v>169</v>
+      </c>
+      <c r="B9" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E9" s="2" t="n">
         <f aca="false">F8</f>
-        <v>2438.4</v>
+        <v>2235.2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <f aca="false">25*B1</f>
-        <v>2540</v>
+        <f aca="false">23*B1</f>
+        <v>2336.8</v>
       </c>
       <c r="G9" s="2" t="n">
         <f aca="false">F9-E9</f>
@@ -3958,39 +4373,39 @@
       </c>
       <c r="H9" s="5" t="n">
         <f aca="false">G9/0.3048</f>
-        <v>333.333333333334</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="27" t="n">
+        <v>172</v>
+      </c>
+      <c r="B10" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E10" s="2" t="n">
         <f aca="false">F9</f>
-        <v>2540</v>
+        <v>2336.8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <f aca="false">26*B1</f>
-        <v>2641.6</v>
+        <f aca="false">24*B1</f>
+        <v>2438.4</v>
       </c>
       <c r="G10" s="2" t="n">
         <f aca="false">F10-E10</f>
@@ -4001,36 +4416,36 @@
         <v>333.333333333333</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B11" s="27" t="n">
+        <v>176</v>
+      </c>
+      <c r="B11" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E11" s="2" t="n">
         <f aca="false">F10</f>
-        <v>2641.6</v>
+        <v>2438.4</v>
       </c>
       <c r="F11" s="2" t="n">
-        <f aca="false">27*B1</f>
-        <v>2743.2</v>
+        <f aca="false">25*B1</f>
+        <v>2540</v>
       </c>
       <c r="G11" s="2" t="n">
         <f aca="false">F11-E11</f>
@@ -4038,39 +4453,39 @@
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">G11/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="27" t="n">
+        <v>180</v>
+      </c>
+      <c r="B12" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E12" s="2" t="n">
         <f aca="false">F11</f>
-        <v>2743.2</v>
+        <v>2540</v>
       </c>
       <c r="F12" s="2" t="n">
-        <f aca="false">28*B1</f>
-        <v>2844.8</v>
+        <f aca="false">26*B1</f>
+        <v>2641.6</v>
       </c>
       <c r="G12" s="2" t="n">
         <f aca="false">F12-E12</f>
@@ -4088,29 +4503,29 @@
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="27" t="n">
+        <v>183</v>
+      </c>
+      <c r="B13" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">F12</f>
-        <v>2844.8</v>
+        <v>2641.6</v>
       </c>
       <c r="F13" s="2" t="n">
-        <f aca="false">29*B1</f>
-        <v>2946.4</v>
+        <f aca="false">27*B1</f>
+        <v>2743.2</v>
       </c>
       <c r="G13" s="2" t="n">
         <f aca="false">F13-E13</f>
@@ -4121,137 +4536,141 @@
         <v>333.333333333333</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="38" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="E14" s="9" t="n">
+      <c r="D14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <f aca="false">F13</f>
-        <v>2946.4</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>3050.512</v>
-      </c>
-      <c r="G14" s="9" t="n">
+        <v>2743.2</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <f aca="false">28*B1</f>
+        <v>2844.8</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <f aca="false">F14-E14</f>
-        <v>104.112000000001</v>
-      </c>
-      <c r="H14" s="10" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <f aca="false">G14/0.3048</f>
-        <v>341.574803149608</v>
-      </c>
-      <c r="I14" s="7" t="s">
+        <v>333.333333333333</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="1" t="s">
         <v>187</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="1" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>188</v>
+        <v>89</v>
+      </c>
+      <c r="B15" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.512</v>
+        <f aca="false">F14</f>
+        <v>2844.8</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>176.021</v>
+        <f aca="false">29*B1</f>
+        <v>2946.4</v>
       </c>
       <c r="G15" s="2" t="n">
         <f aca="false">F15-E15</f>
-        <v>173.509</v>
+        <v>101.6</v>
       </c>
       <c r="H15" s="5" t="n">
         <f aca="false">G15/0.3048</f>
-        <v>569.255249343832</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K15" s="12"/>
+      <c r="L15" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="E16" s="9" t="n">
+        <f aca="false">F15</f>
+        <v>2946.4</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>3050.512</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <f aca="false">F16-E16</f>
+        <v>104.112000000001</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <f aca="false">G16/0.3048</f>
+        <v>341.574803149608</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="K15" s="30" t="s">
+      <c r="J16" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="1" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L15" s="1" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B16" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <f aca="false">F15</f>
-        <v>176.021</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>203.53</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <f aca="false">F16-E16</f>
-        <v>27.509</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <f aca="false">G16/0.3048</f>
-        <v>90.2526246719161</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K16" s="30"/>
-      <c r="L16" s="1" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B17" s="27" t="n">
-        <v>10</v>
+      <c r="B17" s="38" t="s">
+        <v>155</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>1</v>
@@ -4260,31 +4679,38 @@
         <v>193</v>
       </c>
       <c r="E17" s="2" t="n">
-        <f aca="false">F16</f>
-        <v>203.53</v>
+        <v>2.512</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>231.2793</v>
+        <v>176.021</v>
       </c>
       <c r="G17" s="2" t="n">
         <f aca="false">F17-E17</f>
-        <v>27.7493</v>
+        <v>173.509</v>
       </c>
       <c r="H17" s="5" t="n">
         <f aca="false">G17/0.3048</f>
-        <v>91.0410104986877</v>
-      </c>
-      <c r="K17" s="30"/>
+        <v>569.255249343832</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K17" s="41" t="s">
+        <v>105</v>
+      </c>
       <c r="L17" s="1" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="38" t="s">
         <v>196</v>
-      </c>
-      <c r="B18" s="27" t="n">
-        <v>10</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>1</v>
@@ -4293,764 +4719,871 @@
         <v>193</v>
       </c>
       <c r="E18" s="2" t="n">
-        <f aca="false">F17</f>
-        <v>231.2793</v>
+        <v>2.512</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>260.48</v>
+        <v>176.021</v>
       </c>
       <c r="G18" s="2" t="n">
         <f aca="false">F18-E18</f>
-        <v>29.2007</v>
+        <v>173.509</v>
       </c>
       <c r="H18" s="5" t="n">
         <f aca="false">G18/0.3048</f>
-        <v>95.8028215223098</v>
-      </c>
-      <c r="K18" s="30"/>
+        <v>569.255249343832</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" s="41"/>
       <c r="L18" s="1" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E19" s="2" t="n">
-        <f aca="false">F18</f>
-        <v>260.48</v>
+        <f aca="false">F17</f>
+        <v>176.021</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>286.76</v>
+        <v>203.53</v>
       </c>
       <c r="G19" s="2" t="n">
         <f aca="false">F19-E19</f>
-        <v>26.28</v>
+        <v>27.509</v>
       </c>
       <c r="H19" s="5" t="n">
         <f aca="false">G19/0.3048</f>
-        <v>86.2204724409448</v>
-      </c>
-      <c r="K19" s="30"/>
+        <v>90.2526246719161</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="K19" s="41"/>
       <c r="L19" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B20" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B20" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="E20" s="2" t="n">
         <f aca="false">F19</f>
-        <v>286.76</v>
+        <v>203.53</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>314.53</v>
+        <v>231.2793</v>
       </c>
       <c r="G20" s="2" t="n">
         <f aca="false">F20-E20</f>
-        <v>27.77</v>
+        <v>27.7493</v>
       </c>
       <c r="H20" s="5" t="n">
         <f aca="false">G20/0.3048</f>
-        <v>91.1089238845144</v>
-      </c>
-      <c r="K20" s="30"/>
+        <v>91.0410104986877</v>
+      </c>
+      <c r="K20" s="41"/>
       <c r="L20" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B21" s="27" t="n">
+        <v>201</v>
+      </c>
+      <c r="B21" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E21" s="2" t="n">
         <f aca="false">F20</f>
-        <v>314.53</v>
+        <v>231.2793</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>342.27</v>
+        <v>260.48</v>
       </c>
       <c r="G21" s="2" t="n">
         <f aca="false">F21-E21</f>
-        <v>27.74</v>
+        <v>29.2007</v>
       </c>
       <c r="H21" s="5" t="n">
         <f aca="false">G21/0.3048</f>
-        <v>91.0104986876641</v>
-      </c>
-      <c r="K21" s="30"/>
+        <v>95.8028215223098</v>
+      </c>
+      <c r="K21" s="41"/>
       <c r="L21" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B22" s="27" t="n">
+        <v>202</v>
+      </c>
+      <c r="B22" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E22" s="2" t="n">
         <f aca="false">F21</f>
-        <v>342.27</v>
+        <v>260.48</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>371.42</v>
+        <v>286.76</v>
       </c>
       <c r="G22" s="2" t="n">
         <f aca="false">F22-E22</f>
-        <v>29.15</v>
+        <v>26.28</v>
       </c>
       <c r="H22" s="5" t="n">
         <f aca="false">G22/0.3048</f>
-        <v>95.6364829396327</v>
-      </c>
-      <c r="K22" s="30"/>
+        <v>86.2204724409448</v>
+      </c>
+      <c r="K22" s="41"/>
       <c r="L22" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B23" s="27" t="n">
+        <v>203</v>
+      </c>
+      <c r="B23" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E23" s="2" t="n">
         <f aca="false">F22</f>
-        <v>371.42</v>
+        <v>286.76</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>397.76</v>
+        <v>314.53</v>
       </c>
       <c r="G23" s="2" t="n">
         <f aca="false">F23-E23</f>
-        <v>26.34</v>
+        <v>27.77</v>
       </c>
       <c r="H23" s="5" t="n">
         <f aca="false">G23/0.3048</f>
-        <v>86.4173228346456</v>
-      </c>
-      <c r="K23" s="30"/>
+        <v>91.1089238845144</v>
+      </c>
+      <c r="K23" s="41"/>
       <c r="L23" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B24" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="B24" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E24" s="2" t="n">
         <f aca="false">F23</f>
-        <v>397.76</v>
+        <v>314.53</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>425.53</v>
+        <v>342.27</v>
       </c>
       <c r="G24" s="2" t="n">
         <f aca="false">F24-E24</f>
-        <v>27.77</v>
+        <v>27.74</v>
       </c>
       <c r="H24" s="5" t="n">
         <f aca="false">G24/0.3048</f>
-        <v>91.1089238845144</v>
-      </c>
-      <c r="K24" s="30"/>
+        <v>91.0104986876641</v>
+      </c>
+      <c r="K24" s="41"/>
       <c r="L24" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B25" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="B25" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E25" s="2" t="n">
         <f aca="false">F24</f>
-        <v>425.53</v>
+        <v>342.27</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>453.28</v>
+        <v>371.42</v>
       </c>
       <c r="G25" s="2" t="n">
         <f aca="false">F25-E25</f>
-        <v>27.75</v>
+        <v>29.15</v>
       </c>
       <c r="H25" s="5" t="n">
         <f aca="false">G25/0.3048</f>
-        <v>91.0433070866142</v>
-      </c>
-      <c r="K25" s="30"/>
+        <v>95.6364829396327</v>
+      </c>
+      <c r="K25" s="41"/>
       <c r="L25" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B26" s="27" t="n">
+        <v>206</v>
+      </c>
+      <c r="B26" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E26" s="2" t="n">
         <f aca="false">F25</f>
-        <v>453.28</v>
+        <v>371.42</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>481.03</v>
+        <v>397.76</v>
       </c>
       <c r="G26" s="2" t="n">
         <f aca="false">F26-E26</f>
-        <v>27.75</v>
+        <v>26.34</v>
       </c>
       <c r="H26" s="5" t="n">
         <f aca="false">G26/0.3048</f>
-        <v>91.0433070866142</v>
-      </c>
-      <c r="K26" s="30"/>
+        <v>86.4173228346456</v>
+      </c>
+      <c r="K26" s="41"/>
       <c r="L26" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B27" s="27" t="n">
+        <v>207</v>
+      </c>
+      <c r="B27" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E27" s="2" t="n">
         <f aca="false">F26</f>
-        <v>481.03</v>
+        <v>397.76</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>514.740001</v>
+        <v>425.53</v>
       </c>
       <c r="G27" s="2" t="n">
         <f aca="false">F27-E27</f>
-        <v>33.710001</v>
+        <v>27.77</v>
       </c>
       <c r="H27" s="5" t="n">
         <f aca="false">G27/0.3048</f>
-        <v>110.597116141732</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="K27" s="30"/>
+        <v>91.1089238845144</v>
+      </c>
+      <c r="K27" s="41"/>
       <c r="L27" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B28" s="27" t="n">
+        <v>208</v>
+      </c>
+      <c r="B28" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E28" s="2" t="n">
         <f aca="false">F27</f>
-        <v>514.740001</v>
+        <v>425.53</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>551.208985</v>
+        <v>453.28</v>
       </c>
       <c r="G28" s="2" t="n">
         <f aca="false">F28-E28</f>
-        <v>36.468984</v>
-      </c>
-      <c r="H28" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <f aca="false">G28/0.3048</f>
-        <v>119.648897637795</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="K28" s="30"/>
+        <v>91.0433070866142</v>
+      </c>
+      <c r="K28" s="41"/>
       <c r="L28" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B29" s="27" t="n">
+        <v>209</v>
+      </c>
+      <c r="B29" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E29" s="2" t="n">
         <f aca="false">F28</f>
-        <v>551.208985</v>
+        <v>453.28</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>587.322985</v>
+        <v>481.03</v>
       </c>
       <c r="G29" s="2" t="n">
         <f aca="false">F29-E29</f>
-        <v>36.114</v>
-      </c>
-      <c r="H29" s="2" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <f aca="false">G29/0.3048</f>
-        <v>118.484251968504</v>
-      </c>
-      <c r="K29" s="30"/>
+        <v>91.0433070866142</v>
+      </c>
+      <c r="K29" s="41"/>
       <c r="L29" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B30" s="27" t="n">
+        <v>210</v>
+      </c>
+      <c r="B30" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E30" s="2" t="n">
         <f aca="false">F29</f>
-        <v>587.322985</v>
+        <v>481.03</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>623.436985</v>
+        <v>514.740001</v>
       </c>
       <c r="G30" s="2" t="n">
         <f aca="false">F30-E30</f>
-        <v>36.114</v>
-      </c>
-      <c r="H30" s="2" t="n">
+        <v>33.710001</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <f aca="false">G30/0.3048</f>
-        <v>118.484251968504</v>
-      </c>
-      <c r="K30" s="30"/>
+        <v>110.597116141732</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K30" s="41"/>
       <c r="L30" s="1" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E31" s="2" t="n">
         <f aca="false">F30</f>
-        <v>623.436985</v>
+        <v>514.740001</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>670.486493</v>
+        <v>551.208985</v>
       </c>
       <c r="G31" s="2" t="n">
         <f aca="false">F31-E31</f>
-        <v>47.0495079999999</v>
+        <v>36.468984</v>
       </c>
       <c r="H31" s="2" t="n">
         <f aca="false">G31/0.3048</f>
-        <v>154.361902887139</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K31" s="30"/>
+        <v>119.648897637795</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="K31" s="41"/>
       <c r="L31" s="1" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B32" s="27" t="n">
+        <v>215</v>
+      </c>
+      <c r="B32" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E32" s="2" t="n">
         <f aca="false">F31</f>
-        <v>670.486493</v>
+        <v>551.208985</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>686.41</v>
+        <v>587.322985</v>
       </c>
       <c r="G32" s="2" t="n">
         <f aca="false">F32-E32</f>
-        <v>15.923507</v>
-      </c>
-      <c r="H32" s="5" t="n">
+        <v>36.114</v>
+      </c>
+      <c r="H32" s="2" t="n">
         <f aca="false">G32/0.3048</f>
-        <v>52.2424770341206</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="K32" s="30"/>
+        <v>118.484251968504</v>
+      </c>
+      <c r="K32" s="41"/>
       <c r="L32" s="1" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B33" s="27" t="n">
+        <v>216</v>
+      </c>
+      <c r="B33" s="38" t="n">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E33" s="2" t="n">
         <f aca="false">F32</f>
-        <v>686.41</v>
+        <v>587.322985</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>717.475</v>
+        <v>623.436985</v>
       </c>
       <c r="G33" s="2" t="n">
         <f aca="false">F33-E33</f>
-        <v>31.0650000000001</v>
-      </c>
-      <c r="H33" s="5" t="n">
+        <v>36.114</v>
+      </c>
+      <c r="H33" s="2" t="n">
         <f aca="false">G33/0.3048</f>
-        <v>101.919291338583</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="K33" s="30"/>
+        <v>118.484251968504</v>
+      </c>
+      <c r="K33" s="41"/>
       <c r="L33" s="1" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B34" s="27" t="n">
-        <v>11</v>
+        <v>217</v>
+      </c>
+      <c r="B34" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>686.410331</v>
+        <f aca="false">F33</f>
+        <v>623.436985</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>714.076201</v>
+        <v>670.486493</v>
       </c>
       <c r="G34" s="2" t="n">
         <f aca="false">F34-E34</f>
-        <v>27.6658699999999</v>
-      </c>
-      <c r="H34" s="5" t="n">
+        <v>47.0495079999999</v>
+      </c>
+      <c r="H34" s="2" t="n">
         <f aca="false">G34/0.3048</f>
-        <v>90.7672900262465</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>224</v>
+        <v>154.361902887139</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K34" s="30"/>
+        <v>218</v>
+      </c>
+      <c r="K34" s="41"/>
       <c r="L34" s="1" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B35" s="27" t="n">
-        <v>15</v>
+        <v>219</v>
+      </c>
+      <c r="B35" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>146</v>
+        <v>220</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>69.408165</v>
+        <f aca="false">F34</f>
+        <v>670.486493</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>313.055703</v>
+        <v>686.41</v>
       </c>
       <c r="G35" s="2" t="n">
         <f aca="false">F35-E35</f>
-        <v>243.647538</v>
+        <v>15.923507</v>
       </c>
       <c r="H35" s="5" t="n">
         <f aca="false">G35/0.3048</f>
-        <v>799.368562992126</v>
+        <v>52.2424770341206</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K35" s="30"/>
+        <v>222</v>
+      </c>
+      <c r="K35" s="41"/>
       <c r="L35" s="1" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>12</v>
+        <v>223</v>
+      </c>
+      <c r="B36" s="38" t="n">
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>700.528</v>
+        <f aca="false">F35</f>
+        <v>686.41</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>759.061929</v>
+        <v>717.475</v>
       </c>
       <c r="G36" s="2" t="n">
         <f aca="false">F36-E36</f>
-        <v>58.5339289999999</v>
+        <v>31.0650000000001</v>
       </c>
       <c r="H36" s="5" t="n">
         <f aca="false">G36/0.3048</f>
-        <v>192.040449475065</v>
+        <v>101.919291338583</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="1" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>686.410331</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>714.076201</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <f aca="false">F37-E37</f>
+        <v>27.6658699999999</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <f aca="false">G37/0.3048</f>
+        <v>90.7672900262465</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J36" s="20" t="s">
+      <c r="K37" s="41"/>
+      <c r="L37" s="1" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>69.408165</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>313.055703</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <f aca="false">F38-E38</f>
+        <v>243.647538</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <f aca="false">G38/0.3048</f>
+        <v>799.368562992126</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K36" s="30"/>
-      <c r="L36" s="1" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B37" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>739.999999</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>758.360869</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <f aca="false">F37-E37</f>
-        <v>18.36087</v>
-      </c>
-      <c r="H37" s="10" t="n">
-        <f aca="false">G37/0.3048</f>
-        <v>60.2390748031495</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="30"/>
-      <c r="L37" s="1" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K38" s="31"/>
+      <c r="J38" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K38" s="41"/>
+      <c r="L38" s="1" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B39" s="27"/>
-      <c r="K39" s="31"/>
+        <v>232</v>
+      </c>
+      <c r="B39" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>700.528</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>759.061929</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <f aca="false">F39-E39</f>
+        <v>58.5339289999999</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <f aca="false">G39/0.3048</f>
+        <v>192.040449475065</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J39" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="1" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="K40" s="31"/>
+      <c r="A40" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B40" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>739.999999</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>758.360869</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <f aca="false">F40-E40</f>
+        <v>18.36087</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <f aca="false">G40/0.3048</f>
+        <v>60.2390748031495</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="J40" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="1" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K41" s="31"/>
+      <c r="K41" s="42"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K42" s="31"/>
+      <c r="A42" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="38"/>
+      <c r="K42" s="42"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K43" s="31"/>
+      <c r="A43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="K43" s="42"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K44" s="31"/>
+      <c r="K44" s="42"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K45" s="31"/>
+      <c r="K45" s="42"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K46" s="31"/>
+      <c r="K46" s="42"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K47" s="31"/>
+      <c r="K47" s="42"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K48" s="31"/>
+      <c r="K48" s="42"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K49" s="31"/>
+      <c r="K49" s="42"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K50" s="31"/>
+      <c r="K50" s="42"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K51" s="31"/>
+      <c r="K51" s="42"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K52" s="31"/>
+      <c r="K52" s="42"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K53" s="31"/>
+      <c r="K53" s="42"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K54" s="31"/>
+      <c r="K54" s="42"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K55" s="31"/>
+      <c r="K55" s="42"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K56" s="31"/>
+      <c r="K56" s="42"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K57" s="42"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K58" s="42"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K59" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="K4:K14"/>
-    <mergeCell ref="K15:K37"/>
+    <mergeCell ref="K4:K16"/>
+    <mergeCell ref="K17:K40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5068,12 +5601,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="10.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.71"/>
@@ -5081,7 +5614,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -5104,13 +5637,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>517.54</v>
@@ -5127,18 +5660,18 @@
         <v>8.02654855643056</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>519.986492</v>
@@ -5155,18 +5688,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>524.386492</v>
@@ -5183,18 +5716,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>528.786492</v>
@@ -5211,18 +5744,18 @@
         <v>14.435695538058</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>533.186492</v>
@@ -5239,18 +5772,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>537.586492</v>
@@ -5267,18 +5800,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>541.986492</v>
@@ -5295,18 +5828,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>546.386492</v>
@@ -5323,18 +5856,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>550.786492</v>
@@ -5351,18 +5884,18 @@
         <v>14.435695538058</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>555.186492</v>
@@ -5379,18 +5912,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>559.586492</v>
@@ -5407,7 +5940,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>26</v>
@@ -5415,13 +5948,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>563.986492</v>
@@ -5438,7 +5971,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>27</v>
@@ -5446,13 +5979,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>568.386492</v>
@@ -5469,7 +6002,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>28</v>
@@ -5477,13 +6010,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>572.786492</v>
@@ -5500,7 +6033,7 @@
         <v>14.435695538058</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>29</v>
@@ -5508,13 +6041,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>577.186492</v>
@@ -5531,7 +6064,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>30</v>
@@ -5539,13 +6072,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>581.586492</v>
@@ -5562,7 +6095,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>31</v>
@@ -5570,13 +6103,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>585.986492</v>
@@ -5593,7 +6126,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>32</v>
@@ -5601,13 +6134,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>590.386492</v>
@@ -5624,7 +6157,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>33</v>
@@ -5632,13 +6165,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>594.786492</v>
@@ -5655,7 +6188,7 @@
         <v>14.435695538058</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>34</v>
@@ -5663,13 +6196,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>599.186492</v>
@@ -5686,18 +6219,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>603.586492</v>
@@ -5714,7 +6247,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>36</v>
@@ -5722,13 +6255,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>607.986492</v>
@@ -5745,7 +6278,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>37</v>
@@ -5753,13 +6286,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>612.386492</v>
@@ -5776,7 +6309,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>38</v>
@@ -5784,13 +6317,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>616.786492</v>
@@ -5807,7 +6340,7 @@
         <v>14.435695538058</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>39</v>
@@ -5815,13 +6348,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>621.186492</v>
@@ -5838,7 +6371,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>40</v>
@@ -5846,13 +6379,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>625.586492</v>
@@ -5869,7 +6402,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>41</v>
@@ -5877,13 +6410,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>629.986492</v>
@@ -5900,7 +6433,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>42</v>
@@ -5908,13 +6441,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>634.386492</v>
@@ -5931,7 +6464,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>43</v>
@@ -5939,13 +6472,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>638.786492</v>
@@ -5962,7 +6495,7 @@
         <v>14.435695538058</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>44</v>
@@ -5970,13 +6503,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>643.186492</v>
@@ -5993,7 +6526,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>45</v>
@@ -6001,13 +6534,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>647.586492</v>
@@ -6024,7 +6557,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>46</v>
@@ -6032,13 +6565,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>651.986492</v>
@@ -6055,7 +6588,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>47</v>
@@ -6063,13 +6596,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>656.386492</v>
@@ -6086,18 +6619,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>660.786492</v>
@@ -6114,18 +6647,18 @@
         <v>14.435695538058</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>665.186492</v>
@@ -6142,7 +6675,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -6162,16 +6695,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="10.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -6194,13 +6727,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>514.740001</v>
@@ -6217,7 +6750,7 @@
         <v>14.3295603674542</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>13</v>
@@ -6225,13 +6758,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>519.107651</v>
@@ -6248,7 +6781,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>14</v>
@@ -6256,13 +6789,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>523.120318</v>
@@ -6279,7 +6812,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>15</v>
@@ -6287,13 +6820,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>527.132985</v>
@@ -6310,7 +6843,7 @@
         <v>13.164914698163</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>16</v>
@@ -6318,13 +6851,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>531.145651</v>
@@ -6341,7 +6874,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>17</v>
@@ -6349,13 +6882,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>535.158318</v>
@@ -6372,7 +6905,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>18</v>
@@ -6380,13 +6913,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>539.170985</v>
@@ -6403,7 +6936,7 @@
         <v>13.164914698163</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>19</v>
@@ -6411,13 +6944,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>543.183651</v>
@@ -6434,7 +6967,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>20</v>
@@ -6442,13 +6975,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>547.196318</v>
@@ -6465,19 +6998,19 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>551.208985</v>
@@ -6494,7 +7027,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>22</v>
@@ -6502,13 +7035,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>555.221651</v>
@@ -6525,7 +7058,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>23</v>
@@ -6533,13 +7066,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>559.234318</v>
@@ -6556,7 +7089,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>24</v>
@@ -6564,13 +7097,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>563.246985</v>
@@ -6587,7 +7120,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>25</v>
@@ -6595,13 +7128,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>567.259651</v>
@@ -6618,7 +7151,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>26</v>
@@ -6626,13 +7159,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>571.272318</v>
@@ -6649,7 +7182,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>27</v>
@@ -6657,13 +7190,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>575.284985</v>
@@ -6680,19 +7213,19 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>579.297651</v>
@@ -6709,7 +7242,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>29</v>
@@ -6717,13 +7250,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>583.310318</v>
@@ -6740,7 +7273,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>30</v>
@@ -6748,13 +7281,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>587.322985</v>
@@ -6771,7 +7304,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>31</v>
@@ -6779,13 +7312,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>591.335651</v>
@@ -6802,7 +7335,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>32</v>
@@ -6810,13 +7343,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>595.348318</v>
@@ -6833,7 +7366,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>33</v>
@@ -6841,13 +7374,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>599.360985</v>
@@ -6864,7 +7397,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>34</v>
@@ -6872,13 +7405,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>603.373651</v>
@@ -6895,7 +7428,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>35</v>
@@ -6903,13 +7436,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>607.386318</v>
@@ -6926,7 +7459,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>36</v>
@@ -6934,13 +7467,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>611.398985</v>
@@ -6957,7 +7490,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>37</v>
@@ -6965,13 +7498,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>615.411651</v>
@@ -6988,7 +7521,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>38</v>
@@ -6996,13 +7529,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>619.424318</v>
@@ -7019,7 +7552,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>39</v>
@@ -7027,13 +7560,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>623.436985</v>
@@ -7050,7 +7583,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>40</v>
@@ -7058,13 +7591,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>627.449651</v>
@@ -7081,7 +7614,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>41</v>
@@ -7089,13 +7622,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>631.462318</v>
@@ -7112,7 +7645,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>42</v>
@@ -7120,13 +7653,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>635.474985</v>
@@ -7143,7 +7676,7 @@
         <v>13.164914698163</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>43</v>
@@ -7151,13 +7684,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>639.487651</v>
@@ -7174,7 +7707,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>44</v>
@@ -7182,13 +7715,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>643.500318</v>
@@ -7205,7 +7738,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>45</v>
@@ -7213,13 +7746,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>647.512985</v>
@@ -7236,7 +7769,7 @@
         <v>13.164914698163</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>46</v>
@@ -7244,13 +7777,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>651.525651</v>
@@ -7267,7 +7800,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>47</v>
@@ -7275,13 +7808,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>655.538318</v>
@@ -7298,18 +7831,18 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>659.550985</v>
@@ -7326,18 +7859,18 @@
         <v>13.164914698163</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>663.563651</v>
@@ -7354,7 +7887,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/python/scripts/oracle_upload/sectors.xlsx
+++ b/python/scripts/oracle_upload/sectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="scS" sheetId="1" state="visible" r:id="rId2"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="396">
   <si>
     <t xml:space="preserve">Lsector=</t>
   </si>
@@ -511,6 +511,12 @@
     <t xml:space="preserve">15</t>
   </si>
   <si>
+    <t xml:space="preserve">BEGGSPEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDGSPEC</t>
+  </si>
+  <si>
     <t xml:space="preserve">S21</t>
   </si>
   <si>
@@ -524,6 +530,12 @@
   </si>
   <si>
     <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEGSPEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDSPEC</t>
   </si>
   <si>
     <t xml:space="preserve">S22</t>
@@ -1539,8 +1551,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="71.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="31.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="5.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.28"/>
@@ -4073,7 +4085,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.29"/>
@@ -4216,10 +4228,10 @@
         <v>56.1799475065617</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K5" s="12"/>
       <c r="L5" s="1" t="n">
@@ -4228,7 +4240,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B6" s="38" t="s">
         <v>155</v>
@@ -4237,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E6" s="2" t="n">
         <f aca="false">F4</f>
@@ -4256,10 +4268,10 @@
         <v>323.375557742782</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="1" t="n">
@@ -4268,16 +4280,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E7" s="2" t="n">
         <f aca="false">F4</f>
@@ -4296,10 +4308,10 @@
         <v>323.375557742782</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="1" t="n">
@@ -4308,7 +4320,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B8" s="38" t="n">
         <v>10</v>
@@ -4317,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E8" s="2" t="n">
         <f aca="false">F6</f>
@@ -4336,10 +4348,10 @@
         <v>333.333333333333</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="1" t="n">
@@ -4348,7 +4360,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B9" s="38" t="n">
         <v>10</v>
@@ -4357,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E9" s="2" t="n">
         <f aca="false">F8</f>
@@ -4373,13 +4385,13 @@
       </c>
       <c r="H9" s="5" t="n">
         <f aca="false">G9/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="1" t="n">
@@ -4388,7 +4400,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B10" s="38" t="n">
         <v>10</v>
@@ -4397,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E10" s="2" t="n">
         <f aca="false">F9</f>
@@ -4416,10 +4428,10 @@
         <v>333.333333333333</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="1" t="n">
@@ -4428,7 +4440,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B11" s="38" t="n">
         <v>10</v>
@@ -4437,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E11" s="2" t="n">
         <f aca="false">F10</f>
@@ -4453,13 +4465,13 @@
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">G11/0.3048</f>
-        <v>333.333333333334</v>
+        <v>333.333333333333</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="1" t="n">
@@ -4468,7 +4480,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B12" s="38" t="n">
         <v>10</v>
@@ -4477,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E12" s="2" t="n">
         <f aca="false">F11</f>
@@ -4496,10 +4508,10 @@
         <v>333.333333333333</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="1" t="n">
@@ -4508,7 +4520,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B13" s="38" t="n">
         <v>10</v>
@@ -4517,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">F12</f>
@@ -4536,10 +4548,10 @@
         <v>333.333333333333</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="1" t="n">
@@ -4557,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E14" s="2" t="n">
         <f aca="false">F13</f>
@@ -4573,13 +4585,13 @@
       </c>
       <c r="H14" s="5" t="n">
         <f aca="false">G14/0.3048</f>
-        <v>333.333333333333</v>
+        <v>333.333333333334</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="1" t="n">
@@ -4597,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E15" s="2" t="n">
         <f aca="false">F14</f>
@@ -4616,10 +4628,10 @@
         <v>333.333333333333</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="1" t="n">
@@ -4637,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">F15</f>
@@ -4648,17 +4660,17 @@
       </c>
       <c r="G16" s="9" t="n">
         <f aca="false">F16-E16</f>
-        <v>104.112000000001</v>
+        <v>104.112</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">G16/0.3048</f>
-        <v>341.574803149608</v>
+        <v>341.574803149607</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="1" t="n">
@@ -4676,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>2.512</v>
@@ -4693,10 +4705,10 @@
         <v>569.255249343832</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K17" s="41" t="s">
         <v>105</v>
@@ -4710,13 +4722,13 @@
         <v>101</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>2.512</v>
@@ -4733,10 +4745,10 @@
         <v>569.255249343832</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K18" s="41"/>
       <c r="L18" s="1" t="n">
@@ -4745,7 +4757,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B19" s="38" t="n">
         <v>10</v>
@@ -4754,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E19" s="2" t="n">
         <f aca="false">F17</f>
@@ -4772,7 +4784,7 @@
         <v>90.2526246719161</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K19" s="41"/>
       <c r="L19" s="1" t="n">
@@ -4781,7 +4793,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B20" s="38" t="n">
         <v>10</v>
@@ -4790,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E20" s="2" t="n">
         <f aca="false">F19</f>
@@ -4814,7 +4826,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B21" s="38" t="n">
         <v>10</v>
@@ -4823,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E21" s="2" t="n">
         <f aca="false">F20</f>
@@ -4847,7 +4859,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B22" s="38" t="n">
         <v>10</v>
@@ -4856,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E22" s="2" t="n">
         <f aca="false">F21</f>
@@ -4880,7 +4892,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B23" s="38" t="n">
         <v>10</v>
@@ -4889,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E23" s="2" t="n">
         <f aca="false">F22</f>
@@ -4913,7 +4925,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B24" s="38" t="n">
         <v>10</v>
@@ -4922,7 +4934,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E24" s="2" t="n">
         <f aca="false">F23</f>
@@ -4946,7 +4958,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B25" s="38" t="n">
         <v>10</v>
@@ -4955,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E25" s="2" t="n">
         <f aca="false">F24</f>
@@ -4979,7 +4991,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B26" s="38" t="n">
         <v>10</v>
@@ -4988,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E26" s="2" t="n">
         <f aca="false">F25</f>
@@ -5012,7 +5024,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B27" s="38" t="n">
         <v>10</v>
@@ -5021,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E27" s="2" t="n">
         <f aca="false">F26</f>
@@ -5045,7 +5057,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B28" s="38" t="n">
         <v>10</v>
@@ -5054,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E28" s="2" t="n">
         <f aca="false">F27</f>
@@ -5078,7 +5090,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B29" s="38" t="n">
         <v>10</v>
@@ -5087,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E29" s="2" t="n">
         <f aca="false">F28</f>
@@ -5111,7 +5123,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B30" s="38" t="n">
         <v>10</v>
@@ -5120,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E30" s="2" t="n">
         <f aca="false">F29</f>
@@ -5138,7 +5150,7 @@
         <v>110.597116141732</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="1" t="n">
@@ -5147,7 +5159,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B31" s="38" t="n">
         <v>10</v>
@@ -5156,7 +5168,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E31" s="2" t="n">
         <f aca="false">F30</f>
@@ -5174,7 +5186,7 @@
         <v>119.648897637795</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K31" s="41"/>
       <c r="L31" s="1" t="n">
@@ -5183,7 +5195,7 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B32" s="38" t="n">
         <v>10</v>
@@ -5192,7 +5204,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E32" s="2" t="n">
         <f aca="false">F31</f>
@@ -5216,7 +5228,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B33" s="38" t="n">
         <v>10</v>
@@ -5225,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E33" s="2" t="n">
         <f aca="false">F32</f>
@@ -5249,7 +5261,7 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B34" s="38" t="n">
         <v>10</v>
@@ -5258,7 +5270,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E34" s="2" t="n">
         <f aca="false">F33</f>
@@ -5276,7 +5288,7 @@
         <v>154.361902887139</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K34" s="41"/>
       <c r="L34" s="1" t="n">
@@ -5285,7 +5297,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B35" s="38" t="n">
         <v>10</v>
@@ -5294,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E35" s="2" t="n">
         <f aca="false">F34</f>
@@ -5312,10 +5324,10 @@
         <v>52.2424770341206</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="1" t="n">
@@ -5324,7 +5336,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B36" s="38" t="n">
         <v>10</v>
@@ -5333,7 +5345,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E36" s="2" t="n">
         <f aca="false">F35</f>
@@ -5351,10 +5363,10 @@
         <v>101.919291338583</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K36" s="41"/>
       <c r="L36" s="1" t="n">
@@ -5363,7 +5375,7 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B37" s="38" t="n">
         <v>11</v>
@@ -5372,7 +5384,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>686.410331</v>
@@ -5389,10 +5401,10 @@
         <v>90.7672900262465</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K37" s="41"/>
       <c r="L37" s="1" t="n">
@@ -5427,7 +5439,7 @@
         <v>799.368562992126</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>151</v>
@@ -5439,7 +5451,7 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B39" s="38" t="n">
         <v>12</v>
@@ -5448,7 +5460,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>700.528</v>
@@ -5465,10 +5477,10 @@
         <v>192.040449475065</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="K39" s="41"/>
       <c r="L39" s="1" t="n">
@@ -5477,7 +5489,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B40" s="40" t="n">
         <v>13</v>
@@ -5486,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E40" s="9" t="n">
         <v>739.999999</v>
@@ -5503,10 +5515,10 @@
         <v>60.2390748031495</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K40" s="41"/>
       <c r="L40" s="1" t="n">
@@ -5580,6 +5592,7 @@
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K59" s="42"/>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K4:K16"/>
@@ -5614,7 +5627,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -5637,13 +5650,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>517.54</v>
@@ -5660,18 +5673,18 @@
         <v>8.02654855643056</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>519.986492</v>
@@ -5688,18 +5701,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>524.386492</v>
@@ -5716,18 +5729,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>528.786492</v>
@@ -5744,18 +5757,18 @@
         <v>14.435695538058</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>533.186492</v>
@@ -5772,18 +5785,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>537.586492</v>
@@ -5800,18 +5813,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>541.986492</v>
@@ -5828,18 +5841,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>546.386492</v>
@@ -5856,18 +5869,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>550.786492</v>
@@ -5884,18 +5897,18 @@
         <v>14.435695538058</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>555.186492</v>
@@ -5912,18 +5925,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>559.586492</v>
@@ -5940,7 +5953,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>26</v>
@@ -5948,13 +5961,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>563.986492</v>
@@ -5971,7 +5984,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>27</v>
@@ -5979,13 +5992,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>568.386492</v>
@@ -6002,7 +6015,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>28</v>
@@ -6010,13 +6023,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>572.786492</v>
@@ -6033,7 +6046,7 @@
         <v>14.435695538058</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>29</v>
@@ -6041,13 +6054,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>577.186492</v>
@@ -6064,7 +6077,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>30</v>
@@ -6072,13 +6085,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>581.586492</v>
@@ -6095,7 +6108,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>31</v>
@@ -6103,13 +6116,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>585.986492</v>
@@ -6126,7 +6139,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>32</v>
@@ -6134,13 +6147,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>590.386492</v>
@@ -6157,7 +6170,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>33</v>
@@ -6165,13 +6178,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>594.786492</v>
@@ -6188,7 +6201,7 @@
         <v>14.435695538058</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>34</v>
@@ -6196,13 +6209,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>599.186492</v>
@@ -6219,18 +6232,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>603.586492</v>
@@ -6247,7 +6260,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>36</v>
@@ -6255,13 +6268,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>607.986492</v>
@@ -6278,7 +6291,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>37</v>
@@ -6286,13 +6299,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>612.386492</v>
@@ -6309,7 +6322,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>38</v>
@@ -6317,13 +6330,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>616.786492</v>
@@ -6340,7 +6353,7 @@
         <v>14.435695538058</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>39</v>
@@ -6348,13 +6361,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>621.186492</v>
@@ -6371,7 +6384,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>40</v>
@@ -6379,13 +6392,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>625.586492</v>
@@ -6402,7 +6415,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>41</v>
@@ -6410,13 +6423,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>629.986492</v>
@@ -6433,7 +6446,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>42</v>
@@ -6441,13 +6454,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>634.386492</v>
@@ -6464,7 +6477,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>43</v>
@@ -6472,13 +6485,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>638.786492</v>
@@ -6495,7 +6508,7 @@
         <v>14.435695538058</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>44</v>
@@ -6503,13 +6516,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>643.186492</v>
@@ -6526,7 +6539,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>45</v>
@@ -6534,13 +6547,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>647.586492</v>
@@ -6557,7 +6570,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>46</v>
@@ -6565,13 +6578,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>651.986492</v>
@@ -6588,7 +6601,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>47</v>
@@ -6596,13 +6609,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>656.386492</v>
@@ -6619,18 +6632,18 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>660.786492</v>
@@ -6647,18 +6660,18 @@
         <v>14.435695538058</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>665.186492</v>
@@ -6675,7 +6688,7 @@
         <v>14.4356955380577</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -6704,7 +6717,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
@@ -6727,13 +6740,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>514.740001</v>
@@ -6750,7 +6763,7 @@
         <v>14.3295603674542</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>13</v>
@@ -6758,13 +6771,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>519.107651</v>
@@ -6781,7 +6794,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>14</v>
@@ -6789,13 +6802,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>523.120318</v>
@@ -6812,7 +6825,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>15</v>
@@ -6820,13 +6833,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>527.132985</v>
@@ -6843,7 +6856,7 @@
         <v>13.164914698163</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>16</v>
@@ -6851,13 +6864,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>531.145651</v>
@@ -6874,7 +6887,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>17</v>
@@ -6882,13 +6895,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>535.158318</v>
@@ -6905,7 +6918,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>18</v>
@@ -6913,13 +6926,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>539.170985</v>
@@ -6936,7 +6949,7 @@
         <v>13.164914698163</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>19</v>
@@ -6944,13 +6957,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>543.183651</v>
@@ -6967,7 +6980,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>20</v>
@@ -6975,13 +6988,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>547.196318</v>
@@ -6998,19 +7011,19 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>551.208985</v>
@@ -7027,7 +7040,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>22</v>
@@ -7035,13 +7048,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>555.221651</v>
@@ -7058,7 +7071,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>23</v>
@@ -7066,13 +7079,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>559.234318</v>
@@ -7089,7 +7102,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>24</v>
@@ -7097,13 +7110,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>563.246985</v>
@@ -7120,7 +7133,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>25</v>
@@ -7128,13 +7141,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>567.259651</v>
@@ -7151,7 +7164,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>26</v>
@@ -7159,13 +7172,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>571.272318</v>
@@ -7182,7 +7195,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>27</v>
@@ -7190,13 +7203,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>575.284985</v>
@@ -7213,19 +7226,19 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>579.297651</v>
@@ -7242,7 +7255,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>29</v>
@@ -7250,13 +7263,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>583.310318</v>
@@ -7273,7 +7286,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>30</v>
@@ -7281,13 +7294,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>587.322985</v>
@@ -7304,7 +7317,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>31</v>
@@ -7312,13 +7325,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>591.335651</v>
@@ -7335,7 +7348,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>32</v>
@@ -7343,13 +7356,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>595.348318</v>
@@ -7366,7 +7379,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>33</v>
@@ -7374,13 +7387,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>599.360985</v>
@@ -7397,7 +7410,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>34</v>
@@ -7405,13 +7418,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>603.373651</v>
@@ -7428,7 +7441,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>35</v>
@@ -7436,13 +7449,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>607.386318</v>
@@ -7459,7 +7472,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>36</v>
@@ -7467,13 +7480,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>611.398985</v>
@@ -7490,7 +7503,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>37</v>
@@ -7498,13 +7511,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>615.411651</v>
@@ -7521,7 +7534,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>38</v>
@@ -7529,13 +7542,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>619.424318</v>
@@ -7552,7 +7565,7 @@
         <v>13.1649179790029</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>39</v>
@@ -7560,13 +7573,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>623.436985</v>
@@ -7583,7 +7596,7 @@
         <v>13.1649146981626</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>40</v>
@@ -7591,13 +7604,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>627.449651</v>
@@ -7614,7 +7627,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>41</v>
@@ -7622,13 +7635,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>631.462318</v>
@@ -7645,7 +7658,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>42</v>
@@ -7653,13 +7666,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>635.474985</v>
@@ -7676,7 +7689,7 @@
         <v>13.164914698163</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>43</v>
@@ -7684,13 +7697,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>639.487651</v>
@@ -7707,7 +7720,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>44</v>
@@ -7715,13 +7728,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>643.500318</v>
@@ -7738,7 +7751,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I34" s="1" t="n">
         <v>45</v>
@@ -7746,13 +7759,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>647.512985</v>
@@ -7769,7 +7782,7 @@
         <v>13.164914698163</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>46</v>
@@ -7777,13 +7790,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>651.525651</v>
@@ -7800,7 +7813,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>47</v>
@@ -7808,13 +7821,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>655.538318</v>
@@ -7831,18 +7844,18 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>659.550985</v>
@@ -7859,18 +7872,18 @@
         <v>13.164914698163</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>663.563651</v>
@@ -7887,7 +7900,7 @@
         <v>13.1649179790025</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/python/scripts/oracle_upload/sectors.xlsx
+++ b/python/scripts/oracle_upload/sectors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AD_ACCEL\20240901s\RDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AD_ACCEL\preRelease\RDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F009E48A-F2A8-436E-B63D-9BC608CC10BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589ED238-D39A-4F94-AB36-994F3D8894CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24165" yWindow="3735" windowWidth="17460" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9735" yWindow="405" windowWidth="15480" windowHeight="17175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scS" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="388">
   <si>
     <t>S00</t>
   </si>
@@ -1086,9 +1086,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>CLTH/BSYH1/BSYH2</t>
-  </si>
-  <si>
     <t>BEGL1</t>
   </si>
   <si>
@@ -1134,9 +1131,6 @@
     <t>BEGCLTH_1</t>
   </si>
   <si>
-    <t>ENDBSYH_2</t>
-  </si>
-  <si>
     <t>ENDUNDH</t>
   </si>
   <si>
@@ -1161,12 +1155,6 @@
     <t>ENDSFTH_2</t>
   </si>
   <si>
-    <t>BEGBSYA_1</t>
-  </si>
-  <si>
-    <t>ENDBSYA_2</t>
-  </si>
-  <si>
     <t>BEGL3</t>
   </si>
   <si>
@@ -1218,13 +1206,43 @@
     <t>HXRSS chicane</t>
   </si>
   <si>
-    <t>SXR extension</t>
-  </si>
-  <si>
     <t>SXRSS chicane</t>
   </si>
   <si>
-    <t>ENDBSY_2</t>
+    <t>ENDESA</t>
+  </si>
+  <si>
+    <t>BSYA</t>
+  </si>
+  <si>
+    <t>ESA</t>
+  </si>
+  <si>
+    <t>BRAM1B</t>
+  </si>
+  <si>
+    <t>ENDBSYA</t>
+  </si>
+  <si>
+    <t>CLTH/BSYH</t>
+  </si>
+  <si>
+    <t>ENDBSYH</t>
+  </si>
+  <si>
+    <t>partial cell</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>CBXFEL chicane #1</t>
+  </si>
+  <si>
+    <t>contains</t>
+  </si>
+  <si>
+    <t>Delta-II</t>
   </si>
 </sst>
 </file>
@@ -1410,9 +1428,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1421,6 +1436,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1705,7 +1723,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1804,7 +1822,7 @@
       <c r="I4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="K4" s="24" t="s">
         <v>28</v>
       </c>
       <c r="L4" s="1">
@@ -1840,7 +1858,7 @@
         <f t="shared" ref="H5:H34" si="4">G5/0.3048</f>
         <v>333.33333333333331</v>
       </c>
-      <c r="K5" s="25"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="1">
         <v>2</v>
       </c>
@@ -1874,7 +1892,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333331</v>
       </c>
-      <c r="K6" s="25"/>
+      <c r="K6" s="24"/>
       <c r="L6" s="1">
         <v>3</v>
       </c>
@@ -1908,7 +1926,7 @@
         <f t="shared" si="4"/>
         <v>333.3333333333332</v>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="24"/>
       <c r="L7" s="1">
         <v>4</v>
       </c>
@@ -1942,7 +1960,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K8" s="25"/>
+      <c r="K8" s="24"/>
       <c r="L8" s="1">
         <v>5</v>
       </c>
@@ -1976,7 +1994,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K9" s="25"/>
+      <c r="K9" s="24"/>
       <c r="L9" s="1">
         <v>6</v>
       </c>
@@ -2010,7 +2028,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="24"/>
       <c r="L10" s="1">
         <v>7</v>
       </c>
@@ -2044,7 +2062,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K11" s="25"/>
+      <c r="K11" s="24"/>
       <c r="L11" s="1">
         <v>8</v>
       </c>
@@ -2078,7 +2096,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="24"/>
       <c r="L12" s="1">
         <v>9</v>
       </c>
@@ -2118,7 +2136,7 @@
       <c r="J13" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="24"/>
       <c r="L13" s="1">
         <v>10</v>
       </c>
@@ -2158,7 +2176,7 @@
       <c r="J14" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="K14" s="25"/>
+      <c r="K14" s="24"/>
       <c r="L14" s="1">
         <v>11</v>
       </c>
@@ -2198,7 +2216,7 @@
       <c r="J15" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="K15" s="25"/>
+      <c r="K15" s="24"/>
       <c r="L15" s="1">
         <v>12</v>
       </c>
@@ -2238,7 +2256,7 @@
       <c r="J16" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="K16" s="25"/>
+      <c r="K16" s="24"/>
       <c r="L16" s="1">
         <v>13</v>
       </c>
@@ -2278,7 +2296,7 @@
       <c r="J17" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="K17" s="25"/>
+      <c r="K17" s="24"/>
       <c r="L17" s="1">
         <v>14</v>
       </c>
@@ -2318,7 +2336,7 @@
       <c r="J18" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="K18" s="25"/>
+      <c r="K18" s="24"/>
       <c r="L18" s="1">
         <v>15</v>
       </c>
@@ -2358,7 +2376,7 @@
       <c r="J19" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K19" s="25"/>
+      <c r="K19" s="24"/>
       <c r="L19" s="1">
         <v>16</v>
       </c>
@@ -2398,7 +2416,7 @@
       <c r="J20" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="K20" s="25"/>
+      <c r="K20" s="24"/>
       <c r="L20" s="1">
         <v>17</v>
       </c>
@@ -2438,7 +2456,7 @@
       <c r="J21" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="K21" s="25"/>
+      <c r="K21" s="24"/>
       <c r="L21" s="1">
         <v>18</v>
       </c>
@@ -2478,7 +2496,7 @@
       <c r="J22" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K22" s="25"/>
+      <c r="K22" s="24"/>
       <c r="L22" s="1">
         <v>19</v>
       </c>
@@ -2518,7 +2536,7 @@
       <c r="J23" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K23" s="25"/>
+      <c r="K23" s="24"/>
       <c r="L23" s="1">
         <v>20</v>
       </c>
@@ -2558,7 +2576,7 @@
       <c r="J24" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="K24" s="25"/>
+      <c r="K24" s="24"/>
       <c r="L24" s="1">
         <v>21</v>
       </c>
@@ -2598,7 +2616,7 @@
       <c r="J25" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K25" s="25"/>
+      <c r="K25" s="24"/>
       <c r="L25" s="1">
         <v>22</v>
       </c>
@@ -2638,7 +2656,7 @@
       <c r="J26" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="K26" s="25"/>
+      <c r="K26" s="24"/>
       <c r="L26" s="1">
         <v>23</v>
       </c>
@@ -2678,7 +2696,7 @@
       <c r="J27" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="K27" s="25"/>
+      <c r="K27" s="24"/>
       <c r="L27" s="1">
         <v>24</v>
       </c>
@@ -2718,7 +2736,7 @@
       <c r="J28" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="K28" s="25"/>
+      <c r="K28" s="24"/>
       <c r="L28" s="1">
         <v>25</v>
       </c>
@@ -2758,7 +2776,7 @@
       <c r="J29" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="K29" s="25"/>
+      <c r="K29" s="24"/>
       <c r="L29" s="1">
         <v>26</v>
       </c>
@@ -2798,7 +2816,7 @@
       <c r="J30" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="K30" s="25"/>
+      <c r="K30" s="24"/>
       <c r="L30" s="1">
         <v>27</v>
       </c>
@@ -2838,7 +2856,7 @@
       <c r="J31" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="K31" s="25"/>
+      <c r="K31" s="24"/>
       <c r="L31" s="1">
         <v>28</v>
       </c>
@@ -2872,7 +2890,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K32" s="25"/>
+      <c r="K32" s="24"/>
       <c r="L32" s="1">
         <v>29</v>
       </c>
@@ -2906,7 +2924,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K33" s="25"/>
+      <c r="K33" s="24"/>
       <c r="L33" s="1">
         <v>30</v>
       </c>
@@ -2943,7 +2961,7 @@
       <c r="J34" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="K34" s="26"/>
+      <c r="K34" s="25"/>
       <c r="L34" s="1">
         <v>31</v>
       </c>
@@ -2981,7 +2999,7 @@
       <c r="J35" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="K35" s="27" t="s">
+      <c r="K35" s="26" t="s">
         <v>29</v>
       </c>
       <c r="L35" s="1">
@@ -3019,7 +3037,7 @@
       <c r="I36" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K36" s="25"/>
+      <c r="K36" s="24"/>
       <c r="L36" s="1">
         <v>33</v>
       </c>
@@ -3052,7 +3070,7 @@
         <f t="shared" si="6"/>
         <v>85.171587926509247</v>
       </c>
-      <c r="K37" s="25"/>
+      <c r="K37" s="24"/>
       <c r="L37" s="1">
         <v>34</v>
       </c>
@@ -3085,7 +3103,7 @@
         <f t="shared" si="6"/>
         <v>90.504265091863431</v>
       </c>
-      <c r="K38" s="25"/>
+      <c r="K38" s="24"/>
       <c r="L38" s="1">
         <v>35</v>
       </c>
@@ -3118,7 +3136,7 @@
         <f t="shared" si="6"/>
         <v>100.17946194225736</v>
       </c>
-      <c r="K39" s="25"/>
+      <c r="K39" s="24"/>
       <c r="L39" s="1">
         <v>36</v>
       </c>
@@ -3151,7 +3169,7 @@
         <f t="shared" si="6"/>
         <v>89.236876640419837</v>
       </c>
-      <c r="K40" s="25"/>
+      <c r="K40" s="24"/>
       <c r="L40" s="1">
         <v>37</v>
       </c>
@@ -3184,7 +3202,7 @@
         <f t="shared" si="6"/>
         <v>90.484908136482858</v>
       </c>
-      <c r="K41" s="25"/>
+      <c r="K41" s="24"/>
       <c r="L41" s="1">
         <v>38</v>
       </c>
@@ -3217,7 +3235,7 @@
         <f t="shared" si="6"/>
         <v>75.762795275590648</v>
       </c>
-      <c r="K42" s="25"/>
+      <c r="K42" s="24"/>
       <c r="L42" s="1">
         <v>39</v>
       </c>
@@ -3250,7 +3268,7 @@
         <f t="shared" si="6"/>
         <v>95.227034120734857</v>
       </c>
-      <c r="K43" s="25"/>
+      <c r="K43" s="24"/>
       <c r="L43" s="1">
         <v>40</v>
       </c>
@@ -3283,7 +3301,7 @@
         <f t="shared" si="6"/>
         <v>99.886811023622172</v>
       </c>
-      <c r="K44" s="25"/>
+      <c r="K44" s="24"/>
       <c r="L44" s="1">
         <v>41</v>
       </c>
@@ -3316,7 +3334,7 @@
         <f t="shared" si="6"/>
         <v>88.113845144356958</v>
       </c>
-      <c r="K45" s="25"/>
+      <c r="K45" s="24"/>
       <c r="L45" s="1">
         <v>42</v>
       </c>
@@ -3349,7 +3367,7 @@
         <f t="shared" si="6"/>
         <v>95.997703412073378</v>
       </c>
-      <c r="K46" s="25"/>
+      <c r="K46" s="24"/>
       <c r="L46" s="1">
         <v>43</v>
       </c>
@@ -3385,7 +3403,7 @@
       <c r="J47" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="K47" s="25"/>
+      <c r="K47" s="24"/>
       <c r="L47" s="1">
         <v>44</v>
       </c>
@@ -3415,13 +3433,13 @@
         <v>41.929491999999982</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" ref="H48:H58" si="9">G48/0.3048</f>
+        <f t="shared" ref="H48:H57" si="9">G48/0.3048</f>
         <v>137.56395013123353</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="K48" s="25"/>
+        <v>339</v>
+      </c>
+      <c r="K48" s="24"/>
       <c r="L48" s="1">
         <v>45</v>
       </c>
@@ -3454,7 +3472,7 @@
         <f t="shared" si="9"/>
         <v>115.48556430446172</v>
       </c>
-      <c r="K49" s="25"/>
+      <c r="K49" s="24"/>
       <c r="L49" s="1">
         <v>46</v>
       </c>
@@ -3487,7 +3505,7 @@
         <f t="shared" si="9"/>
         <v>115.48556430446209</v>
       </c>
-      <c r="K50" s="25"/>
+      <c r="K50" s="24"/>
       <c r="L50" s="1">
         <v>47</v>
       </c>
@@ -3521,9 +3539,9 @@
         <v>132.8740157480315</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="K51" s="25"/>
+        <v>340</v>
+      </c>
+      <c r="K51" s="24"/>
       <c r="L51" s="1">
         <v>48</v>
       </c>
@@ -3557,12 +3575,12 @@
         <v>52.242480314960531</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="K52" s="25"/>
+      <c r="K52" s="24"/>
       <c r="L52" s="1">
         <v>49</v>
       </c>
@@ -3596,12 +3614,12 @@
         <v>101.91929133858285</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="J53" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="K53" s="25"/>
+      <c r="K53" s="24"/>
       <c r="L53" s="1">
         <v>50</v>
       </c>
@@ -3634,12 +3652,12 @@
         <v>90.767290026246471</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J54" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="J54" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="K54" s="25"/>
+      <c r="K54" s="24"/>
       <c r="L54" s="1">
         <v>51</v>
       </c>
@@ -3655,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E55" s="3">
         <v>700.52800000000002</v>
@@ -3672,12 +3690,12 @@
         <v>130.42318241469803</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="J55" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="K55" s="25"/>
+        <v>366</v>
+      </c>
+      <c r="K55" s="24"/>
       <c r="L55" s="1">
         <v>52</v>
       </c>
@@ -3693,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E56" s="3">
         <v>733.77200000000005</v>
@@ -3710,12 +3728,12 @@
         <v>73.253152887138924</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J56" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="K56" s="25"/>
+        <v>372</v>
+      </c>
+      <c r="K56" s="24"/>
       <c r="L56" s="1">
         <v>53</v>
       </c>
@@ -3731,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E57" s="1">
         <v>733.77200000000005</v>
@@ -3748,69 +3766,109 @@
         <v>80.439632545931474</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J57" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="K57" s="25"/>
+        <v>369</v>
+      </c>
+      <c r="K57" s="24"/>
       <c r="L57" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="12" t="s">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B58" s="12">
+      <c r="B58" s="1">
         <v>9</v>
       </c>
-      <c r="C58" s="12">
-        <v>1</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="E58" s="12">
-        <v>176.02099999999999</v>
-      </c>
-      <c r="F58" s="13">
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E58" s="1">
+        <v>131.417</v>
+      </c>
+      <c r="F58" s="3">
         <v>313.05599999999998</v>
       </c>
-      <c r="G58" s="13">
+      <c r="G58" s="3">
         <f t="shared" si="8"/>
-        <v>137.035</v>
-      </c>
-      <c r="H58" s="14">
-        <f t="shared" si="9"/>
-        <v>449.58989501312334</v>
-      </c>
-      <c r="I58" s="12"/>
-      <c r="J58" s="18" t="s">
-        <v>381</v>
+        <v>181.63899999999998</v>
+      </c>
+      <c r="H58" s="2">
+        <f>G58/0.3048</f>
+        <v>595.92847769028867</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J58" s="17" t="s">
+        <v>380</v>
       </c>
       <c r="K58" s="24"/>
       <c r="L58" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B59" s="12">
+        <v>9</v>
+      </c>
+      <c r="C59" s="12">
+        <v>1</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="E59" s="12">
+        <v>313.05599999999998</v>
+      </c>
+      <c r="F59" s="13">
+        <v>455.10700000000003</v>
+      </c>
+      <c r="G59" s="13">
+        <f t="shared" ref="G59" si="10">F59-E59</f>
+        <v>142.05100000000004</v>
+      </c>
+      <c r="H59" s="14">
+        <f t="shared" ref="H59" si="11">G59/0.3048</f>
+        <v>466.04658792650929</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="K59" s="25"/>
+      <c r="L59" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>1</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>338</v>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>1</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K4:K34"/>
-    <mergeCell ref="K35:K57"/>
+    <mergeCell ref="K35:K59"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="61" orientation="portrait" r:id="rId1"/>
@@ -3822,7 +3880,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -3926,12 +3984,12 @@
         <v>56.179947506561689</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="K4" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="K4" s="24" t="s">
         <v>28</v>
       </c>
       <c r="L4" s="1">
@@ -3968,12 +4026,12 @@
         <v>323.37555774278189</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="K5" s="25"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="1">
         <v>2</v>
       </c>
@@ -4013,7 +4071,7 @@
       <c r="J6" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K6" s="25"/>
+      <c r="K6" s="24"/>
       <c r="L6" s="1">
         <v>3</v>
       </c>
@@ -4053,7 +4111,7 @@
       <c r="J7" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="24"/>
       <c r="L7" s="1">
         <v>4</v>
       </c>
@@ -4091,9 +4149,9 @@
         <v>163</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="K8" s="25"/>
+        <v>336</v>
+      </c>
+      <c r="K8" s="24"/>
       <c r="L8" s="1">
         <v>5</v>
       </c>
@@ -4128,12 +4186,12 @@
         <v>333.33333333333451</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K9" s="25"/>
+      <c r="K9" s="24"/>
       <c r="L9" s="1">
         <v>6</v>
       </c>
@@ -4173,7 +4231,7 @@
       <c r="J10" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="24"/>
       <c r="L10" s="1">
         <v>7</v>
       </c>
@@ -4213,7 +4271,7 @@
       <c r="J11" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K11" s="25"/>
+      <c r="K11" s="24"/>
       <c r="L11" s="1">
         <v>8</v>
       </c>
@@ -4253,7 +4311,7 @@
       <c r="J12" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="24"/>
       <c r="L12" s="1">
         <v>9</v>
       </c>
@@ -4293,7 +4351,7 @@
       <c r="J13" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="24"/>
       <c r="L13" s="1">
         <v>10</v>
       </c>
@@ -4330,9 +4388,9 @@
         <v>331</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="K14" s="26"/>
+        <v>348</v>
+      </c>
+      <c r="K14" s="25"/>
       <c r="L14" s="1">
         <v>11</v>
       </c>
@@ -4348,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="E15" s="3">
         <v>2.512</v>
@@ -4365,14 +4423,12 @@
         <v>569.25524934383191</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="K15" s="27" t="s">
-        <v>29</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="K15" s="26"/>
       <c r="L15" s="1">
         <v>12</v>
       </c>
@@ -4408,7 +4464,7 @@
       <c r="I16" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K16" s="25"/>
+      <c r="K16" s="24"/>
       <c r="L16" s="1">
         <v>13</v>
       </c>
@@ -4441,7 +4497,7 @@
         <f t="shared" si="4"/>
         <v>91.041010498687683</v>
       </c>
-      <c r="K17" s="25"/>
+      <c r="K17" s="24"/>
       <c r="L17" s="1">
         <v>14</v>
       </c>
@@ -4474,7 +4530,7 @@
         <f t="shared" si="4"/>
         <v>95.802821522309742</v>
       </c>
-      <c r="K18" s="25"/>
+      <c r="K18" s="24"/>
       <c r="L18" s="1">
         <v>15</v>
       </c>
@@ -4507,7 +4563,7 @@
         <f t="shared" si="4"/>
         <v>86.220472440944789</v>
       </c>
-      <c r="K19" s="25"/>
+      <c r="K19" s="24"/>
       <c r="L19" s="1">
         <v>16</v>
       </c>
@@ -4540,7 +4596,7 @@
         <f t="shared" si="4"/>
         <v>91.108923884514368</v>
       </c>
-      <c r="K20" s="25"/>
+      <c r="K20" s="24"/>
       <c r="L20" s="1">
         <v>17</v>
       </c>
@@ -4573,7 +4629,7 @@
         <f t="shared" si="4"/>
         <v>91.010498687664068</v>
       </c>
-      <c r="K21" s="25"/>
+      <c r="K21" s="24"/>
       <c r="L21" s="1">
         <v>18</v>
       </c>
@@ -4606,7 +4662,7 @@
         <f t="shared" si="4"/>
         <v>95.636482939632657</v>
       </c>
-      <c r="K22" s="25"/>
+      <c r="K22" s="24"/>
       <c r="L22" s="1">
         <v>19</v>
       </c>
@@ -4639,7 +4695,7 @@
         <f t="shared" si="4"/>
         <v>86.417322834645589</v>
       </c>
-      <c r="K23" s="25"/>
+      <c r="K23" s="24"/>
       <c r="L23" s="1">
         <v>20</v>
       </c>
@@ -4672,7 +4728,7 @@
         <f t="shared" si="4"/>
         <v>91.108923884514368</v>
       </c>
-      <c r="K24" s="25"/>
+      <c r="K24" s="24"/>
       <c r="L24" s="1">
         <v>21</v>
       </c>
@@ -4705,7 +4761,7 @@
         <f t="shared" si="4"/>
         <v>91.043307086614163</v>
       </c>
-      <c r="K25" s="25"/>
+      <c r="K25" s="24"/>
       <c r="L25" s="1">
         <v>22</v>
       </c>
@@ -4738,7 +4794,7 @@
         <f t="shared" si="4"/>
         <v>91.043307086614163</v>
       </c>
-      <c r="K26" s="25"/>
+      <c r="K26" s="24"/>
       <c r="L26" s="1">
         <v>23</v>
       </c>
@@ -4774,7 +4830,7 @@
       <c r="J27" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="K27" s="25"/>
+      <c r="K27" s="24"/>
       <c r="L27" s="1">
         <v>24</v>
       </c>
@@ -4800,7 +4856,7 @@
         <v>551.20898499999998</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" ref="G28:G37" si="6">F28-E28</f>
+        <f t="shared" ref="G28:G36" si="6">F28-E28</f>
         <v>36.468983999999978</v>
       </c>
       <c r="H28" s="3">
@@ -4808,9 +4864,9 @@
         <v>119.6488976377952</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="K28" s="25"/>
+        <v>351</v>
+      </c>
+      <c r="K28" s="24"/>
       <c r="L28" s="1">
         <v>25</v>
       </c>
@@ -4843,7 +4899,7 @@
         <f>G29/0.3048</f>
         <v>118.48425196850404</v>
       </c>
-      <c r="K29" s="25"/>
+      <c r="K29" s="24"/>
       <c r="L29" s="1">
         <v>26</v>
       </c>
@@ -4876,7 +4932,7 @@
         <f>G30/0.3048</f>
         <v>118.48425196850404</v>
       </c>
-      <c r="K30" s="25"/>
+      <c r="K30" s="24"/>
       <c r="L30" s="1">
         <v>27</v>
       </c>
@@ -4910,9 +4966,9 @@
         <v>154.36190288713891</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="K31" s="25"/>
+        <v>350</v>
+      </c>
+      <c r="K31" s="24"/>
       <c r="L31" s="1">
         <v>28</v>
       </c>
@@ -4946,12 +5002,12 @@
         <v>52.24247703412064</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="K32" s="25"/>
+        <v>353</v>
+      </c>
+      <c r="K32" s="24"/>
       <c r="L32" s="1">
         <v>29</v>
       </c>
@@ -4985,12 +5041,12 @@
         <v>101.91929133858285</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="K33" s="25"/>
+        <v>355</v>
+      </c>
+      <c r="K33" s="24"/>
       <c r="L33" s="1">
         <v>30</v>
       </c>
@@ -5023,147 +5079,112 @@
         <v>90.767290026246471</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="K34" s="25"/>
+        <v>357</v>
+      </c>
+      <c r="K34" s="24"/>
       <c r="L34" s="1">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>328</v>
+        <v>112</v>
       </c>
       <c r="B35" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>328</v>
+        <v>111</v>
       </c>
       <c r="E35" s="3">
-        <v>69.408164999999997</v>
+        <v>700.52800000000002</v>
       </c>
       <c r="F35" s="3">
-        <v>313.05570299999999</v>
+        <v>759.06192899999996</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" ref="G35:G36" si="9">F35-E35</f>
-        <v>243.647538</v>
+        <f t="shared" ref="G35" si="9">F35-E35</f>
+        <v>58.533928999999944</v>
       </c>
       <c r="H35" s="2">
-        <f t="shared" ref="H35:H36" si="10">G35/0.3048</f>
-        <v>799.36856299212593</v>
+        <f t="shared" ref="H35" si="10">G35/0.3048</f>
+        <v>192.04044947506543</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J35" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="K35" s="25"/>
+      <c r="K35" s="24"/>
       <c r="L35" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="1">
-        <v>12</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E36" s="3">
-        <v>700.52800000000002</v>
-      </c>
-      <c r="F36" s="3">
-        <v>759.06192899999996</v>
-      </c>
-      <c r="G36" s="3">
-        <f t="shared" si="9"/>
-        <v>58.533928999999944</v>
-      </c>
-      <c r="H36" s="2">
-        <f t="shared" si="10"/>
-        <v>192.04044947506543</v>
-      </c>
-      <c r="I36" s="1" t="s">
+      <c r="B36" s="12">
+        <v>13</v>
+      </c>
+      <c r="C36" s="12">
+        <v>1</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="E36" s="13">
+        <v>739.999999</v>
+      </c>
+      <c r="F36" s="13">
+        <v>758.36086899999998</v>
+      </c>
+      <c r="G36" s="13">
+        <f t="shared" si="6"/>
+        <v>18.360869999999977</v>
+      </c>
+      <c r="H36" s="14">
+        <f t="shared" ref="H36" si="11">G36/0.3048</f>
+        <v>60.239074803149528</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="J36" s="18" t="s">
         <v>363</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>364</v>
       </c>
       <c r="K36" s="25"/>
       <c r="L36" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="12">
-        <v>13</v>
-      </c>
-      <c r="C37" s="12">
-        <v>1</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="E37" s="13">
-        <v>739.999999</v>
-      </c>
-      <c r="F37" s="13">
-        <v>758.36086899999998</v>
-      </c>
-      <c r="G37" s="13">
-        <f t="shared" si="6"/>
-        <v>18.360869999999977</v>
-      </c>
-      <c r="H37" s="14">
-        <f t="shared" ref="H37" si="11">G37/0.3048</f>
-        <v>60.239074803149528</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="J37" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="K37" s="26"/>
-      <c r="L37" s="1">
-        <v>34</v>
-      </c>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K37" s="11"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B38" s="1"/>
       <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B39" s="1"/>
+      <c r="A39" s="1">
+        <v>1</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>337</v>
+      </c>
       <c r="K39" s="11"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>1</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>338</v>
-      </c>
       <c r="K40" s="11"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -5210,14 +5231,11 @@
     </row>
     <row r="55" spans="11:11" x14ac:dyDescent="0.25">
       <c r="K55" s="11"/>
-    </row>
-    <row r="56" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K56" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K4:K14"/>
-    <mergeCell ref="K15:K37"/>
+    <mergeCell ref="K15:K36"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="60" orientation="portrait" r:id="rId1"/>
@@ -5235,7 +5253,7 @@
     <col min="4" max="5" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="3"/>
     <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5260,6 +5278,12 @@
       <c r="G1" s="14" t="s">
         <v>26</v>
       </c>
+      <c r="H1" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -5285,8 +5309,8 @@
         <f>F2/0.3048</f>
         <v>8.0265485564305603</v>
       </c>
-      <c r="H2" t="s">
-        <v>379</v>
+      <c r="I2" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -5313,8 +5337,8 @@
         <f t="shared" ref="G3:G36" si="1">F3/0.3048</f>
         <v>14.435695538057667</v>
       </c>
-      <c r="H3" t="s">
-        <v>379</v>
+      <c r="H3" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5341,8 +5365,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H4" t="s">
-        <v>379</v>
+      <c r="H4" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5369,8 +5393,8 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H5" t="s">
-        <v>379</v>
+      <c r="H5" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -5397,8 +5421,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H6" t="s">
-        <v>379</v>
+      <c r="H6" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5425,8 +5449,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H7" t="s">
-        <v>379</v>
+      <c r="H7" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -5453,8 +5477,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H8" t="s">
-        <v>379</v>
+      <c r="H8" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5481,8 +5505,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H9" t="s">
-        <v>379</v>
+      <c r="H9" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -5509,8 +5533,8 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H10" t="s">
-        <v>379</v>
+      <c r="H10" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -5537,8 +5561,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H11" t="s">
-        <v>379</v>
+      <c r="H11" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -5565,11 +5589,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I12" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -5596,11 +5617,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I13" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -5627,11 +5645,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I14" s="1">
-        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -5658,11 +5673,8 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I15" s="1">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -5689,14 +5701,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I16" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>303</v>
       </c>
@@ -5720,14 +5729,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I17" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>304</v>
       </c>
@@ -5751,14 +5757,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I18" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>311</v>
       </c>
@@ -5782,14 +5785,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I19" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>305</v>
       </c>
@@ -5813,14 +5813,11 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I20" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>306</v>
       </c>
@@ -5844,11 +5841,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H21" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H21" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>307</v>
       </c>
@@ -5872,14 +5869,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I22" s="1">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>308</v>
       </c>
@@ -5903,14 +5897,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I23" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>309</v>
       </c>
@@ -5934,14 +5925,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I24" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>310</v>
       </c>
@@ -5965,14 +5953,11 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I25" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>312</v>
       </c>
@@ -5996,14 +5981,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I26" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>313</v>
       </c>
@@ -6027,14 +6009,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I27" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>314</v>
       </c>
@@ -6058,14 +6037,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I28" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>315</v>
       </c>
@@ -6089,14 +6065,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I29" s="1">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>321</v>
       </c>
@@ -6120,14 +6093,11 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I30" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>316</v>
       </c>
@@ -6151,14 +6121,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I31" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>317</v>
       </c>
@@ -6182,11 +6149,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I32" s="1">
-        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -6213,11 +6177,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I33" s="1">
-        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -6244,8 +6205,11 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>210</v>
+      </c>
+      <c r="I34" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -6272,7 +6236,7 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="1" t="s">
         <v>210</v>
       </c>
     </row>
@@ -6300,7 +6264,7 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="1" t="s">
         <v>210</v>
       </c>
     </row>
@@ -6317,7 +6281,7 @@
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6342,6 +6306,12 @@
       <c r="G1" s="14" t="s">
         <v>26</v>
       </c>
+      <c r="H1" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6367,11 +6337,8 @@
         <f t="shared" ref="G2:G4" si="1">F2/0.3048</f>
         <v>14.329560367454153</v>
       </c>
-      <c r="H2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I2" s="1">
-        <v>13</v>
+      <c r="H2" s="1" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -6398,11 +6365,8 @@
         <f t="shared" si="1"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I3" s="1">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -6429,11 +6393,8 @@
         <f t="shared" si="1"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I4" s="1">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -6460,11 +6421,8 @@
         <f>F5/0.3048</f>
         <v>13.164914698162995</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I5" s="1">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -6491,11 +6449,8 @@
         <f t="shared" ref="G6:G39" si="3">F6/0.3048</f>
         <v>13.164917979002508</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I6" s="1">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -6522,11 +6477,8 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I7" s="1">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -6553,11 +6505,8 @@
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I8" s="1">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -6584,11 +6533,8 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I9" s="1">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -6615,10 +6561,9 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H10" t="s">
-        <v>377</v>
-      </c>
-      <c r="I10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -6644,11 +6589,8 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I11" s="1">
-        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -6675,11 +6617,8 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I12" s="1">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -6706,11 +6645,8 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I13" s="1">
-        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -6737,11 +6673,8 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I14" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -6768,11 +6701,8 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="I15" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -6799,14 +6729,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I16" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>265</v>
       </c>
@@ -6830,12 +6757,11 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H17" t="s">
-        <v>378</v>
-      </c>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H17" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>266</v>
       </c>
@@ -6859,14 +6785,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I18" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>267</v>
       </c>
@@ -6890,14 +6813,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I19" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>268</v>
       </c>
@@ -6921,14 +6841,11 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I20" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>269</v>
       </c>
@@ -6952,14 +6869,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I21" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>270</v>
       </c>
@@ -6983,14 +6897,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I22" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>271</v>
       </c>
@@ -7014,14 +6925,11 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I23" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>272</v>
       </c>
@@ -7045,14 +6953,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I24" s="1">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>273</v>
       </c>
@@ -7076,14 +6981,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I25" s="1">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>274</v>
       </c>
@@ -7107,14 +7009,11 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I26" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>275</v>
       </c>
@@ -7138,14 +7037,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I27" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>276</v>
       </c>
@@ -7169,14 +7065,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I28" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>277</v>
       </c>
@@ -7200,14 +7093,11 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I29" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>278</v>
       </c>
@@ -7231,14 +7121,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I30" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>279</v>
       </c>
@@ -7262,14 +7149,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I31" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>280</v>
       </c>
@@ -7293,14 +7177,11 @@
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I32" s="1">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>281</v>
       </c>
@@ -7324,14 +7205,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I33" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>282</v>
       </c>
@@ -7355,14 +7233,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I34" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>283</v>
       </c>
@@ -7386,14 +7261,11 @@
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I35" s="1">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>284</v>
       </c>
@@ -7417,14 +7289,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I36" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>285</v>
       </c>
@@ -7448,11 +7317,11 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>286</v>
       </c>
@@ -7476,11 +7345,11 @@
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>287</v>
       </c>
@@ -7504,7 +7373,7 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="1" t="s">
         <v>210</v>
       </c>
     </row>

--- a/python/scripts/oracle_upload/sectors.xlsx
+++ b/python/scripts/oracle_upload/sectors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AD_ACCEL\20240901s\RDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AD_ACCEL\preRelease\RDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F009E48A-F2A8-436E-B63D-9BC608CC10BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F8A872-AE4A-40F9-B9C8-F96991968D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24165" yWindow="3735" windowWidth="17460" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="225" windowWidth="23190" windowHeight="20670" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scS" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="408">
   <si>
     <t>S00</t>
   </si>
@@ -288,9 +288,6 @@
     <t>DMPH</t>
   </si>
   <si>
-    <t>GUN1/GUN2/L0/HTR/EMIT/BX0</t>
-  </si>
-  <si>
     <t>L2/BC2</t>
   </si>
   <si>
@@ -1086,9 +1083,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>CLTH/BSYH1/BSYH2</t>
-  </si>
-  <si>
     <t>BEGL1</t>
   </si>
   <si>
@@ -1134,9 +1128,6 @@
     <t>BEGCLTH_1</t>
   </si>
   <si>
-    <t>ENDBSYH_2</t>
-  </si>
-  <si>
     <t>ENDUNDH</t>
   </si>
   <si>
@@ -1161,12 +1152,6 @@
     <t>ENDSFTH_2</t>
   </si>
   <si>
-    <t>BEGBSYA_1</t>
-  </si>
-  <si>
-    <t>ENDBSYA_2</t>
-  </si>
-  <si>
     <t>BEGL3</t>
   </si>
   <si>
@@ -1218,13 +1203,106 @@
     <t>HXRSS chicane</t>
   </si>
   <si>
-    <t>SXR extension</t>
-  </si>
-  <si>
     <t>SXRSS chicane</t>
   </si>
   <si>
-    <t>ENDBSY_2</t>
+    <t>ENDESA</t>
+  </si>
+  <si>
+    <t>ESA</t>
+  </si>
+  <si>
+    <t>ENDBSYA</t>
+  </si>
+  <si>
+    <t>CLTH/BSYH</t>
+  </si>
+  <si>
+    <t>ENDBSYH</t>
+  </si>
+  <si>
+    <t>partial cell</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>CBXFEL chicane #1</t>
+  </si>
+  <si>
+    <t>contains</t>
+  </si>
+  <si>
+    <t>Delta-II</t>
+  </si>
+  <si>
+    <t>overlay</t>
+  </si>
+  <si>
+    <t>SPH</t>
+  </si>
+  <si>
+    <t>SPA</t>
+  </si>
+  <si>
+    <t>SLTD</t>
+  </si>
+  <si>
+    <t>SLTA</t>
+  </si>
+  <si>
+    <t>BYP/SPH</t>
+  </si>
+  <si>
+    <t>SPD1/SPD2/SPD3</t>
+  </si>
+  <si>
+    <t>SPD3</t>
+  </si>
+  <si>
+    <t>SPD1/SPD2/SPA</t>
+  </si>
+  <si>
+    <t>ENDSLTA</t>
+  </si>
+  <si>
+    <t>SLTH/BSYH</t>
+  </si>
+  <si>
+    <t>BEGBSYA</t>
+  </si>
+  <si>
+    <t>BEGCLTS</t>
+  </si>
+  <si>
+    <t>ENDCLTS</t>
+  </si>
+  <si>
+    <t>CLTS</t>
+  </si>
+  <si>
+    <t>BSY coordinates</t>
+  </si>
+  <si>
+    <t>ENDGSPEC</t>
+  </si>
+  <si>
+    <t>GUN/L0/HTR/EMIT/BX0</t>
+  </si>
+  <si>
+    <t>SPEC</t>
+  </si>
+  <si>
+    <t>GSPEC</t>
+  </si>
+  <si>
+    <t>BEGGSPEC</t>
+  </si>
+  <si>
+    <t>BEGSPEC</t>
+  </si>
+  <si>
+    <t>ENDSPEC</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1410,9 +1488,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1421,6 +1496,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1705,7 +1798,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1714,8 +1807,10 @@
     <col min="4" max="4" width="24.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" customWidth="1"/>
     <col min="12" max="12" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1746,10 +1841,10 @@
         <v>21</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>56</v>
@@ -1767,10 +1862,10 @@
         <v>26</v>
       </c>
       <c r="I3" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="K3" s="15"/>
     </row>
@@ -1802,9 +1897,9 @@
         <v>33.300524934383205</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K4" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="K4" s="24" t="s">
         <v>28</v>
       </c>
       <c r="L4" s="1">
@@ -1822,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" ref="E5:E34" si="2">F4</f>
@@ -1840,7 +1935,7 @@
         <f t="shared" ref="H5:H34" si="4">G5/0.3048</f>
         <v>333.33333333333331</v>
       </c>
-      <c r="K5" s="25"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="1">
         <v>2</v>
       </c>
@@ -1874,7 +1969,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333331</v>
       </c>
-      <c r="K6" s="25"/>
+      <c r="K6" s="24"/>
       <c r="L6" s="1">
         <v>3</v>
       </c>
@@ -1908,7 +2003,7 @@
         <f t="shared" si="4"/>
         <v>333.3333333333332</v>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="24"/>
       <c r="L7" s="1">
         <v>4</v>
       </c>
@@ -1942,7 +2037,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K8" s="25"/>
+      <c r="K8" s="24"/>
       <c r="L8" s="1">
         <v>5</v>
       </c>
@@ -1976,7 +2071,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K9" s="25"/>
+      <c r="K9" s="24"/>
       <c r="L9" s="1">
         <v>6</v>
       </c>
@@ -2010,7 +2105,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="24"/>
       <c r="L10" s="1">
         <v>7</v>
       </c>
@@ -2044,7 +2139,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K11" s="25"/>
+      <c r="K11" s="24"/>
       <c r="L11" s="1">
         <v>8</v>
       </c>
@@ -2078,7 +2173,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="24"/>
       <c r="L12" s="1">
         <v>9</v>
       </c>
@@ -2113,12 +2208,12 @@
         <v>333.33333333333337</v>
       </c>
       <c r="I13" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="J13" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="24"/>
       <c r="L13" s="1">
         <v>10</v>
       </c>
@@ -2153,12 +2248,12 @@
         <v>333.33333333333337</v>
       </c>
       <c r="I14" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="K14" s="25"/>
+      <c r="K14" s="24"/>
       <c r="L14" s="1">
         <v>11</v>
       </c>
@@ -2193,12 +2288,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I15" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="K15" s="25"/>
+      <c r="K15" s="24"/>
       <c r="L15" s="1">
         <v>12</v>
       </c>
@@ -2233,12 +2328,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="K16" s="25"/>
+        <v>140</v>
+      </c>
+      <c r="K16" s="24"/>
       <c r="L16" s="1">
         <v>13</v>
       </c>
@@ -2273,12 +2368,12 @@
         <v>333.33333333333377</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="K17" s="25"/>
+        <v>141</v>
+      </c>
+      <c r="K17" s="24"/>
       <c r="L17" s="1">
         <v>14</v>
       </c>
@@ -2313,12 +2408,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="K18" s="25"/>
+        <v>142</v>
+      </c>
+      <c r="K18" s="24"/>
       <c r="L18" s="1">
         <v>15</v>
       </c>
@@ -2353,12 +2448,12 @@
         <v>333.33333333333377</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="K19" s="25"/>
+        <v>143</v>
+      </c>
+      <c r="K19" s="24"/>
       <c r="L19" s="1">
         <v>16</v>
       </c>
@@ -2393,12 +2488,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="K20" s="25"/>
+        <v>144</v>
+      </c>
+      <c r="K20" s="24"/>
       <c r="L20" s="1">
         <v>17</v>
       </c>
@@ -2433,12 +2528,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="K21" s="25"/>
+        <v>145</v>
+      </c>
+      <c r="K21" s="24"/>
       <c r="L21" s="1">
         <v>18</v>
       </c>
@@ -2473,12 +2568,12 @@
         <v>333.33333333333377</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="K22" s="25"/>
+        <v>146</v>
+      </c>
+      <c r="K22" s="24"/>
       <c r="L22" s="1">
         <v>19</v>
       </c>
@@ -2513,12 +2608,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="K23" s="25"/>
+        <v>147</v>
+      </c>
+      <c r="K23" s="24"/>
       <c r="L23" s="1">
         <v>20</v>
       </c>
@@ -2553,12 +2648,12 @@
         <v>333.33333333333377</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K24" s="25"/>
+        <v>148</v>
+      </c>
+      <c r="K24" s="24"/>
       <c r="L24" s="1">
         <v>21</v>
       </c>
@@ -2593,12 +2688,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="K25" s="25"/>
+        <v>149</v>
+      </c>
+      <c r="K25" s="24"/>
       <c r="L25" s="1">
         <v>22</v>
       </c>
@@ -2633,12 +2728,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="K26" s="25"/>
+        <v>150</v>
+      </c>
+      <c r="K26" s="24"/>
       <c r="L26" s="1">
         <v>23</v>
       </c>
@@ -2673,12 +2768,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="K27" s="25"/>
+        <v>151</v>
+      </c>
+      <c r="K27" s="24"/>
       <c r="L27" s="1">
         <v>24</v>
       </c>
@@ -2713,12 +2808,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="K28" s="25"/>
+        <v>152</v>
+      </c>
+      <c r="K28" s="24"/>
       <c r="L28" s="1">
         <v>25</v>
       </c>
@@ -2753,12 +2848,12 @@
         <v>333.33333333333451</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="K29" s="25"/>
+        <v>153</v>
+      </c>
+      <c r="K29" s="24"/>
       <c r="L29" s="1">
         <v>26</v>
       </c>
@@ -2793,12 +2888,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="K30" s="25"/>
+        <v>154</v>
+      </c>
+      <c r="K30" s="24"/>
       <c r="L30" s="1">
         <v>27</v>
       </c>
@@ -2833,12 +2928,12 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="K31" s="25"/>
+        <v>155</v>
+      </c>
+      <c r="K31" s="24"/>
       <c r="L31" s="1">
         <v>28</v>
       </c>
@@ -2872,7 +2967,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K32" s="25"/>
+      <c r="K32" s="24"/>
       <c r="L32" s="1">
         <v>29</v>
       </c>
@@ -2906,7 +3001,7 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="K33" s="25"/>
+      <c r="K33" s="24"/>
       <c r="L33" s="1">
         <v>30</v>
       </c>
@@ -2941,9 +3036,9 @@
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="K34" s="26"/>
+        <v>322</v>
+      </c>
+      <c r="K34" s="25"/>
       <c r="L34" s="1">
         <v>31</v>
       </c>
@@ -2976,12 +3071,12 @@
         <v>569.25524934383191</v>
       </c>
       <c r="I35" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="J35" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="J35" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="K35" s="27" t="s">
+      <c r="K35" s="26" t="s">
         <v>29</v>
       </c>
       <c r="L35" s="1">
@@ -2990,7 +3085,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
@@ -3017,16 +3112,16 @@
         <v>99.234580052493442</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="K36" s="25"/>
+        <v>325</v>
+      </c>
+      <c r="K36" s="24"/>
       <c r="L36" s="1">
         <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B37" s="1">
         <v>1</v>
@@ -3052,14 +3147,14 @@
         <f t="shared" si="6"/>
         <v>85.171587926509247</v>
       </c>
-      <c r="K37" s="25"/>
+      <c r="K37" s="24"/>
       <c r="L37" s="1">
         <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
@@ -3085,14 +3180,14 @@
         <f t="shared" si="6"/>
         <v>90.504265091863431</v>
       </c>
-      <c r="K38" s="25"/>
+      <c r="K38" s="24"/>
       <c r="L38" s="1">
         <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
@@ -3118,14 +3213,14 @@
         <f t="shared" si="6"/>
         <v>100.17946194225736</v>
       </c>
-      <c r="K39" s="25"/>
+      <c r="K39" s="24"/>
       <c r="L39" s="1">
         <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
@@ -3151,14 +3246,14 @@
         <f t="shared" si="6"/>
         <v>89.236876640419837</v>
       </c>
-      <c r="K40" s="25"/>
+      <c r="K40" s="24"/>
       <c r="L40" s="1">
         <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
@@ -3184,14 +3279,14 @@
         <f t="shared" si="6"/>
         <v>90.484908136482858</v>
       </c>
-      <c r="K41" s="25"/>
+      <c r="K41" s="24"/>
       <c r="L41" s="1">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
@@ -3217,14 +3312,14 @@
         <f t="shared" si="6"/>
         <v>75.762795275590648</v>
       </c>
-      <c r="K42" s="25"/>
+      <c r="K42" s="24"/>
       <c r="L42" s="1">
         <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
@@ -3250,14 +3345,14 @@
         <f t="shared" si="6"/>
         <v>95.227034120734857</v>
       </c>
-      <c r="K43" s="25"/>
+      <c r="K43" s="24"/>
       <c r="L43" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B44" s="1">
         <v>1</v>
@@ -3283,14 +3378,14 @@
         <f t="shared" si="6"/>
         <v>99.886811023622172</v>
       </c>
-      <c r="K44" s="25"/>
+      <c r="K44" s="24"/>
       <c r="L44" s="1">
         <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B45" s="1">
         <v>1</v>
@@ -3316,14 +3411,14 @@
         <f t="shared" si="6"/>
         <v>88.113845144356958</v>
       </c>
-      <c r="K45" s="25"/>
+      <c r="K45" s="24"/>
       <c r="L45" s="1">
         <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B46" s="1">
         <v>1</v>
@@ -3349,14 +3444,14 @@
         <f t="shared" si="6"/>
         <v>95.997703412073378</v>
       </c>
-      <c r="K46" s="25"/>
+      <c r="K46" s="24"/>
       <c r="L46" s="1">
         <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B47" s="1">
         <v>1</v>
@@ -3383,16 +3478,16 @@
         <v>111.05314960629936</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="K47" s="25"/>
+        <v>332</v>
+      </c>
+      <c r="K47" s="24"/>
       <c r="L47" s="1">
         <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
@@ -3415,20 +3510,20 @@
         <v>41.929491999999982</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" ref="H48:H58" si="9">G48/0.3048</f>
+        <f t="shared" ref="H48:H57" si="9">G48/0.3048</f>
         <v>137.56395013123353</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="K48" s="25"/>
+        <v>338</v>
+      </c>
+      <c r="K48" s="24"/>
       <c r="L48" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B49" s="1">
         <v>1</v>
@@ -3454,14 +3549,14 @@
         <f t="shared" si="9"/>
         <v>115.48556430446172</v>
       </c>
-      <c r="K49" s="25"/>
+      <c r="K49" s="24"/>
       <c r="L49" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B50" s="1">
         <v>1</v>
@@ -3487,14 +3582,14 @@
         <f t="shared" si="9"/>
         <v>115.48556430446209</v>
       </c>
-      <c r="K50" s="25"/>
+      <c r="K50" s="24"/>
       <c r="L50" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B51" s="1">
         <v>1</v>
@@ -3521,16 +3616,16 @@
         <v>132.8740157480315</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="K51" s="25"/>
+        <v>339</v>
+      </c>
+      <c r="K51" s="24"/>
       <c r="L51" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
@@ -3557,19 +3652,19 @@
         <v>52.242480314960531</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="K52" s="25"/>
+        <v>341</v>
+      </c>
+      <c r="K52" s="24"/>
       <c r="L52" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B53" s="1">
         <v>1</v>
@@ -3596,19 +3691,19 @@
         <v>101.91929133858285</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="K53" s="25"/>
+        <v>343</v>
+      </c>
+      <c r="K53" s="24"/>
       <c r="L53" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B54" s="1">
         <v>2</v>
@@ -3617,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E54" s="3">
         <v>686.41033000000004</v>
@@ -3634,19 +3729,19 @@
         <v>90.767290026246471</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J54" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="K54" s="25"/>
+        <v>345</v>
+      </c>
+      <c r="K54" s="24"/>
       <c r="L54" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B55" s="1">
         <v>3</v>
@@ -3655,7 +3750,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E55" s="3">
         <v>700.52800000000002</v>
@@ -3672,19 +3767,19 @@
         <v>130.42318241469803</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="J55" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="K55" s="25"/>
+        <v>365</v>
+      </c>
+      <c r="K55" s="24"/>
       <c r="L55" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B56" s="1">
         <v>4</v>
@@ -3693,7 +3788,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E56" s="3">
         <v>733.77200000000005</v>
@@ -3710,19 +3805,19 @@
         <v>73.253152887138924</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="J56" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="J56" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="K56" s="25"/>
+      <c r="K56" s="24"/>
       <c r="L56" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B57" s="1">
         <v>5</v>
@@ -3731,7 +3826,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E57" s="1">
         <v>733.77200000000005</v>
@@ -3748,72 +3843,649 @@
         <v>80.439632545931474</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="J57" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="K57" s="25"/>
+        <v>368</v>
+      </c>
+      <c r="K57" s="24"/>
       <c r="L57" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="B58" s="12">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B58" s="1">
         <v>9</v>
       </c>
-      <c r="C58" s="12">
-        <v>1</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="E58" s="12">
-        <v>176.02099999999999</v>
-      </c>
-      <c r="F58" s="13">
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E58" s="1">
+        <v>130.392</v>
+      </c>
+      <c r="F58" s="3">
         <v>313.05599999999998</v>
       </c>
-      <c r="G58" s="13">
+      <c r="G58" s="3">
         <f t="shared" si="8"/>
-        <v>137.035</v>
-      </c>
-      <c r="H58" s="14">
-        <f t="shared" si="9"/>
-        <v>449.58989501312334</v>
-      </c>
-      <c r="I58" s="12"/>
-      <c r="J58" s="18" t="s">
-        <v>381</v>
+        <v>182.66399999999999</v>
+      </c>
+      <c r="H58" s="2">
+        <f>G58/0.3048</f>
+        <v>599.2913385826771</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J58" s="17" t="s">
+        <v>377</v>
       </c>
       <c r="K58" s="24"/>
       <c r="L58" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>1</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>338</v>
+    <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B59" s="12">
+        <v>9</v>
+      </c>
+      <c r="C59" s="12">
+        <v>1</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="E59" s="12">
+        <v>313.05599999999998</v>
+      </c>
+      <c r="F59" s="13">
+        <v>455.10700000000003</v>
+      </c>
+      <c r="G59" s="13">
+        <f t="shared" ref="G59" si="10">F59-E59</f>
+        <v>142.05100000000004</v>
+      </c>
+      <c r="H59" s="14">
+        <f t="shared" ref="H59" si="11">G59/0.3048</f>
+        <v>466.04658792650929</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="K59" s="25"/>
+      <c r="L59" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="str">
+        <f>$A$5</f>
+        <v>S01</v>
+      </c>
+      <c r="B60" s="1">
+        <v>8</v>
+      </c>
+      <c r="C60" s="1">
+        <f>$C$5</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="1" t="str">
+        <f>$D$5</f>
+        <v>L0B/HTR/DIAG0/COL0/L1B</v>
+      </c>
+      <c r="E60" s="3">
+        <f>$E$5</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <f>$F$5</f>
+        <v>101.6</v>
+      </c>
+      <c r="G60" s="3">
+        <f>$G$5</f>
+        <v>101.6</v>
+      </c>
+      <c r="H60" s="2">
+        <f>$H$5</f>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="K60" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="L60" s="1">
+        <v>57</v>
+      </c>
+      <c r="M60" s="1">
+        <f>$L$5</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="str">
+        <f>$A$32</f>
+        <v>S28</v>
+      </c>
+      <c r="B61" s="1">
+        <v>6</v>
+      </c>
+      <c r="C61" s="1">
+        <f>$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="E61" s="3">
+        <f>$E$32</f>
+        <v>2743.2</v>
+      </c>
+      <c r="F61" s="3">
+        <f>$F$32</f>
+        <v>2844.7999999999997</v>
+      </c>
+      <c r="G61" s="3">
+        <f>$G$32</f>
+        <v>101.59999999999991</v>
+      </c>
+      <c r="H61" s="2">
+        <f>$H$32</f>
+        <v>333.33333333333303</v>
+      </c>
+      <c r="K61" s="31"/>
+      <c r="L61" s="1">
+        <v>58</v>
+      </c>
+      <c r="M61" s="1">
+        <f>$L$32</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="str">
+        <f>$A$32</f>
+        <v>S28</v>
+      </c>
+      <c r="B62" s="1">
+        <v>7</v>
+      </c>
+      <c r="C62" s="1">
+        <f>$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="9" t="str">
+        <f>$D$32</f>
+        <v>BYP/SPD1</v>
+      </c>
+      <c r="E62" s="3">
+        <f>$E$32</f>
+        <v>2743.2</v>
+      </c>
+      <c r="F62" s="3">
+        <f>$F$32</f>
+        <v>2844.7999999999997</v>
+      </c>
+      <c r="G62" s="3">
+        <f>$G$32</f>
+        <v>101.59999999999991</v>
+      </c>
+      <c r="H62" s="2">
+        <f>$H$32</f>
+        <v>333.33333333333303</v>
+      </c>
+      <c r="K62" s="31"/>
+      <c r="L62" s="1">
+        <v>59</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" ref="M62:M63" si="12">$L$32</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="str">
+        <f>$A$32</f>
+        <v>S28</v>
+      </c>
+      <c r="B63" s="1">
+        <v>9</v>
+      </c>
+      <c r="C63" s="1">
+        <f>$C$32</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="9" t="str">
+        <f>$D$32</f>
+        <v>BYP/SPD1</v>
+      </c>
+      <c r="E63" s="3">
+        <f>$E$32</f>
+        <v>2743.2</v>
+      </c>
+      <c r="F63" s="3">
+        <f>$F$32</f>
+        <v>2844.7999999999997</v>
+      </c>
+      <c r="G63" s="3">
+        <f>$G$32</f>
+        <v>101.59999999999991</v>
+      </c>
+      <c r="H63" s="2">
+        <f>$H$32</f>
+        <v>333.33333333333303</v>
+      </c>
+      <c r="K63" s="31"/>
+      <c r="L63" s="1">
+        <v>60</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="12"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" s="9" t="str">
+        <f>$A$33</f>
+        <v>S29</v>
+      </c>
+      <c r="B64" s="1">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1">
+        <f>$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E64" s="3">
+        <f>$E$33</f>
+        <v>2844.7999999999997</v>
+      </c>
+      <c r="F64" s="3">
+        <f>$F$33</f>
+        <v>2946.3999999999996</v>
+      </c>
+      <c r="G64" s="3">
+        <f>$G$33</f>
+        <v>101.59999999999991</v>
+      </c>
+      <c r="H64" s="2">
+        <f>$H$33</f>
+        <v>333.33333333333303</v>
+      </c>
+      <c r="K64" s="31"/>
+      <c r="L64" s="1">
+        <v>61</v>
+      </c>
+      <c r="M64" s="1">
+        <f>$L$33</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="str">
+        <f>$A$33</f>
+        <v>S29</v>
+      </c>
+      <c r="B65" s="1">
+        <v>7</v>
+      </c>
+      <c r="C65" s="1">
+        <f>$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="E65" s="3">
+        <f>$E$33</f>
+        <v>2844.7999999999997</v>
+      </c>
+      <c r="F65" s="3">
+        <f>$F$33</f>
+        <v>2946.3999999999996</v>
+      </c>
+      <c r="G65" s="3">
+        <f>$G$33</f>
+        <v>101.59999999999991</v>
+      </c>
+      <c r="H65" s="2">
+        <f>$H$33</f>
+        <v>333.33333333333303</v>
+      </c>
+      <c r="K65" s="31"/>
+      <c r="L65" s="1">
+        <v>62</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" ref="M65:M66" si="13">$L$33</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="str">
+        <f>$A$33</f>
+        <v>S29</v>
+      </c>
+      <c r="B66" s="1">
+        <v>9</v>
+      </c>
+      <c r="C66" s="1">
+        <f>$C$33</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E66" s="3">
+        <f>$E$33</f>
+        <v>2844.7999999999997</v>
+      </c>
+      <c r="F66" s="3">
+        <f>$F$33</f>
+        <v>2946.3999999999996</v>
+      </c>
+      <c r="G66" s="3">
+        <f>$G$33</f>
+        <v>101.59999999999991</v>
+      </c>
+      <c r="H66" s="2">
+        <f>$H$33</f>
+        <v>333.33333333333303</v>
+      </c>
+      <c r="K66" s="31"/>
+      <c r="L66" s="1">
+        <v>63</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="30" t="str">
+        <f>$A$34</f>
+        <v>S30</v>
+      </c>
+      <c r="B67" s="30">
+        <v>6</v>
+      </c>
+      <c r="C67" s="30">
+        <f>$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="E67" s="28">
+        <f>$E$34</f>
+        <v>2946.3999999999996</v>
+      </c>
+      <c r="F67" s="28">
+        <f>$F$34</f>
+        <v>3050.5120000000002</v>
+      </c>
+      <c r="G67" s="28">
+        <f>$G$34</f>
+        <v>104.11200000000053</v>
+      </c>
+      <c r="H67" s="29">
+        <f>$H$34</f>
+        <v>341.57480314960804</v>
+      </c>
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="1">
+        <v>64</v>
+      </c>
+      <c r="M67" s="1">
+        <f>$L$34</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="30" t="str">
+        <f>$A$34</f>
+        <v>S30</v>
+      </c>
+      <c r="B68" s="30">
+        <v>7</v>
+      </c>
+      <c r="C68" s="30">
+        <f>$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="E68" s="28">
+        <f>$E$34</f>
+        <v>2946.3999999999996</v>
+      </c>
+      <c r="F68" s="28">
+        <f>$F$34</f>
+        <v>3050.5120000000002</v>
+      </c>
+      <c r="G68" s="28">
+        <f>$G$34</f>
+        <v>104.11200000000053</v>
+      </c>
+      <c r="H68" s="29">
+        <f>$H$34</f>
+        <v>341.57480314960804</v>
+      </c>
+      <c r="I68" s="27"/>
+      <c r="J68" s="27"/>
+      <c r="K68" s="31"/>
+      <c r="L68" s="1">
+        <v>65</v>
+      </c>
+      <c r="M68" s="1">
+        <f>$L$34</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="30" t="str">
+        <f>$A$34</f>
+        <v>S30</v>
+      </c>
+      <c r="B69" s="30">
+        <v>9</v>
+      </c>
+      <c r="C69" s="30">
+        <f>$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="D69" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="E69" s="28">
+        <f>$E$34</f>
+        <v>2946.3999999999996</v>
+      </c>
+      <c r="F69" s="28">
+        <f>$F$34</f>
+        <v>3050.5120000000002</v>
+      </c>
+      <c r="G69" s="28">
+        <f>$G$34</f>
+        <v>104.11200000000053</v>
+      </c>
+      <c r="H69" s="29">
+        <f>$H$34</f>
+        <v>341.57480314960804</v>
+      </c>
+      <c r="I69" s="27"/>
+      <c r="J69" s="27"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="1">
+        <v>66</v>
+      </c>
+      <c r="M69" s="1">
+        <f>$L$34</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="27" t="str">
+        <f>$A$35</f>
+        <v>BSY</v>
+      </c>
+      <c r="B70" s="27">
+        <v>6</v>
+      </c>
+      <c r="C70" s="27">
+        <f>$C$35</f>
+        <v>1</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="E70" s="28">
+        <v>2.512</v>
+      </c>
+      <c r="F70" s="28">
+        <v>176.02099999999999</v>
+      </c>
+      <c r="G70" s="28">
+        <f>F70-E70</f>
+        <v>173.50899999999999</v>
+      </c>
+      <c r="H70" s="29">
+        <f>G70/0.3048</f>
+        <v>569.25524934383191</v>
+      </c>
+      <c r="I70" s="27"/>
+      <c r="J70" s="27"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="1">
+        <v>67</v>
+      </c>
+      <c r="M70" s="1">
+        <f>$L$35</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="27" t="str">
+        <f>$A$35</f>
+        <v>BSY</v>
+      </c>
+      <c r="B71" s="27">
+        <v>7</v>
+      </c>
+      <c r="C71" s="27">
+        <f>$C$35</f>
+        <v>1</v>
+      </c>
+      <c r="D71" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="E71" s="28">
+        <v>2.512</v>
+      </c>
+      <c r="F71" s="28">
+        <v>162.65100000000001</v>
+      </c>
+      <c r="G71" s="28">
+        <f>F71-E71</f>
+        <v>160.13900000000001</v>
+      </c>
+      <c r="H71" s="29">
+        <f>G71/0.3048</f>
+        <v>525.39041994750653</v>
+      </c>
+      <c r="I71" s="27"/>
+      <c r="J71" s="27"/>
+      <c r="K71" s="31"/>
+      <c r="L71" s="1">
+        <v>68</v>
+      </c>
+      <c r="M71" s="1">
+        <f>$L$35</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="12" t="str">
+        <f>$A$35</f>
+        <v>BSY</v>
+      </c>
+      <c r="B72" s="12">
+        <v>9</v>
+      </c>
+      <c r="C72" s="12">
+        <f>$C$35</f>
+        <v>1</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="E72" s="13">
+        <v>2.512</v>
+      </c>
+      <c r="F72" s="13">
+        <v>130.392</v>
+      </c>
+      <c r="G72" s="13">
+        <f>F72-E72</f>
+        <v>127.88</v>
+      </c>
+      <c r="H72" s="14">
+        <f>G72/0.3048</f>
+        <v>419.5538057742782</v>
+      </c>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="K72" s="32"/>
+      <c r="L72" s="1">
+        <v>69</v>
+      </c>
+      <c r="M72" s="27">
+        <f>$L$35</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>1</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="K4:K34"/>
-    <mergeCell ref="K35:K57"/>
+    <mergeCell ref="K35:K59"/>
+    <mergeCell ref="K60:K72"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="61" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G60:H60 G71" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3822,7 +4494,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -3831,7 +4503,8 @@
     <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -3853,7 +4526,7 @@
       <c r="C1" s="10"/>
       <c r="F1" s="7"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="2"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -3863,17 +4536,17 @@
       <c r="E2" s="5"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>56</v>
@@ -3887,14 +4560,14 @@
       <c r="G3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>26</v>
       </c>
       <c r="I3" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="K3" s="15"/>
     </row>
@@ -3909,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>402</v>
       </c>
       <c r="E4" s="3">
         <v>2017.911482</v>
@@ -3921,17 +4594,17 @@
         <f>F4-E4</f>
         <v>17.123648000000003</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <f>G4/0.3048</f>
         <v>56.179947506561689</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="K4" s="25" t="s">
+        <v>346</v>
+      </c>
+      <c r="K4" s="24" t="s">
         <v>28</v>
       </c>
       <c r="L4" s="1">
@@ -3949,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E5" s="3">
         <f>F4</f>
@@ -3963,17 +4636,17 @@
         <f t="shared" ref="G5:G14" si="0">F5-E5</f>
         <v>98.564869999999928</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <f t="shared" ref="H5:H14" si="1">G5/0.3048</f>
         <v>323.37555774278189</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="K5" s="25"/>
+        <v>328</v>
+      </c>
+      <c r="K5" s="24"/>
       <c r="L5" s="1">
         <v>2</v>
       </c>
@@ -4003,17 +4676,17 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K6" s="25"/>
+      <c r="K6" s="24"/>
       <c r="L6" s="1">
         <v>3</v>
       </c>
@@ -4043,17 +4716,17 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="K7" s="25"/>
+        <v>167</v>
+      </c>
+      <c r="K7" s="24"/>
       <c r="L7" s="1">
         <v>4</v>
       </c>
@@ -4069,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="2"/>
@@ -4083,17 +4756,17 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="K8" s="25"/>
+        <v>335</v>
+      </c>
+      <c r="K8" s="24"/>
       <c r="L8" s="1">
         <v>5</v>
       </c>
@@ -4123,17 +4796,17 @@
         <f t="shared" si="0"/>
         <v>101.60000000000036</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333451</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K9" s="25"/>
+        <v>168</v>
+      </c>
+      <c r="K9" s="24"/>
       <c r="L9" s="1">
         <v>6</v>
       </c>
@@ -4163,17 +4836,17 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K10" s="25"/>
+        <v>169</v>
+      </c>
+      <c r="K10" s="24"/>
       <c r="L10" s="1">
         <v>7</v>
       </c>
@@ -4203,17 +4876,17 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K11" s="25"/>
+        <v>170</v>
+      </c>
+      <c r="K11" s="24"/>
       <c r="L11" s="1">
         <v>8</v>
       </c>
@@ -4243,17 +4916,17 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="K12" s="25"/>
+        <v>171</v>
+      </c>
+      <c r="K12" s="24"/>
       <c r="L12" s="1">
         <v>9</v>
       </c>
@@ -4283,17 +4956,17 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="3">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K13" s="25"/>
+        <v>172</v>
+      </c>
+      <c r="K13" s="24"/>
       <c r="L13" s="1">
         <v>10</v>
       </c>
@@ -4309,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" s="13">
         <f t="shared" si="2"/>
@@ -4322,17 +4995,17 @@
         <f t="shared" si="0"/>
         <v>104.11200000000053</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <f t="shared" si="1"/>
         <v>341.57480314960804</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="K14" s="26"/>
+        <v>347</v>
+      </c>
+      <c r="K14" s="25"/>
       <c r="L14" s="1">
         <v>11</v>
       </c>
@@ -4348,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="E15" s="3">
         <v>2.512</v>
@@ -4360,18 +5033,18 @@
         <f t="shared" ref="G15:G27" si="3">F15-E15</f>
         <v>173.50899999999999</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <f t="shared" ref="H15:H27" si="4">G15/0.3048</f>
         <v>569.25524934383191</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="K15" s="27" t="s">
-        <v>29</v>
+        <v>379</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>400</v>
       </c>
       <c r="L15" s="1">
         <v>12</v>
@@ -4379,7 +5052,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
@@ -4401,21 +5074,21 @@
         <f t="shared" si="3"/>
         <v>27.509000000000015</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <f t="shared" si="4"/>
         <v>90.252624671916053</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="K16" s="25"/>
+        <v>326</v>
+      </c>
+      <c r="K16" s="24"/>
       <c r="L16" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="1">
         <v>10</v>
@@ -4437,18 +5110,18 @@
         <f t="shared" si="3"/>
         <v>27.749300000000005</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="3">
         <f t="shared" si="4"/>
         <v>91.041010498687683</v>
       </c>
-      <c r="K17" s="25"/>
+      <c r="K17" s="24"/>
       <c r="L17" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1">
         <v>10</v>
@@ -4470,18 +5143,18 @@
         <f t="shared" si="3"/>
         <v>29.200700000000012</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="3">
         <f t="shared" si="4"/>
         <v>95.802821522309742</v>
       </c>
-      <c r="K18" s="25"/>
+      <c r="K18" s="24"/>
       <c r="L18" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" s="1">
         <v>10</v>
@@ -4503,18 +5176,18 @@
         <f t="shared" si="3"/>
         <v>26.279999999999973</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="3">
         <f t="shared" si="4"/>
         <v>86.220472440944789</v>
       </c>
-      <c r="K19" s="25"/>
+      <c r="K19" s="24"/>
       <c r="L19" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="1">
         <v>10</v>
@@ -4536,18 +5209,18 @@
         <f t="shared" si="3"/>
         <v>27.769999999999982</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="3">
         <f t="shared" si="4"/>
         <v>91.108923884514368</v>
       </c>
-      <c r="K20" s="25"/>
+      <c r="K20" s="24"/>
       <c r="L20" s="1">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
@@ -4569,18 +5242,18 @@
         <f t="shared" si="3"/>
         <v>27.740000000000009</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="3">
         <f t="shared" si="4"/>
         <v>91.010498687664068</v>
       </c>
-      <c r="K21" s="25"/>
+      <c r="K21" s="24"/>
       <c r="L21" s="1">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B22" s="1">
         <v>10</v>
@@ -4602,18 +5275,18 @@
         <f t="shared" si="3"/>
         <v>29.150000000000034</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="3">
         <f t="shared" si="4"/>
         <v>95.636482939632657</v>
       </c>
-      <c r="K22" s="25"/>
+      <c r="K22" s="24"/>
       <c r="L22" s="1">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
@@ -4635,18 +5308,18 @@
         <f t="shared" si="3"/>
         <v>26.339999999999975</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="3">
         <f t="shared" si="4"/>
         <v>86.417322834645589</v>
       </c>
-      <c r="K23" s="25"/>
+      <c r="K23" s="24"/>
       <c r="L23" s="1">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="1">
         <v>10</v>
@@ -4668,18 +5341,18 @@
         <f t="shared" si="3"/>
         <v>27.769999999999982</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="3">
         <f t="shared" si="4"/>
         <v>91.108923884514368</v>
       </c>
-      <c r="K24" s="25"/>
+      <c r="K24" s="24"/>
       <c r="L24" s="1">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="1">
         <v>10</v>
@@ -4701,18 +5374,18 @@
         <f t="shared" si="3"/>
         <v>27.75</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="3">
         <f t="shared" si="4"/>
         <v>91.043307086614163</v>
       </c>
-      <c r="K25" s="25"/>
+      <c r="K25" s="24"/>
       <c r="L25" s="1">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B26" s="1">
         <v>10</v>
@@ -4734,18 +5407,18 @@
         <f t="shared" si="3"/>
         <v>27.75</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="3">
         <f t="shared" si="4"/>
         <v>91.043307086614163</v>
       </c>
-      <c r="K26" s="25"/>
+      <c r="K26" s="24"/>
       <c r="L26" s="1">
         <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B27" s="1">
         <v>10</v>
@@ -4767,21 +5440,21 @@
         <f t="shared" si="3"/>
         <v>33.710001000000034</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="3">
         <f t="shared" si="4"/>
         <v>110.59711614173239</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="K27" s="25"/>
+        <v>331</v>
+      </c>
+      <c r="K27" s="24"/>
       <c r="L27" s="1">
         <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="1">
         <v>10</v>
@@ -4808,16 +5481,16 @@
         <v>119.6488976377952</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="K28" s="25"/>
+        <v>350</v>
+      </c>
+      <c r="K28" s="24"/>
       <c r="L28" s="1">
         <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B29" s="1">
         <v>10</v>
@@ -4843,14 +5516,14 @@
         <f>G29/0.3048</f>
         <v>118.48425196850404</v>
       </c>
-      <c r="K29" s="25"/>
+      <c r="K29" s="24"/>
       <c r="L29" s="1">
         <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="1">
         <v>10</v>
@@ -4876,14 +5549,14 @@
         <f>G30/0.3048</f>
         <v>118.48425196850404</v>
       </c>
-      <c r="K30" s="25"/>
+      <c r="K30" s="24"/>
       <c r="L30" s="1">
         <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B31" s="1">
         <v>10</v>
@@ -4910,16 +5583,16 @@
         <v>154.36190288713891</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="K31" s="25"/>
+        <v>349</v>
+      </c>
+      <c r="K31" s="24"/>
       <c r="L31" s="1">
         <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B32" s="1">
         <v>10</v>
@@ -4928,7 +5601,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E32" s="3">
         <f t="shared" si="5"/>
@@ -4941,24 +5614,24 @@
         <f t="shared" si="6"/>
         <v>15.923506999999972</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="3">
         <f t="shared" ref="H32" si="7">G32/0.3048</f>
         <v>52.24247703412064</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="K32" s="25"/>
+        <v>352</v>
+      </c>
+      <c r="K32" s="24"/>
       <c r="L32" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="1">
         <v>10</v>
@@ -4980,24 +5653,24 @@
         <f t="shared" si="6"/>
         <v>31.065000000000055</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="3">
         <f>G33/0.3048</f>
         <v>101.91929133858285</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="K33" s="25"/>
+        <v>354</v>
+      </c>
+      <c r="K33" s="24"/>
       <c r="L33" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B34" s="1">
         <v>11</v>
@@ -5006,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E34" s="3">
         <v>686.41033100000004</v>
@@ -5018,176 +5691,257 @@
         <f t="shared" si="6"/>
         <v>27.665869999999927</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="3">
         <f t="shared" ref="H34" si="8">G34/0.3048</f>
         <v>90.767290026246471</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="K34" s="25"/>
+        <v>356</v>
+      </c>
+      <c r="K34" s="24"/>
       <c r="L34" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>328</v>
+        <v>111</v>
       </c>
       <c r="B35" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>328</v>
+        <v>110</v>
       </c>
       <c r="E35" s="3">
-        <v>69.408164999999997</v>
+        <v>700.52800000000002</v>
       </c>
       <c r="F35" s="3">
-        <v>313.05570299999999</v>
+        <v>759.06192899999996</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" ref="G35:G36" si="9">F35-E35</f>
-        <v>243.647538</v>
-      </c>
-      <c r="H35" s="2">
-        <f t="shared" ref="H35:H36" si="10">G35/0.3048</f>
-        <v>799.36856299212593</v>
+        <f t="shared" ref="G35" si="9">F35-E35</f>
+        <v>58.533928999999944</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" ref="H35" si="10">G35/0.3048</f>
+        <v>192.04044947506543</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="K35" s="25"/>
+        <v>358</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="K35" s="24"/>
       <c r="L35" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="1">
-        <v>12</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="1" t="s">
+    <row r="36" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E36" s="3">
-        <v>700.52800000000002</v>
-      </c>
-      <c r="F36" s="3">
-        <v>759.06192899999996</v>
-      </c>
-      <c r="G36" s="3">
-        <f t="shared" si="9"/>
-        <v>58.533928999999944</v>
-      </c>
-      <c r="H36" s="2">
-        <f t="shared" si="10"/>
-        <v>192.04044947506543</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>364</v>
+      <c r="B36" s="12">
+        <v>13</v>
+      </c>
+      <c r="C36" s="12">
+        <v>1</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="E36" s="13">
+        <v>739.999999</v>
+      </c>
+      <c r="F36" s="13">
+        <v>758.36086899999998</v>
+      </c>
+      <c r="G36" s="13">
+        <f t="shared" si="6"/>
+        <v>18.360869999999977</v>
+      </c>
+      <c r="H36" s="13">
+        <f t="shared" ref="H36:H37" si="11">G36/0.3048</f>
+        <v>60.239074803149528</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>362</v>
       </c>
       <c r="K36" s="25"/>
       <c r="L36" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="12">
-        <v>13</v>
-      </c>
-      <c r="C37" s="12">
-        <v>1</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="E37" s="13">
-        <v>739.999999</v>
-      </c>
-      <c r="F37" s="13">
-        <v>758.36086899999998</v>
-      </c>
-      <c r="G37" s="13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="1">
+        <v>14</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E37" s="3">
+        <v>10.456</v>
+      </c>
+      <c r="F37" s="3">
+        <v>129.65199999999999</v>
+      </c>
+      <c r="G37" s="3">
         <f t="shared" si="6"/>
-        <v>18.360869999999977</v>
-      </c>
-      <c r="H37" s="14">
-        <f t="shared" ref="H37" si="11">G37/0.3048</f>
-        <v>60.239074803149528</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="J37" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="K37" s="26"/>
+        <v>119.19599999999998</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="11"/>
+        <v>391.06299212598418</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K37" s="26" t="s">
+        <v>385</v>
+      </c>
       <c r="L37" s="1">
         <v>34</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K38" s="11"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="K39" s="11"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>1</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>338</v>
-      </c>
+      <c r="M37" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="1">
+        <v>15</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2018.712</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2018.4469999999999</v>
+      </c>
+      <c r="G38" s="3">
+        <f>E38-F38</f>
+        <v>0.26500000000010004</v>
+      </c>
+      <c r="H38" s="3">
+        <f>G38/0.3048</f>
+        <v>0.86942257217880592</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="K38" s="24"/>
+      <c r="L38" s="1">
+        <v>35</v>
+      </c>
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="12">
+        <v>16</v>
+      </c>
+      <c r="C39" s="12">
+        <v>0</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E39" s="13">
+        <v>2031.991</v>
+      </c>
+      <c r="F39" s="13">
+        <v>2036.7750000000001</v>
+      </c>
+      <c r="G39" s="13">
+        <f>F39-E39</f>
+        <v>4.7840000000001055</v>
+      </c>
+      <c r="H39" s="13">
+        <f t="shared" ref="H39" si="12">G39/0.3048</f>
+        <v>15.695538057743127</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="K39" s="25"/>
+      <c r="L39" s="1">
+        <v>36</v>
+      </c>
+      <c r="M39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K40" s="11"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B41" s="1"/>
       <c r="K41" s="11"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>1</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>336</v>
+      </c>
       <c r="K42" s="11"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K43" s="11"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K44" s="11"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K45" s="11"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K46" s="11"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K47" s="11"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K48" s="11"/>
     </row>
     <row r="49" spans="11:11" x14ac:dyDescent="0.25">
@@ -5214,13 +5968,23 @@
     <row r="56" spans="11:11" x14ac:dyDescent="0.25">
       <c r="K56" s="11"/>
     </row>
+    <row r="57" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K57" s="11"/>
+    </row>
+    <row r="58" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K58" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="K4:K14"/>
-    <mergeCell ref="K15:K37"/>
+    <mergeCell ref="K15:K36"/>
+    <mergeCell ref="K37:K39"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="60" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G38" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5235,15 +5999,15 @@
     <col min="4" max="5" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="3"/>
     <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>56</v>
@@ -5260,16 +6024,22 @@
       <c r="G1" s="14" t="s">
         <v>26</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D2" s="3">
         <v>517.54</v>
@@ -5285,19 +6055,19 @@
         <f>F2/0.3048</f>
         <v>8.0265485564305603</v>
       </c>
-      <c r="H2" t="s">
-        <v>379</v>
+      <c r="I2" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D3" s="3">
         <v>519.986492</v>
@@ -5313,19 +6083,19 @@
         <f t="shared" ref="G3:G36" si="1">F3/0.3048</f>
         <v>14.435695538057667</v>
       </c>
-      <c r="H3" t="s">
-        <v>379</v>
+      <c r="H3" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D4" s="3">
         <v>524.38649199999998</v>
@@ -5341,19 +6111,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H4" t="s">
-        <v>379</v>
+      <c r="H4" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D5" s="3">
         <v>528.78649199999995</v>
@@ -5369,19 +6139,19 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H5" t="s">
-        <v>379</v>
+      <c r="H5" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D6" s="3">
         <v>533.18649200000004</v>
@@ -5397,19 +6167,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H6" t="s">
-        <v>379</v>
+      <c r="H6" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D7" s="3">
         <v>537.58649200000002</v>
@@ -5425,19 +6195,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H7" t="s">
-        <v>379</v>
+      <c r="H7" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D8" s="3">
         <v>541.986492</v>
@@ -5453,19 +6223,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H8" t="s">
-        <v>379</v>
+      <c r="H8" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D9" s="3">
         <v>546.38649199999998</v>
@@ -5481,19 +6251,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H9" t="s">
-        <v>379</v>
+      <c r="H9" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D10" s="3">
         <v>550.78649199999995</v>
@@ -5509,19 +6279,19 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H10" t="s">
-        <v>379</v>
+      <c r="H10" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D11" s="3">
         <v>555.18649200000004</v>
@@ -5537,19 +6307,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H11" t="s">
-        <v>379</v>
+      <c r="H11" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D12" s="3">
         <v>559.58649200000002</v>
@@ -5565,22 +6335,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H12" t="s">
-        <v>209</v>
-      </c>
-      <c r="I12" s="1">
-        <v>26</v>
+      <c r="H12" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D13" s="3">
         <v>563.986492</v>
@@ -5596,22 +6363,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H13" t="s">
-        <v>209</v>
-      </c>
-      <c r="I13" s="1">
-        <v>27</v>
+      <c r="H13" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3">
         <v>568.38649199999998</v>
@@ -5627,22 +6391,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H14" t="s">
-        <v>209</v>
-      </c>
-      <c r="I14" s="1">
-        <v>28</v>
+      <c r="H14" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D15" s="3">
         <v>572.78649199999995</v>
@@ -5658,22 +6419,19 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H15" t="s">
-        <v>209</v>
-      </c>
-      <c r="I15" s="1">
-        <v>29</v>
+      <c r="H15" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D16" s="3">
         <v>577.18649200000004</v>
@@ -5689,22 +6447,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H16" t="s">
-        <v>209</v>
-      </c>
-      <c r="I16" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H16" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D17" s="3">
         <v>581.58649200000002</v>
@@ -5720,22 +6475,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H17" t="s">
-        <v>209</v>
-      </c>
-      <c r="I17" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H17" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D18" s="3">
         <v>585.986492</v>
@@ -5751,22 +6503,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H18" t="s">
-        <v>209</v>
-      </c>
-      <c r="I18" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H18" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D19" s="3">
         <v>590.38649199999998</v>
@@ -5782,22 +6531,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H19" t="s">
-        <v>209</v>
-      </c>
-      <c r="I19" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H19" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D20" s="3">
         <v>594.78649199999995</v>
@@ -5813,22 +6559,19 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H20" t="s">
-        <v>209</v>
-      </c>
-      <c r="I20" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H20" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D21" s="3">
         <v>599.18649200000004</v>
@@ -5844,19 +6587,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H21" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H21" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D22" s="3">
         <v>603.58649200000002</v>
@@ -5872,22 +6615,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H22" t="s">
-        <v>209</v>
-      </c>
-      <c r="I22" s="1">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H22" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23" s="3">
         <v>607.986492</v>
@@ -5903,22 +6643,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H23" t="s">
-        <v>209</v>
-      </c>
-      <c r="I23" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H23" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D24" s="3">
         <v>612.38649199999998</v>
@@ -5934,22 +6671,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H24" t="s">
-        <v>209</v>
-      </c>
-      <c r="I24" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H24" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D25" s="3">
         <v>616.78649199999995</v>
@@ -5965,22 +6699,19 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H25" t="s">
-        <v>209</v>
-      </c>
-      <c r="I25" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H25" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D26" s="3">
         <v>621.18649200000004</v>
@@ -5996,22 +6727,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H26" t="s">
-        <v>209</v>
-      </c>
-      <c r="I26" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H26" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D27" s="3">
         <v>625.58649200000002</v>
@@ -6027,22 +6755,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H27" t="s">
-        <v>209</v>
-      </c>
-      <c r="I27" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H27" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D28" s="3">
         <v>629.986492</v>
@@ -6058,22 +6783,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H28" t="s">
-        <v>209</v>
-      </c>
-      <c r="I28" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H28" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D29" s="3">
         <v>634.38649199999998</v>
@@ -6089,22 +6811,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H29" t="s">
-        <v>209</v>
-      </c>
-      <c r="I29" s="1">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H29" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D30" s="3">
         <v>638.78649199999995</v>
@@ -6120,22 +6839,19 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H30" t="s">
-        <v>209</v>
-      </c>
-      <c r="I30" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H30" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D31" s="3">
         <v>643.18649200000004</v>
@@ -6151,22 +6867,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H31" t="s">
-        <v>209</v>
-      </c>
-      <c r="I31" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H31" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D32" s="3">
         <v>647.58649200000002</v>
@@ -6182,22 +6895,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H32" t="s">
-        <v>209</v>
-      </c>
-      <c r="I32" s="1">
-        <v>46</v>
+      <c r="H32" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D33" s="3">
         <v>651.986492</v>
@@ -6213,22 +6923,19 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H33" t="s">
-        <v>209</v>
-      </c>
-      <c r="I33" s="1">
-        <v>47</v>
+      <c r="H33" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B34" s="1">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D34" s="3">
         <v>656.38649199999998</v>
@@ -6244,19 +6951,22 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H34" t="s">
-        <v>210</v>
+      <c r="H34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I34" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D35" s="3">
         <v>660.78649199999995</v>
@@ -6272,19 +6982,19 @@
         <f t="shared" si="1"/>
         <v>14.43569553805804</v>
       </c>
-      <c r="H35" t="s">
-        <v>210</v>
+      <c r="H35" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D36" s="3">
         <v>665.18649200000004</v>
@@ -6300,8 +7010,8 @@
         <f t="shared" si="1"/>
         <v>14.435695538057667</v>
       </c>
-      <c r="H36" t="s">
-        <v>210</v>
+      <c r="H36" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -6317,15 +7027,15 @@
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>56</v>
@@ -6342,16 +7052,22 @@
       <c r="G1" s="14" t="s">
         <v>26</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D2" s="3">
         <v>514.74000100000001</v>
@@ -6367,22 +7083,19 @@
         <f t="shared" ref="G2:G4" si="1">F2/0.3048</f>
         <v>14.329560367454153</v>
       </c>
-      <c r="H2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I2" s="1">
-        <v>13</v>
+      <c r="H2" s="1" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B3" s="1">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D3" s="3">
         <v>519.10765100000003</v>
@@ -6398,22 +7111,19 @@
         <f t="shared" si="1"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I3" s="1">
-        <v>14</v>
+      <c r="H3" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B4" s="1">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D4" s="3">
         <v>523.120318</v>
@@ -6429,22 +7139,19 @@
         <f t="shared" si="1"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H4" t="s">
-        <v>209</v>
-      </c>
-      <c r="I4" s="1">
-        <v>15</v>
+      <c r="H4" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B5" s="1">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D5" s="3">
         <v>527.13298499999996</v>
@@ -6460,22 +7167,19 @@
         <f>F5/0.3048</f>
         <v>13.164914698162995</v>
       </c>
-      <c r="H5" t="s">
-        <v>209</v>
-      </c>
-      <c r="I5" s="1">
-        <v>16</v>
+      <c r="H5" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B6" s="1">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D6" s="3">
         <v>531.14565100000004</v>
@@ -6491,22 +7195,19 @@
         <f t="shared" ref="G6:G39" si="3">F6/0.3048</f>
         <v>13.164917979002508</v>
       </c>
-      <c r="H6" t="s">
-        <v>209</v>
-      </c>
-      <c r="I6" s="1">
-        <v>17</v>
+      <c r="H6" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D7" s="3">
         <v>535.15831800000001</v>
@@ -6522,22 +7223,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H7" t="s">
-        <v>209</v>
-      </c>
-      <c r="I7" s="1">
-        <v>18</v>
+      <c r="H7" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B8" s="1">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D8" s="3">
         <v>539.17098499999997</v>
@@ -6553,22 +7251,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H8" t="s">
-        <v>209</v>
-      </c>
-      <c r="I8" s="1">
-        <v>19</v>
+      <c r="H8" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B9" s="1">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D9" s="3">
         <v>543.18365100000005</v>
@@ -6584,22 +7279,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H9" t="s">
-        <v>209</v>
-      </c>
-      <c r="I9" s="1">
-        <v>20</v>
+      <c r="H9" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B10" s="1">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D10" s="3">
         <v>547.19631800000002</v>
@@ -6615,20 +7307,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H10" t="s">
-        <v>377</v>
-      </c>
-      <c r="I10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D11" s="3">
         <v>551.20898499999998</v>
@@ -6644,22 +7335,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H11" t="s">
-        <v>209</v>
-      </c>
-      <c r="I11" s="1">
-        <v>22</v>
+      <c r="H11" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D12" s="3">
         <v>555.22165099999995</v>
@@ -6675,22 +7363,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H12" t="s">
-        <v>209</v>
-      </c>
-      <c r="I12" s="1">
-        <v>23</v>
+      <c r="H12" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D13" s="3">
         <v>559.23431800000003</v>
@@ -6706,22 +7391,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H13" t="s">
-        <v>209</v>
-      </c>
-      <c r="I13" s="1">
-        <v>24</v>
+      <c r="H13" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D14" s="3">
         <v>563.246985</v>
@@ -6737,22 +7419,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H14" t="s">
-        <v>209</v>
-      </c>
-      <c r="I14" s="1">
-        <v>25</v>
+      <c r="H14" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D15" s="3">
         <v>567.25965099999996</v>
@@ -6768,22 +7447,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H15" t="s">
-        <v>209</v>
-      </c>
-      <c r="I15" s="1">
-        <v>26</v>
+      <c r="H15" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D16" s="3">
         <v>571.27231800000004</v>
@@ -6799,22 +7475,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H16" t="s">
-        <v>209</v>
-      </c>
-      <c r="I16" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H16" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B17" s="1">
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D17" s="3">
         <v>575.28498500000001</v>
@@ -6830,20 +7503,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H17" t="s">
-        <v>378</v>
-      </c>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H17" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B18" s="1">
         <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D18" s="3">
         <v>579.29765099999997</v>
@@ -6859,22 +7531,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H18" t="s">
-        <v>209</v>
-      </c>
-      <c r="I18" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H18" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B19" s="1">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D19" s="3">
         <v>583.31031800000005</v>
@@ -6890,22 +7559,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H19" t="s">
-        <v>209</v>
-      </c>
-      <c r="I19" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H19" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B20" s="1">
         <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D20" s="3">
         <v>587.32298500000002</v>
@@ -6921,22 +7587,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H20" t="s">
-        <v>209</v>
-      </c>
-      <c r="I20" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H20" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D21" s="3">
         <v>591.33565099999998</v>
@@ -6952,22 +7615,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H21" t="s">
-        <v>209</v>
-      </c>
-      <c r="I21" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H21" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B22" s="1">
         <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D22" s="3">
         <v>595.34831799999995</v>
@@ -6983,22 +7643,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H22" t="s">
-        <v>209</v>
-      </c>
-      <c r="I22" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H22" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D23" s="3">
         <v>599.36098500000003</v>
@@ -7014,22 +7671,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H23" t="s">
-        <v>209</v>
-      </c>
-      <c r="I23" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H23" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B24" s="1">
         <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D24" s="3">
         <v>603.373651</v>
@@ -7045,22 +7699,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H24" t="s">
-        <v>209</v>
-      </c>
-      <c r="I24" s="1">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H24" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B25" s="1">
         <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D25" s="3">
         <v>607.38631799999996</v>
@@ -7076,22 +7727,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H25" t="s">
-        <v>209</v>
-      </c>
-      <c r="I25" s="1">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H25" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B26" s="1">
         <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D26" s="3">
         <v>611.39898500000004</v>
@@ -7107,22 +7755,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H26" t="s">
-        <v>209</v>
-      </c>
-      <c r="I26" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H26" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B27" s="1">
         <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D27" s="3">
         <v>615.41165100000001</v>
@@ -7138,22 +7783,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H27" t="s">
-        <v>209</v>
-      </c>
-      <c r="I27" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H27" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B28" s="1">
         <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D28" s="3">
         <v>619.42431799999997</v>
@@ -7169,22 +7811,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002881</v>
       </c>
-      <c r="H28" t="s">
-        <v>209</v>
-      </c>
-      <c r="I28" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H28" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B29" s="1">
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D29" s="3">
         <v>623.43698500000005</v>
@@ -7200,22 +7839,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162622</v>
       </c>
-      <c r="H29" t="s">
-        <v>209</v>
-      </c>
-      <c r="I29" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H29" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B30" s="1">
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D30" s="3">
         <v>627.44965100000002</v>
@@ -7231,22 +7867,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H30" t="s">
-        <v>209</v>
-      </c>
-      <c r="I30" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H30" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B31" s="1">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D31" s="3">
         <v>631.46231799999998</v>
@@ -7262,22 +7895,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H31" t="s">
-        <v>209</v>
-      </c>
-      <c r="I31" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H31" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B32" s="1">
         <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D32" s="3">
         <v>635.47498499999995</v>
@@ -7293,22 +7923,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H32" t="s">
-        <v>209</v>
-      </c>
-      <c r="I32" s="1">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H32" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B33" s="1">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D33" s="3">
         <v>639.48765100000003</v>
@@ -7324,22 +7951,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H33" t="s">
-        <v>209</v>
-      </c>
-      <c r="I33" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H33" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B34" s="1">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D34" s="3">
         <v>643.50031799999999</v>
@@ -7355,22 +7979,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H34" t="s">
-        <v>209</v>
-      </c>
-      <c r="I34" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H34" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B35" s="1">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D35" s="3">
         <v>647.51298499999996</v>
@@ -7386,22 +8007,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H35" t="s">
-        <v>209</v>
-      </c>
-      <c r="I35" s="1">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H35" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B36" s="1">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D36" s="3">
         <v>651.52565100000004</v>
@@ -7417,22 +8035,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H36" t="s">
-        <v>209</v>
-      </c>
-      <c r="I36" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H36" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B37" s="1">
         <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D37" s="3">
         <v>655.538318</v>
@@ -7448,19 +8063,19 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H37" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H37" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B38" s="1">
         <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D38" s="3">
         <v>659.55098499999997</v>
@@ -7476,19 +8091,19 @@
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H38" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H38" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B39" s="1">
         <v>10</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D39" s="3">
         <v>663.56365100000005</v>
@@ -7504,8 +8119,8 @@
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H39" t="s">
-        <v>210</v>
+      <c r="H39" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/python/scripts/oracle_upload/sectors.xlsx
+++ b/python/scripts/oracle_upload/sectors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AD_ACCEL\preRelease\RDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AD_ACCEL_HE\preRelease\RDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F8A872-AE4A-40F9-B9C8-F96991968D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFAD30A-4D35-45CE-B291-C8CD3AF4CF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="225" windowWidth="23190" windowHeight="20670" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25665" yWindow="2460" windowWidth="22710" windowHeight="16245" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scS" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="416">
   <si>
     <t>S00</t>
   </si>
@@ -171,18 +171,9 @@
 coordinates</t>
   </si>
   <si>
-    <t>BPN09</t>
-  </si>
-  <si>
     <t>BPN27</t>
   </si>
   <si>
-    <t>BPN10</t>
-  </si>
-  <si>
-    <t>BPN11</t>
-  </si>
-  <si>
     <t>BPN12</t>
   </si>
   <si>
@@ -246,955 +237,1063 @@
     <t>L3B</t>
   </si>
   <si>
-    <t>L3B/EXT/DOG</t>
-  </si>
-  <si>
     <t>areas</t>
   </si>
   <si>
+    <t>BYP/SPD1</t>
+  </si>
+  <si>
+    <t>SPD1/SPS</t>
+  </si>
+  <si>
+    <t>SLTS/BSYS</t>
+  </si>
+  <si>
+    <t>LTUS</t>
+  </si>
+  <si>
+    <t>SXR</t>
+  </si>
+  <si>
+    <t>UES/DMPS</t>
+  </si>
+  <si>
+    <t>DMPS</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>LTUH</t>
+  </si>
+  <si>
+    <t>DMPH</t>
+  </si>
+  <si>
+    <t>GUN1/GUN2/L0/HTR/EMIT/BX0</t>
+  </si>
+  <si>
+    <t>L2/BC2</t>
+  </si>
+  <si>
+    <t>L3/CLTH0</t>
+  </si>
+  <si>
+    <t>UEH/DMPH</t>
+  </si>
+  <si>
+    <t>71H</t>
+  </si>
+  <si>
+    <t>72H</t>
+  </si>
+  <si>
+    <t>73H</t>
+  </si>
+  <si>
+    <t>74H</t>
+  </si>
+  <si>
+    <t>75H</t>
+  </si>
+  <si>
+    <t>76H</t>
+  </si>
+  <si>
+    <t>77H</t>
+  </si>
+  <si>
+    <t>78H</t>
+  </si>
+  <si>
+    <t>79H</t>
+  </si>
+  <si>
+    <t>80H</t>
+  </si>
+  <si>
+    <t>81H</t>
+  </si>
+  <si>
+    <t>82H</t>
+  </si>
+  <si>
+    <t>90H</t>
+  </si>
+  <si>
+    <t>92H</t>
+  </si>
+  <si>
+    <t>71S</t>
+  </si>
+  <si>
+    <t>72S</t>
+  </si>
+  <si>
+    <t>73S</t>
+  </si>
+  <si>
+    <t>74S</t>
+  </si>
+  <si>
+    <t>75S</t>
+  </si>
+  <si>
+    <t>76S</t>
+  </si>
+  <si>
+    <t>77S</t>
+  </si>
+  <si>
+    <t>78S</t>
+  </si>
+  <si>
+    <t>79S</t>
+  </si>
+  <si>
+    <t>80S</t>
+  </si>
+  <si>
+    <t>81S</t>
+  </si>
+  <si>
+    <t>82S</t>
+  </si>
+  <si>
+    <t>90S</t>
+  </si>
+  <si>
+    <t>92S</t>
+  </si>
+  <si>
+    <t>U01S</t>
+  </si>
+  <si>
+    <t>U02S</t>
+  </si>
+  <si>
+    <t>U03S</t>
+  </si>
+  <si>
+    <t>U04S</t>
+  </si>
+  <si>
+    <t>U01H</t>
+  </si>
+  <si>
+    <t>U02H</t>
+  </si>
+  <si>
+    <t>U03H</t>
+  </si>
+  <si>
+    <t>U04H</t>
+  </si>
+  <si>
+    <t>91H</t>
+  </si>
+  <si>
+    <t>SFTH</t>
+  </si>
+  <si>
+    <t>HXTES</t>
+  </si>
+  <si>
+    <t>XTESH</t>
+  </si>
+  <si>
+    <t>froot</t>
+  </si>
+  <si>
+    <t>BSY?</t>
+  </si>
+  <si>
+    <t>91S</t>
+  </si>
+  <si>
+    <t>SFTS</t>
+  </si>
+  <si>
+    <t>XTESS</t>
+  </si>
+  <si>
+    <t>L0B/HTR/DIAG0/COL0/L1B</t>
+  </si>
+  <si>
+    <t>BPN13BEG</t>
+  </si>
+  <si>
+    <t>BPN14BEG</t>
+  </si>
+  <si>
+    <t>BPN15BEG</t>
+  </si>
+  <si>
+    <t>BPN16BEG</t>
+  </si>
+  <si>
+    <t>BPN17BEG</t>
+  </si>
+  <si>
+    <t>BPN18BEG</t>
+  </si>
+  <si>
+    <t>BPN19BEG</t>
+  </si>
+  <si>
+    <t>BPN20BEG</t>
+  </si>
+  <si>
+    <t>BPN21BEG</t>
+  </si>
+  <si>
+    <t>BPN22BEG</t>
+  </si>
+  <si>
+    <t>BPN23BEG</t>
+  </si>
+  <si>
+    <t>BPN24BEG</t>
+  </si>
+  <si>
+    <t>BPN25BEG</t>
+  </si>
+  <si>
+    <t>BPN26BEG</t>
+  </si>
+  <si>
+    <t>BPN27BEG</t>
+  </si>
+  <si>
+    <t>BPN12END</t>
+  </si>
+  <si>
+    <t>BPN13END</t>
+  </si>
+  <si>
+    <t>BPN14END</t>
+  </si>
+  <si>
+    <t>BPN15END</t>
+  </si>
+  <si>
+    <t>BPN16END</t>
+  </si>
+  <si>
+    <t>BPN17END</t>
+  </si>
+  <si>
+    <t>BPN18END</t>
+  </si>
+  <si>
+    <t>BPN19END</t>
+  </si>
+  <si>
+    <t>BPN20END</t>
+  </si>
+  <si>
+    <t>BPN21END</t>
+  </si>
+  <si>
+    <t>BPN22END</t>
+  </si>
+  <si>
+    <t>BPN23END</t>
+  </si>
+  <si>
+    <t>BPN24END</t>
+  </si>
+  <si>
+    <t>BPN25END</t>
+  </si>
+  <si>
+    <t>BPN26END</t>
+  </si>
+  <si>
+    <t>BPN27END</t>
+  </si>
+  <si>
+    <t>Nbegin</t>
+  </si>
+  <si>
+    <t>Nend</t>
+  </si>
+  <si>
+    <t>BEGGUNB</t>
+  </si>
+  <si>
+    <t>LI22BEG</t>
+  </si>
+  <si>
+    <t>LI22END</t>
+  </si>
+  <si>
+    <t>LI23BEG</t>
+  </si>
+  <si>
+    <t>LI24BEG</t>
+  </si>
+  <si>
+    <t>LI26BEG</t>
+  </si>
+  <si>
+    <t>LI27BEG</t>
+  </si>
+  <si>
+    <t>LI28BEG</t>
+  </si>
+  <si>
+    <t>LI29BEG</t>
+  </si>
+  <si>
+    <t>LI23END</t>
+  </si>
+  <si>
+    <t>LI25END</t>
+  </si>
+  <si>
+    <t>LI26END</t>
+  </si>
+  <si>
+    <t>LI27END</t>
+  </si>
+  <si>
+    <t>LI28END</t>
+  </si>
+  <si>
+    <t>LI29END</t>
+  </si>
+  <si>
+    <t>SXR cell 26</t>
+  </si>
+  <si>
+    <t>SXR cell 27</t>
+  </si>
+  <si>
+    <t>SXR cell 28</t>
+  </si>
+  <si>
+    <t>SXR cell 29</t>
+  </si>
+  <si>
+    <t>SXR cell 30</t>
+  </si>
+  <si>
+    <t>SXR cell 31</t>
+  </si>
+  <si>
+    <t>SXR cell 32</t>
+  </si>
+  <si>
+    <t>SXR cell 33</t>
+  </si>
+  <si>
+    <t>SXR cell 34</t>
+  </si>
+  <si>
+    <t>SXR cell 35</t>
+  </si>
+  <si>
+    <t>SXR cell 36</t>
+  </si>
+  <si>
+    <t>SXR cell 37</t>
+  </si>
+  <si>
+    <t>SXR cell 38</t>
+  </si>
+  <si>
+    <t>SXR cell 39</t>
+  </si>
+  <si>
+    <t>SXR cell 40</t>
+  </si>
+  <si>
+    <t>SXR cell 41</t>
+  </si>
+  <si>
+    <t>SXR cell 42</t>
+  </si>
+  <si>
+    <t>SXR cell 43</t>
+  </si>
+  <si>
+    <t>SXR cell 44</t>
+  </si>
+  <si>
+    <t>SXR cell 45</t>
+  </si>
+  <si>
+    <t>SXR cell 46</t>
+  </si>
+  <si>
+    <t>SXR cell 47</t>
+  </si>
+  <si>
+    <t>SXR cell 48</t>
+  </si>
+  <si>
+    <t>SXR cell 49</t>
+  </si>
+  <si>
+    <t>SXR cell 50</t>
+  </si>
+  <si>
+    <t>undulator</t>
+  </si>
+  <si>
+    <t>future</t>
+  </si>
+  <si>
+    <t>HXR cell 16</t>
+  </si>
+  <si>
+    <t>HXR cell 17</t>
+  </si>
+  <si>
+    <t>HXR cell 18</t>
+  </si>
+  <si>
+    <t>HXR cell 19</t>
+  </si>
+  <si>
+    <t>HXR cell 20</t>
+  </si>
+  <si>
+    <t>HXR cell 21</t>
+  </si>
+  <si>
+    <t>HXR cell 22</t>
+  </si>
+  <si>
+    <t>HXR cell 23</t>
+  </si>
+  <si>
+    <t>HXR cell 24</t>
+  </si>
+  <si>
+    <t>HXR cell 25</t>
+  </si>
+  <si>
+    <t>HXR cell 26</t>
+  </si>
+  <si>
+    <t>HXR cell 27</t>
+  </si>
+  <si>
+    <t>HXR cell 28</t>
+  </si>
+  <si>
+    <t>HXR cell 29</t>
+  </si>
+  <si>
+    <t>HXR cell 30</t>
+  </si>
+  <si>
+    <t>HXR cell 31</t>
+  </si>
+  <si>
+    <t>HXR cell 32</t>
+  </si>
+  <si>
+    <t>HXR cell 33</t>
+  </si>
+  <si>
+    <t>HXR cell 34</t>
+  </si>
+  <si>
+    <t>HXR cell 35</t>
+  </si>
+  <si>
+    <t>HXR cell 36</t>
+  </si>
+  <si>
+    <t>HXR cell 37</t>
+  </si>
+  <si>
+    <t>HXR cell 38</t>
+  </si>
+  <si>
+    <t>HXR cell 39</t>
+  </si>
+  <si>
+    <t>HXR cell 40</t>
+  </si>
+  <si>
+    <t>HXR cell 41</t>
+  </si>
+  <si>
+    <t>HXR cell 42</t>
+  </si>
+  <si>
+    <t>HXR cell 43</t>
+  </si>
+  <si>
+    <t>HXR cell 44</t>
+  </si>
+  <si>
+    <t>HXR cell 45</t>
+  </si>
+  <si>
+    <t>HXR cell 46</t>
+  </si>
+  <si>
+    <t>HXR cell 47</t>
+  </si>
+  <si>
+    <t>HXR cell 48</t>
+  </si>
+  <si>
+    <t>HXR cell 49</t>
+  </si>
+  <si>
+    <t>HXR cell 50</t>
+  </si>
+  <si>
+    <t>HXR cell 13</t>
+  </si>
+  <si>
+    <t>HXR cell 14</t>
+  </si>
+  <si>
+    <t>HXR cell 15</t>
+  </si>
+  <si>
+    <t>Undulator Cell</t>
+  </si>
+  <si>
+    <t>HXR 13</t>
+  </si>
+  <si>
+    <t>HXR 14</t>
+  </si>
+  <si>
+    <t>HXR 15</t>
+  </si>
+  <si>
+    <t>HXR 16</t>
+  </si>
+  <si>
+    <t>HXR 17</t>
+  </si>
+  <si>
+    <t>HXR 18</t>
+  </si>
+  <si>
+    <t>HXR 19</t>
+  </si>
+  <si>
+    <t>HXR 20</t>
+  </si>
+  <si>
+    <t>HXR 21</t>
+  </si>
+  <si>
+    <t>HXR 22</t>
+  </si>
+  <si>
+    <t>HXR 23</t>
+  </si>
+  <si>
+    <t>HXR 24</t>
+  </si>
+  <si>
+    <t>HXR 25</t>
+  </si>
+  <si>
+    <t>HXR 26</t>
+  </si>
+  <si>
+    <t>HXR 27</t>
+  </si>
+  <si>
+    <t>HXR 28</t>
+  </si>
+  <si>
+    <t>HXR 29</t>
+  </si>
+  <si>
+    <t>HXR 30</t>
+  </si>
+  <si>
+    <t>HXR 31</t>
+  </si>
+  <si>
+    <t>HXR 32</t>
+  </si>
+  <si>
+    <t>HXR 33</t>
+  </si>
+  <si>
+    <t>HXR 34</t>
+  </si>
+  <si>
+    <t>HXR 35</t>
+  </si>
+  <si>
+    <t>HXR 36</t>
+  </si>
+  <si>
+    <t>HXR 37</t>
+  </si>
+  <si>
+    <t>HXR 38</t>
+  </si>
+  <si>
+    <t>HXR 39</t>
+  </si>
+  <si>
+    <t>HXR 40</t>
+  </si>
+  <si>
+    <t>HXR 41</t>
+  </si>
+  <si>
+    <t>HXR 42</t>
+  </si>
+  <si>
+    <t>HXR 43</t>
+  </si>
+  <si>
+    <t>HXR 44</t>
+  </si>
+  <si>
+    <t>HXR 45</t>
+  </si>
+  <si>
+    <t>HXR 46</t>
+  </si>
+  <si>
+    <t>HXR 47</t>
+  </si>
+  <si>
+    <t>HXR 48</t>
+  </si>
+  <si>
+    <t>HXR 49</t>
+  </si>
+  <si>
+    <t>HXR 50</t>
+  </si>
+  <si>
+    <t>SXR 16</t>
+  </si>
+  <si>
+    <t>SXR 17</t>
+  </si>
+  <si>
+    <t>SXR 18</t>
+  </si>
+  <si>
+    <t>SXR 19</t>
+  </si>
+  <si>
+    <t>SXR 20</t>
+  </si>
+  <si>
+    <t>SXR 21</t>
+  </si>
+  <si>
+    <t>SXR 23</t>
+  </si>
+  <si>
+    <t>SXR 24</t>
+  </si>
+  <si>
+    <t>SXR 25</t>
+  </si>
+  <si>
+    <t>SXR 26</t>
+  </si>
+  <si>
+    <t>SXR 27</t>
+  </si>
+  <si>
+    <t>SXR 28</t>
+  </si>
+  <si>
+    <t>SXR 29</t>
+  </si>
+  <si>
+    <t>SXR 22</t>
+  </si>
+  <si>
+    <t>SXR 30</t>
+  </si>
+  <si>
+    <t>SXR 31</t>
+  </si>
+  <si>
+    <t>SXR 32</t>
+  </si>
+  <si>
+    <t>SXR 34</t>
+  </si>
+  <si>
+    <t>SXR 35</t>
+  </si>
+  <si>
+    <t>SXR 36</t>
+  </si>
+  <si>
+    <t>SXR 37</t>
+  </si>
+  <si>
+    <t>SXR 38</t>
+  </si>
+  <si>
+    <t>SXR 39</t>
+  </si>
+  <si>
+    <t>SXR 33</t>
+  </si>
+  <si>
+    <t>SXR 40</t>
+  </si>
+  <si>
+    <t>SXR 41</t>
+  </si>
+  <si>
+    <t>SXR 42</t>
+  </si>
+  <si>
+    <t>SXR 43</t>
+  </si>
+  <si>
+    <t>SXR 45</t>
+  </si>
+  <si>
+    <t>SXR 46</t>
+  </si>
+  <si>
+    <t>SXR 47</t>
+  </si>
+  <si>
+    <t>SXR 48</t>
+  </si>
+  <si>
+    <t>SXR 49</t>
+  </si>
+  <si>
+    <t>SXR 44</t>
+  </si>
+  <si>
+    <t>SXR 50</t>
+  </si>
+  <si>
+    <t>ENDSPS</t>
+  </si>
+  <si>
+    <t>BEGSLTS</t>
+  </si>
+  <si>
+    <t>ENDBSYS</t>
+  </si>
+  <si>
+    <t>BEGLTUS</t>
+  </si>
+  <si>
+    <t>BEGLTUH</t>
+  </si>
+  <si>
+    <t>ALINE</t>
+  </si>
+  <si>
+    <t>LI21END</t>
+  </si>
+  <si>
+    <t>L1/BC1/L2</t>
+  </si>
+  <si>
+    <t>LI30BEG</t>
+  </si>
+  <si>
+    <t>ENDLTUH</t>
+  </si>
+  <si>
+    <t>ENDLTUS</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>CLTH/BSYH1/BSYH2</t>
+  </si>
+  <si>
+    <t>BEGL1</t>
+  </si>
+  <si>
+    <t>ENDBC2</t>
+  </si>
+  <si>
+    <t>BEGGUN</t>
+  </si>
+  <si>
+    <t>BEGUNDS</t>
+  </si>
+  <si>
+    <t>ENDUNDS</t>
+  </si>
+  <si>
+    <t>BEGDMPS_1</t>
+  </si>
+  <si>
+    <t>ENDDMPS_1</t>
+  </si>
+  <si>
+    <t>BEGDMPS_2</t>
+  </si>
+  <si>
+    <t>ENDDMPS_2</t>
+  </si>
+  <si>
+    <t>BEGSFTS_1</t>
+  </si>
+  <si>
+    <t>ENDSFTS_2</t>
+  </si>
+  <si>
+    <t>ENDDL1_2</t>
+  </si>
+  <si>
+    <t>ENDCLTH_0</t>
+  </si>
+  <si>
+    <t>BEGCLTH_1</t>
+  </si>
+  <si>
+    <t>ENDUNDH</t>
+  </si>
+  <si>
+    <t>BEGUNDH</t>
+  </si>
+  <si>
+    <t>BEGDMPH_1</t>
+  </si>
+  <si>
+    <t>ENDDMPH_1</t>
+  </si>
+  <si>
+    <t>BEGDMPH_2</t>
+  </si>
+  <si>
+    <t>ENDDMPH_2</t>
+  </si>
+  <si>
+    <t>BEGSFTH_1</t>
+  </si>
+  <si>
+    <t>ENDSFTH_2</t>
+  </si>
+  <si>
+    <t>BEGL3</t>
+  </si>
+  <si>
+    <t>BEGHXTES_1</t>
+  </si>
+  <si>
+    <t>ENDHXTES_2</t>
+  </si>
+  <si>
+    <t>HTXI</t>
+  </si>
+  <si>
+    <t>BEGHXTES_3</t>
+  </si>
+  <si>
+    <t>ENDHXTES_3</t>
+  </si>
+  <si>
+    <t>S2_X</t>
+  </si>
+  <si>
+    <t>BEGSXTES_1</t>
+  </si>
+  <si>
+    <t>ENDSXTES_2</t>
+  </si>
+  <si>
+    <t>BEGSXTES_3</t>
+  </si>
+  <si>
+    <t>BEGSXTES_4</t>
+  </si>
+  <si>
+    <t>ENDSXTES_4</t>
+  </si>
+  <si>
+    <t>STXI</t>
+  </si>
+  <si>
+    <t>STMO</t>
+  </si>
+  <si>
+    <t>ENDSXTES_3</t>
+  </si>
+  <si>
+    <t>L4B</t>
+  </si>
+  <si>
+    <t>S09</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>9 cells</t>
+  </si>
+  <si>
+    <t>8 cells</t>
+  </si>
+  <si>
+    <t>PREUNDH,HXR</t>
+  </si>
+  <si>
+    <t>11 cells</t>
+  </si>
+  <si>
+    <t>Sector boundaries from "Beamline Boundaries" PRD (LCLSII-HE-1.3-PR-0028-R0)</t>
+  </si>
+  <si>
+    <t>SXR cell 17</t>
+  </si>
+  <si>
+    <t>SXR cell 18</t>
+  </si>
+  <si>
+    <t>SXR cell 19</t>
+  </si>
+  <si>
+    <t>SXR cell 20</t>
+  </si>
+  <si>
+    <t>SXR cell 21</t>
+  </si>
+  <si>
+    <t>SXR cell 22</t>
+  </si>
+  <si>
+    <t>SXR cell 23</t>
+  </si>
+  <si>
+    <t>SXR cell 24</t>
+  </si>
+  <si>
+    <t>SXR cell 25</t>
+  </si>
+  <si>
+    <t>PREUNDH</t>
+  </si>
+  <si>
+    <t>L3B/BR3B/L4B</t>
+  </si>
+  <si>
+    <t>L4B/EXT/DOG</t>
+  </si>
+  <si>
     <t>DOG</t>
   </si>
   <si>
-    <t>BYP/SPD1</t>
-  </si>
-  <si>
-    <t>SPD1/SPS</t>
-  </si>
-  <si>
-    <t>SLTS/BSYS</t>
-  </si>
-  <si>
-    <t>LTUS</t>
-  </si>
-  <si>
-    <t>SXR</t>
-  </si>
-  <si>
-    <t>UES/DMPS</t>
-  </si>
-  <si>
-    <t>DMPS</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>L3</t>
-  </si>
-  <si>
-    <t>LTUH</t>
-  </si>
-  <si>
-    <t>DMPH</t>
-  </si>
-  <si>
-    <t>L2/BC2</t>
-  </si>
-  <si>
-    <t>L3/CLTH0</t>
-  </si>
-  <si>
-    <t>UEH/DMPH</t>
-  </si>
-  <si>
-    <t>71H</t>
-  </si>
-  <si>
-    <t>72H</t>
-  </si>
-  <si>
-    <t>73H</t>
-  </si>
-  <si>
-    <t>74H</t>
-  </si>
-  <si>
-    <t>75H</t>
-  </si>
-  <si>
-    <t>76H</t>
-  </si>
-  <si>
-    <t>77H</t>
-  </si>
-  <si>
-    <t>78H</t>
-  </si>
-  <si>
-    <t>79H</t>
-  </si>
-  <si>
-    <t>80H</t>
-  </si>
-  <si>
-    <t>81H</t>
-  </si>
-  <si>
-    <t>82H</t>
-  </si>
-  <si>
-    <t>90H</t>
-  </si>
-  <si>
-    <t>92H</t>
-  </si>
-  <si>
-    <t>71S</t>
-  </si>
-  <si>
-    <t>72S</t>
-  </si>
-  <si>
-    <t>73S</t>
-  </si>
-  <si>
-    <t>74S</t>
-  </si>
-  <si>
-    <t>75S</t>
-  </si>
-  <si>
-    <t>76S</t>
-  </si>
-  <si>
-    <t>77S</t>
-  </si>
-  <si>
-    <t>78S</t>
-  </si>
-  <si>
-    <t>79S</t>
-  </si>
-  <si>
-    <t>80S</t>
-  </si>
-  <si>
-    <t>81S</t>
-  </si>
-  <si>
-    <t>82S</t>
-  </si>
-  <si>
-    <t>90S</t>
-  </si>
-  <si>
-    <t>92S</t>
-  </si>
-  <si>
-    <t>U01S</t>
-  </si>
-  <si>
-    <t>U02S</t>
-  </si>
-  <si>
-    <t>U03S</t>
-  </si>
-  <si>
-    <t>U04S</t>
-  </si>
-  <si>
-    <t>U01H</t>
-  </si>
-  <si>
-    <t>U02H</t>
-  </si>
-  <si>
-    <t>U03H</t>
-  </si>
-  <si>
-    <t>U04H</t>
-  </si>
-  <si>
-    <t>91H</t>
-  </si>
-  <si>
-    <t>SFTH</t>
-  </si>
-  <si>
-    <t>HXTES</t>
-  </si>
-  <si>
-    <t>XTESH</t>
-  </si>
-  <si>
-    <t>froot</t>
-  </si>
-  <si>
-    <t>BSY?</t>
-  </si>
-  <si>
-    <t>91S</t>
-  </si>
-  <si>
-    <t>SFTS</t>
-  </si>
-  <si>
-    <t>XTESS</t>
-  </si>
-  <si>
-    <t>L0B/HTR/DIAG0/COL0/L1B</t>
-  </si>
-  <si>
-    <t>BPN09BEG</t>
-  </si>
-  <si>
-    <t>BPN09END</t>
-  </si>
-  <si>
-    <t>BPN10BEG</t>
-  </si>
-  <si>
-    <t>BPN10END</t>
-  </si>
-  <si>
-    <t>BPN11BEG</t>
-  </si>
-  <si>
-    <t>BPN11END</t>
-  </si>
-  <si>
-    <t>BPN12BEG</t>
-  </si>
-  <si>
-    <t>BPN13BEG</t>
-  </si>
-  <si>
-    <t>BPN14BEG</t>
-  </si>
-  <si>
-    <t>BPN15BEG</t>
-  </si>
-  <si>
-    <t>BPN16BEG</t>
-  </si>
-  <si>
-    <t>BPN17BEG</t>
-  </si>
-  <si>
-    <t>BPN18BEG</t>
-  </si>
-  <si>
-    <t>BPN19BEG</t>
-  </si>
-  <si>
-    <t>BPN20BEG</t>
-  </si>
-  <si>
-    <t>BPN21BEG</t>
-  </si>
-  <si>
-    <t>BPN22BEG</t>
-  </si>
-  <si>
-    <t>BPN23BEG</t>
-  </si>
-  <si>
-    <t>BPN24BEG</t>
-  </si>
-  <si>
-    <t>BPN25BEG</t>
-  </si>
-  <si>
-    <t>BPN26BEG</t>
-  </si>
-  <si>
-    <t>BPN27BEG</t>
-  </si>
-  <si>
-    <t>BPN12END</t>
-  </si>
-  <si>
-    <t>BPN13END</t>
-  </si>
-  <si>
-    <t>BPN14END</t>
-  </si>
-  <si>
-    <t>BPN15END</t>
-  </si>
-  <si>
-    <t>BPN16END</t>
-  </si>
-  <si>
-    <t>BPN17END</t>
-  </si>
-  <si>
-    <t>BPN18END</t>
-  </si>
-  <si>
-    <t>BPN19END</t>
-  </si>
-  <si>
-    <t>BPN20END</t>
-  </si>
-  <si>
-    <t>BPN21END</t>
-  </si>
-  <si>
-    <t>BPN22END</t>
-  </si>
-  <si>
-    <t>BPN23END</t>
-  </si>
-  <si>
-    <t>BPN24END</t>
-  </si>
-  <si>
-    <t>BPN25END</t>
-  </si>
-  <si>
-    <t>BPN26END</t>
-  </si>
-  <si>
-    <t>BPN27END</t>
-  </si>
-  <si>
-    <t>Nbegin</t>
-  </si>
-  <si>
-    <t>Nend</t>
-  </si>
-  <si>
-    <t>BEGGUNB</t>
-  </si>
-  <si>
-    <t>LI22BEG</t>
-  </si>
-  <si>
-    <t>LI22END</t>
-  </si>
-  <si>
-    <t>LI23BEG</t>
-  </si>
-  <si>
-    <t>LI24BEG</t>
-  </si>
-  <si>
-    <t>LI26BEG</t>
-  </si>
-  <si>
-    <t>LI27BEG</t>
-  </si>
-  <si>
-    <t>LI28BEG</t>
-  </si>
-  <si>
-    <t>LI29BEG</t>
-  </si>
-  <si>
-    <t>LI23END</t>
-  </si>
-  <si>
-    <t>LI25END</t>
-  </si>
-  <si>
-    <t>LI26END</t>
-  </si>
-  <si>
-    <t>LI27END</t>
-  </si>
-  <si>
-    <t>LI28END</t>
-  </si>
-  <si>
-    <t>LI29END</t>
-  </si>
-  <si>
-    <t>SXR cell 26</t>
-  </si>
-  <si>
-    <t>SXR cell 27</t>
-  </si>
-  <si>
-    <t>SXR cell 28</t>
-  </si>
-  <si>
-    <t>SXR cell 29</t>
-  </si>
-  <si>
-    <t>SXR cell 30</t>
-  </si>
-  <si>
-    <t>SXR cell 31</t>
-  </si>
-  <si>
-    <t>SXR cell 32</t>
-  </si>
-  <si>
-    <t>SXR cell 33</t>
-  </si>
-  <si>
-    <t>SXR cell 34</t>
-  </si>
-  <si>
-    <t>SXR cell 35</t>
-  </si>
-  <si>
-    <t>SXR cell 36</t>
-  </si>
-  <si>
-    <t>SXR cell 37</t>
-  </si>
-  <si>
-    <t>SXR cell 38</t>
-  </si>
-  <si>
-    <t>SXR cell 39</t>
-  </si>
-  <si>
-    <t>SXR cell 40</t>
-  </si>
-  <si>
-    <t>SXR cell 41</t>
-  </si>
-  <si>
-    <t>SXR cell 42</t>
-  </si>
-  <si>
-    <t>SXR cell 43</t>
-  </si>
-  <si>
-    <t>SXR cell 44</t>
-  </si>
-  <si>
-    <t>SXR cell 45</t>
-  </si>
-  <si>
-    <t>SXR cell 46</t>
-  </si>
-  <si>
-    <t>SXR cell 47</t>
-  </si>
-  <si>
-    <t>SXR cell 48</t>
-  </si>
-  <si>
-    <t>SXR cell 49</t>
-  </si>
-  <si>
-    <t>SXR cell 50</t>
+    <t>CLTS</t>
+  </si>
+  <si>
+    <t>BEGCLTS</t>
+  </si>
+  <si>
+    <t>ENDCLTS</t>
+  </si>
+  <si>
+    <t>overlay</t>
+  </si>
+  <si>
+    <t>GSPEC</t>
+  </si>
+  <si>
+    <t>BEGGSPEC</t>
+  </si>
+  <si>
+    <t>ENDGSPEC</t>
+  </si>
+  <si>
+    <t>SPEC</t>
+  </si>
+  <si>
+    <t>BEGSPEC</t>
+  </si>
+  <si>
+    <t>ENDSPEC</t>
+  </si>
+  <si>
+    <t>ENDBSYH</t>
+  </si>
+  <si>
+    <t>ESA</t>
+  </si>
+  <si>
+    <t>ENDBSYA</t>
+  </si>
+  <si>
+    <t>ENDESA</t>
+  </si>
+  <si>
+    <t>BEGBSYA</t>
+  </si>
+  <si>
+    <t>BYP/SPH</t>
+  </si>
+  <si>
+    <t>SPH</t>
+  </si>
+  <si>
+    <t>SPD1/SPD2/SPD3</t>
+  </si>
+  <si>
+    <t>SPD1/SPD2/SPA</t>
+  </si>
+  <si>
+    <t>SPD3</t>
+  </si>
+  <si>
+    <t>SPA</t>
+  </si>
+  <si>
+    <t>SLTH/BSYH</t>
+  </si>
+  <si>
+    <t>SLTD</t>
+  </si>
+  <si>
+    <t>SLTA</t>
+  </si>
+  <si>
+    <t>ENDSLTA</t>
   </si>
   <si>
     <t>SXX cell 16</t>
   </si>
   <si>
-    <t>SXX cell 25</t>
-  </si>
-  <si>
-    <t>SXX cell 17</t>
-  </si>
-  <si>
-    <t>SXX cell 18</t>
-  </si>
-  <si>
-    <t>SXX cell 19</t>
-  </si>
-  <si>
-    <t>SXX cell 20</t>
-  </si>
-  <si>
-    <t>SXX cell 21</t>
-  </si>
-  <si>
-    <t>SXX cell 22</t>
-  </si>
-  <si>
-    <t>SXX cell 23</t>
-  </si>
-  <si>
-    <t>SXX cell 24</t>
-  </si>
-  <si>
-    <t>undulator</t>
-  </si>
-  <si>
-    <t>future</t>
-  </si>
-  <si>
-    <t>HXR cell 16</t>
-  </si>
-  <si>
-    <t>HXR cell 17</t>
-  </si>
-  <si>
-    <t>HXR cell 18</t>
-  </si>
-  <si>
-    <t>HXR cell 19</t>
-  </si>
-  <si>
-    <t>HXR cell 20</t>
-  </si>
-  <si>
-    <t>HXR cell 21</t>
-  </si>
-  <si>
-    <t>HXR cell 22</t>
-  </si>
-  <si>
-    <t>HXR cell 23</t>
-  </si>
-  <si>
-    <t>HXR cell 24</t>
-  </si>
-  <si>
-    <t>HXR cell 25</t>
-  </si>
-  <si>
-    <t>HXR cell 26</t>
-  </si>
-  <si>
-    <t>HXR cell 27</t>
-  </si>
-  <si>
-    <t>HXR cell 28</t>
-  </si>
-  <si>
-    <t>HXR cell 29</t>
-  </si>
-  <si>
-    <t>HXR cell 30</t>
-  </si>
-  <si>
-    <t>HXR cell 31</t>
-  </si>
-  <si>
-    <t>HXR cell 32</t>
-  </si>
-  <si>
-    <t>HXR cell 33</t>
-  </si>
-  <si>
-    <t>HXR cell 34</t>
-  </si>
-  <si>
-    <t>HXR cell 35</t>
-  </si>
-  <si>
-    <t>HXR cell 36</t>
-  </si>
-  <si>
-    <t>HXR cell 37</t>
-  </si>
-  <si>
-    <t>HXR cell 38</t>
-  </si>
-  <si>
-    <t>HXR cell 39</t>
-  </si>
-  <si>
-    <t>HXR cell 40</t>
-  </si>
-  <si>
-    <t>HXR cell 41</t>
-  </si>
-  <si>
-    <t>HXR cell 42</t>
-  </si>
-  <si>
-    <t>HXR cell 43</t>
-  </si>
-  <si>
-    <t>HXR cell 44</t>
-  </si>
-  <si>
-    <t>HXR cell 45</t>
-  </si>
-  <si>
-    <t>HXR cell 46</t>
-  </si>
-  <si>
-    <t>HXR cell 47</t>
-  </si>
-  <si>
-    <t>HXR cell 48</t>
-  </si>
-  <si>
-    <t>HXR cell 49</t>
-  </si>
-  <si>
-    <t>HXR cell 50</t>
-  </si>
-  <si>
-    <t>HXR cell 13</t>
-  </si>
-  <si>
-    <t>HXR cell 14</t>
-  </si>
-  <si>
-    <t>HXR cell 15</t>
-  </si>
-  <si>
-    <t>Undulator Cell</t>
-  </si>
-  <si>
-    <t>HXR 13</t>
-  </si>
-  <si>
-    <t>HXR 14</t>
-  </si>
-  <si>
-    <t>HXR 15</t>
-  </si>
-  <si>
-    <t>HXR 16</t>
-  </si>
-  <si>
-    <t>HXR 17</t>
-  </si>
-  <si>
-    <t>HXR 18</t>
-  </si>
-  <si>
-    <t>HXR 19</t>
-  </si>
-  <si>
-    <t>HXR 20</t>
-  </si>
-  <si>
-    <t>HXR 21</t>
-  </si>
-  <si>
-    <t>HXR 22</t>
-  </si>
-  <si>
-    <t>HXR 23</t>
-  </si>
-  <si>
-    <t>HXR 24</t>
-  </si>
-  <si>
-    <t>HXR 25</t>
-  </si>
-  <si>
-    <t>HXR 26</t>
-  </si>
-  <si>
-    <t>HXR 27</t>
-  </si>
-  <si>
-    <t>HXR 28</t>
-  </si>
-  <si>
-    <t>HXR 29</t>
-  </si>
-  <si>
-    <t>HXR 30</t>
-  </si>
-  <si>
-    <t>HXR 31</t>
-  </si>
-  <si>
-    <t>HXR 32</t>
-  </si>
-  <si>
-    <t>HXR 33</t>
-  </si>
-  <si>
-    <t>HXR 34</t>
-  </si>
-  <si>
-    <t>HXR 35</t>
-  </si>
-  <si>
-    <t>HXR 36</t>
-  </si>
-  <si>
-    <t>HXR 37</t>
-  </si>
-  <si>
-    <t>HXR 38</t>
-  </si>
-  <si>
-    <t>HXR 39</t>
-  </si>
-  <si>
-    <t>HXR 40</t>
-  </si>
-  <si>
-    <t>HXR 41</t>
-  </si>
-  <si>
-    <t>HXR 42</t>
-  </si>
-  <si>
-    <t>HXR 43</t>
-  </si>
-  <si>
-    <t>HXR 44</t>
-  </si>
-  <si>
-    <t>HXR 45</t>
-  </si>
-  <si>
-    <t>HXR 46</t>
-  </si>
-  <si>
-    <t>HXR 47</t>
-  </si>
-  <si>
-    <t>HXR 48</t>
-  </si>
-  <si>
-    <t>HXR 49</t>
-  </si>
-  <si>
-    <t>HXR 50</t>
-  </si>
-  <si>
-    <t>SXR 16</t>
-  </si>
-  <si>
-    <t>SXR 17</t>
-  </si>
-  <si>
-    <t>SXR 18</t>
-  </si>
-  <si>
-    <t>SXR 19</t>
-  </si>
-  <si>
-    <t>SXR 20</t>
-  </si>
-  <si>
-    <t>SXR 21</t>
-  </si>
-  <si>
-    <t>SXR 23</t>
-  </si>
-  <si>
-    <t>SXR 24</t>
-  </si>
-  <si>
-    <t>SXR 25</t>
-  </si>
-  <si>
-    <t>SXR 26</t>
-  </si>
-  <si>
-    <t>SXR 27</t>
-  </si>
-  <si>
-    <t>SXR 28</t>
-  </si>
-  <si>
-    <t>SXR 29</t>
-  </si>
-  <si>
-    <t>SXR 22</t>
-  </si>
-  <si>
-    <t>SXR 30</t>
-  </si>
-  <si>
-    <t>SXR 31</t>
-  </si>
-  <si>
-    <t>SXR 32</t>
-  </si>
-  <si>
-    <t>SXR 34</t>
-  </si>
-  <si>
-    <t>SXR 35</t>
-  </si>
-  <si>
-    <t>SXR 36</t>
-  </si>
-  <si>
-    <t>SXR 37</t>
-  </si>
-  <si>
-    <t>SXR 38</t>
-  </si>
-  <si>
-    <t>SXR 39</t>
-  </si>
-  <si>
-    <t>SXR 33</t>
-  </si>
-  <si>
-    <t>SXR 40</t>
-  </si>
-  <si>
-    <t>SXR 41</t>
-  </si>
-  <si>
-    <t>SXR 42</t>
-  </si>
-  <si>
-    <t>SXR 43</t>
-  </si>
-  <si>
-    <t>SXR 45</t>
-  </si>
-  <si>
-    <t>SXR 46</t>
-  </si>
-  <si>
-    <t>SXR 47</t>
-  </si>
-  <si>
-    <t>SXR 48</t>
-  </si>
-  <si>
-    <t>SXR 49</t>
-  </si>
-  <si>
-    <t>SXR 44</t>
-  </si>
-  <si>
-    <t>SXR 50</t>
-  </si>
-  <si>
-    <t>ENDSPS</t>
-  </si>
-  <si>
-    <t>BEGSLTS</t>
-  </si>
-  <si>
-    <t>ENDBSYS</t>
-  </si>
-  <si>
-    <t>BEGLTUS</t>
-  </si>
-  <si>
-    <t>BEGLTUH</t>
-  </si>
-  <si>
-    <t>ALINE</t>
-  </si>
-  <si>
-    <t>LI21END</t>
-  </si>
-  <si>
-    <t>L1/BC1/L2</t>
-  </si>
-  <si>
-    <t>LI30BEG</t>
-  </si>
-  <si>
-    <t>ENDLTUH</t>
-  </si>
-  <si>
-    <t>ENDLTUS</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>BEGL1</t>
-  </si>
-  <si>
-    <t>ENDBC2</t>
-  </si>
-  <si>
-    <t>Sector boundaries from "Beamline Boundaries" PRD (LCLSII-2.1-PR-0134-R5)</t>
-  </si>
-  <si>
-    <t>BEGGUN</t>
-  </si>
-  <si>
-    <t>BEGUNDS</t>
-  </si>
-  <si>
-    <t>ENDUNDS</t>
-  </si>
-  <si>
-    <t>BEGDMPS_1</t>
-  </si>
-  <si>
-    <t>ENDDMPS_1</t>
-  </si>
-  <si>
-    <t>BEGDMPS_2</t>
-  </si>
-  <si>
-    <t>ENDDMPS_2</t>
-  </si>
-  <si>
-    <t>BEGSFTS_1</t>
-  </si>
-  <si>
-    <t>ENDSFTS_2</t>
-  </si>
-  <si>
-    <t>ENDDL1_2</t>
-  </si>
-  <si>
-    <t>ENDCLTH_0</t>
-  </si>
-  <si>
-    <t>BEGCLTH_1</t>
-  </si>
-  <si>
-    <t>ENDUNDH</t>
-  </si>
-  <si>
-    <t>BEGUNDH</t>
-  </si>
-  <si>
-    <t>BEGDMPH_1</t>
-  </si>
-  <si>
-    <t>ENDDMPH_1</t>
-  </si>
-  <si>
-    <t>BEGDMPH_2</t>
-  </si>
-  <si>
-    <t>ENDDMPH_2</t>
-  </si>
-  <si>
-    <t>BEGSFTH_1</t>
-  </si>
-  <si>
-    <t>ENDSFTH_2</t>
-  </si>
-  <si>
-    <t>BEGL3</t>
-  </si>
-  <si>
-    <t>BEGHXTES_1</t>
-  </si>
-  <si>
-    <t>ENDHXTES_2</t>
-  </si>
-  <si>
-    <t>HTXI</t>
-  </si>
-  <si>
-    <t>BEGHXTES_3</t>
-  </si>
-  <si>
-    <t>ENDHXTES_3</t>
-  </si>
-  <si>
-    <t>S2_X</t>
-  </si>
-  <si>
-    <t>BEGSXTES_1</t>
-  </si>
-  <si>
-    <t>ENDSXTES_2</t>
-  </si>
-  <si>
-    <t>BEGSXTES_3</t>
-  </si>
-  <si>
-    <t>BEGSXTES_4</t>
-  </si>
-  <si>
-    <t>ENDSXTES_4</t>
-  </si>
-  <si>
-    <t>STXI</t>
-  </si>
-  <si>
-    <t>STMO</t>
-  </si>
-  <si>
-    <t>ENDSXTES_3</t>
+    <t>partial cell</t>
+  </si>
+  <si>
+    <t>contains</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>SXRSS chicane</t>
+  </si>
+  <si>
+    <t>Delta-II</t>
+  </si>
+  <si>
+    <t>CBXFEL chicane #1</t>
   </si>
   <si>
     <t>CBXFEL chicane #2</t>
@@ -1203,106 +1302,31 @@
     <t>HXRSS chicane</t>
   </si>
   <si>
-    <t>SXRSS chicane</t>
-  </si>
-  <si>
-    <t>ENDESA</t>
-  </si>
-  <si>
-    <t>ESA</t>
-  </si>
-  <si>
-    <t>ENDBSYA</t>
-  </si>
-  <si>
-    <t>CLTH/BSYH</t>
-  </si>
-  <si>
-    <t>ENDBSYH</t>
-  </si>
-  <si>
-    <t>partial cell</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>CBXFEL chicane #1</t>
-  </si>
-  <si>
-    <t>contains</t>
-  </si>
-  <si>
-    <t>Delta-II</t>
-  </si>
-  <si>
-    <t>overlay</t>
-  </si>
-  <si>
-    <t>SPH</t>
-  </si>
-  <si>
-    <t>SPA</t>
-  </si>
-  <si>
-    <t>SLTD</t>
-  </si>
-  <si>
-    <t>SLTA</t>
-  </si>
-  <si>
-    <t>BYP/SPH</t>
-  </si>
-  <si>
-    <t>SPD1/SPD2/SPD3</t>
-  </si>
-  <si>
-    <t>SPD3</t>
-  </si>
-  <si>
-    <t>SPD1/SPD2/SPA</t>
-  </si>
-  <si>
-    <t>ENDSLTA</t>
-  </si>
-  <si>
-    <t>SLTH/BSYH</t>
-  </si>
-  <si>
-    <t>BEGBSYA</t>
-  </si>
-  <si>
-    <t>BEGCLTS</t>
-  </si>
-  <si>
-    <t>ENDCLTS</t>
-  </si>
-  <si>
-    <t>CLTS</t>
-  </si>
-  <si>
-    <t>BSY coordinates</t>
-  </si>
-  <si>
-    <t>ENDGSPEC</t>
-  </si>
-  <si>
-    <t>GUN/L0/HTR/EMIT/BX0</t>
-  </si>
-  <si>
-    <t>SPEC</t>
-  </si>
-  <si>
-    <t>GSPEC</t>
-  </si>
-  <si>
-    <t>BEGGSPEC</t>
-  </si>
-  <si>
-    <t>BEGSPEC</t>
-  </si>
-  <si>
-    <t>ENDSPEC</t>
+    <t>GUNLEI/L0LEI/LEI1/LEI2</t>
+  </si>
+  <si>
+    <t>BEGGUNLEI</t>
+  </si>
+  <si>
+    <t>LEI2</t>
+  </si>
+  <si>
+    <t>ENDLEI_2</t>
+  </si>
+  <si>
+    <t>DIAGI1</t>
+  </si>
+  <si>
+    <t>BEGDIAGI_1</t>
+  </si>
+  <si>
+    <t>DIAGI1/DIAGI1</t>
+  </si>
+  <si>
+    <t>ENDDIAGI_2</t>
+  </si>
+  <si>
+    <t>BEGESA</t>
   </si>
 </sst>
 </file>
@@ -1423,7 +1447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1497,17 +1521,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1798,7 +1813,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S75"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1807,10 +1822,8 @@
     <col min="4" max="4" width="24.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="16.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" customWidth="1"/>
     <col min="12" max="12" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1841,13 +1854,13 @@
         <v>21</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>22</v>
@@ -1862,10 +1875,10 @@
         <v>26</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="K3" s="15"/>
     </row>
@@ -1880,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3">
         <v>-10.15</v>
@@ -1897,7 +1910,7 @@
         <v>33.300524934383205</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="K4" s="24" t="s">
         <v>28</v>
@@ -1917,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" ref="E5:E34" si="2">F4</f>
@@ -1951,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" si="2"/>
@@ -1985,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="2"/>
@@ -2019,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="2"/>
@@ -2053,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="2"/>
@@ -2087,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="2"/>
@@ -2121,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>370</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="2"/>
@@ -2155,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>351</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="2"/>
@@ -2180,7 +2193,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>30</v>
+        <v>352</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -2189,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>30</v>
+        <v>351</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="2"/>
@@ -2207,12 +2220,8 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>119</v>
-      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
       <c r="K13" s="24"/>
       <c r="L13" s="1">
         <v>10</v>
@@ -2220,7 +2229,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>32</v>
+        <v>353</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -2229,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>32</v>
+        <v>371</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="2"/>
@@ -2247,12 +2256,8 @@
         <f t="shared" si="4"/>
         <v>333.33333333333337</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
       <c r="K14" s="24"/>
       <c r="L14" s="1">
         <v>11</v>
@@ -2260,7 +2265,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>33</v>
+        <v>354</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
@@ -2269,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>33</v>
+        <v>372</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="2"/>
@@ -2287,12 +2292,8 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>123</v>
-      </c>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
       <c r="K15" s="24"/>
       <c r="L15" s="1">
         <v>12</v>
@@ -2300,7 +2301,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
@@ -2309,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" si="2"/>
@@ -2327,11 +2328,9 @@
         <f t="shared" si="4"/>
         <v>333.33333333333303</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>124</v>
-      </c>
+      <c r="I16" s="9"/>
       <c r="J16" s="9" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="K16" s="24"/>
       <c r="L16" s="1">
@@ -2340,7 +2339,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
@@ -2349,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" si="2"/>
@@ -2368,10 +2367,10 @@
         <v>333.33333333333377</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="K17" s="24"/>
       <c r="L17" s="1">
@@ -2380,7 +2379,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
@@ -2389,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="2"/>
@@ -2408,10 +2407,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="K18" s="24"/>
       <c r="L18" s="1">
@@ -2420,7 +2419,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
@@ -2429,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E19" s="3">
         <f t="shared" si="2"/>
@@ -2448,10 +2447,10 @@
         <v>333.33333333333377</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="K19" s="24"/>
       <c r="L19" s="1">
@@ -2460,7 +2459,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -2469,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="2"/>
@@ -2488,10 +2487,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="K20" s="24"/>
       <c r="L20" s="1">
@@ -2500,7 +2499,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
@@ -2509,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E21" s="3">
         <f t="shared" si="2"/>
@@ -2528,10 +2527,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="K21" s="24"/>
       <c r="L21" s="1">
@@ -2540,7 +2539,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
@@ -2549,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="2"/>
@@ -2568,10 +2567,10 @@
         <v>333.33333333333377</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="K22" s="24"/>
       <c r="L22" s="1">
@@ -2580,7 +2579,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
@@ -2589,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E23" s="3">
         <f t="shared" si="2"/>
@@ -2608,10 +2607,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="K23" s="24"/>
       <c r="L23" s="1">
@@ -2620,7 +2619,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
@@ -2629,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="2"/>
@@ -2648,10 +2647,10 @@
         <v>333.33333333333377</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="K24" s="24"/>
       <c r="L24" s="1">
@@ -2660,7 +2659,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
@@ -2669,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="2"/>
@@ -2688,10 +2687,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="K25" s="24"/>
       <c r="L25" s="1">
@@ -2700,7 +2699,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
@@ -2709,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" si="2"/>
@@ -2728,10 +2727,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="K26" s="24"/>
       <c r="L26" s="1">
@@ -2740,7 +2739,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
@@ -2749,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="2"/>
@@ -2768,10 +2767,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="K27" s="24"/>
       <c r="L27" s="1">
@@ -2780,7 +2779,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
@@ -2789,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E28" s="3">
         <f t="shared" si="2"/>
@@ -2808,10 +2807,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="1">
@@ -2820,7 +2819,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
@@ -2829,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E29" s="3">
         <f t="shared" si="2"/>
@@ -2848,10 +2847,10 @@
         <v>333.33333333333451</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="K29" s="24"/>
       <c r="L29" s="1">
@@ -2860,7 +2859,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
@@ -2869,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E30" s="3">
         <f t="shared" si="2"/>
@@ -2888,10 +2887,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="K30" s="24"/>
       <c r="L30" s="1">
@@ -2900,7 +2899,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
@@ -2909,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" s="3">
         <f t="shared" si="2"/>
@@ -2928,10 +2927,10 @@
         <v>333.33333333333303</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="K31" s="24"/>
       <c r="L31" s="1">
@@ -2949,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E32" s="3">
         <f t="shared" si="2"/>
@@ -2972,7 +2971,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>18</v>
       </c>
@@ -2983,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E33" s="3">
         <f t="shared" si="2"/>
@@ -3006,7 +3005,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>19</v>
       </c>
@@ -3017,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E34" s="13">
         <f t="shared" si="2"/>
@@ -3036,14 +3035,14 @@
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="18" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="K34" s="25"/>
       <c r="L34" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>20</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E35" s="22">
         <v>2.512</v>
@@ -3071,10 +3070,10 @@
         <v>569.25524934383191</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="J35" s="21" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="K35" s="26" t="s">
         <v>29</v>
@@ -3083,9 +3082,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
@@ -3094,7 +3093,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E36" s="3">
         <f t="shared" ref="E36:E53" si="7">F35</f>
@@ -3112,16 +3111,16 @@
         <v>99.234580052493442</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="K36" s="24"/>
       <c r="L36" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B37" s="1">
         <v>1</v>
@@ -3130,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E37" s="3">
         <f t="shared" si="7"/>
@@ -3152,9 +3151,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
@@ -3163,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E38" s="3">
         <f t="shared" si="7"/>
@@ -3185,9 +3184,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
@@ -3196,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E39" s="3">
         <f t="shared" si="7"/>
@@ -3218,9 +3217,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B40" s="1">
         <v>1</v>
@@ -3229,7 +3228,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E40" s="3">
         <f t="shared" si="7"/>
@@ -3251,9 +3250,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
@@ -3262,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E41" s="3">
         <f t="shared" si="7"/>
@@ -3284,9 +3283,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
@@ -3295,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E42" s="3">
         <f t="shared" si="7"/>
@@ -3317,9 +3316,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
@@ -3328,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E43" s="3">
         <f t="shared" si="7"/>
@@ -3350,9 +3349,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B44" s="1">
         <v>1</v>
@@ -3361,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E44" s="3">
         <f t="shared" si="7"/>
@@ -3383,9 +3382,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B45" s="1">
         <v>1</v>
@@ -3394,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E45" s="3">
         <f t="shared" si="7"/>
@@ -3416,9 +3415,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B46" s="1">
         <v>1</v>
@@ -3427,7 +3426,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E46" s="3">
         <f t="shared" si="7"/>
@@ -3449,9 +3448,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B47" s="1">
         <v>1</v>
@@ -3460,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E47" s="3">
         <f t="shared" si="7"/>
@@ -3478,16 +3477,16 @@
         <v>111.05314960629936</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="K47" s="24"/>
       <c r="L47" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B48" s="1">
         <v>1</v>
@@ -3496,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E48" s="3">
         <f t="shared" si="7"/>
@@ -3506,24 +3505,27 @@
         <v>559.58649200000002</v>
       </c>
       <c r="G48" s="3">
-        <f t="shared" ref="G48:G58" si="8">F48-E48</f>
+        <f t="shared" ref="G48:G61" si="8">F48-E48</f>
         <v>41.929491999999982</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" ref="H48:H57" si="9">G48/0.3048</f>
+        <f t="shared" ref="H48:H61" si="9">G48/0.3048</f>
         <v>137.56395013123353</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="K48" s="24"/>
       <c r="L48" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N48" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B49" s="1">
         <v>1</v>
@@ -3532,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E49" s="3">
         <f t="shared" si="7"/>
@@ -3553,10 +3555,13 @@
       <c r="L49" s="1">
         <v>46</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N49" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B50" s="1">
         <v>1</v>
@@ -3565,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E50" s="3">
         <f t="shared" si="7"/>
@@ -3586,10 +3591,13 @@
       <c r="L50" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N50" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B51" s="1">
         <v>1</v>
@@ -3598,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E51" s="3">
         <f t="shared" si="7"/>
@@ -3616,16 +3624,19 @@
         <v>132.8740157480315</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="K51" s="24"/>
       <c r="L51" s="1">
         <v>48</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N51" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
@@ -3634,7 +3645,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E52" s="3">
         <f t="shared" si="7"/>
@@ -3652,19 +3663,19 @@
         <v>52.242480314960531</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="K52" s="24"/>
       <c r="L52" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B53" s="1">
         <v>1</v>
@@ -3673,7 +3684,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E53" s="3">
         <f t="shared" si="7"/>
@@ -3691,19 +3702,19 @@
         <v>101.91929133858285</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="K53" s="24"/>
       <c r="L53" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B54" s="1">
         <v>2</v>
@@ -3712,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E54" s="3">
         <v>686.41033000000004</v>
@@ -3729,19 +3740,19 @@
         <v>90.767290026246471</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="J54" s="17" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="K54" s="24"/>
       <c r="L54" s="1">
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B55" s="1">
         <v>3</v>
@@ -3750,7 +3761,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="E55" s="3">
         <v>700.52800000000002</v>
@@ -3767,19 +3778,19 @@
         <v>130.42318241469803</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="J55" s="17" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="K55" s="24"/>
       <c r="L55" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B56" s="1">
         <v>4</v>
@@ -3788,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="E56" s="3">
         <v>733.77200000000005</v>
@@ -3805,19 +3816,19 @@
         <v>73.253152887138924</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="J56" s="17" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="K56" s="24"/>
       <c r="L56" s="1">
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B57" s="1">
         <v>5</v>
@@ -3826,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="E57" s="1">
         <v>733.77200000000005</v>
@@ -3843,19 +3854,19 @@
         <v>80.439632545931474</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="J57" s="17" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="K57" s="24"/>
       <c r="L57" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="B58" s="1">
         <v>9</v>
@@ -3864,7 +3875,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="E58" s="1">
         <v>130.392</v>
@@ -3881,19 +3892,19 @@
         <v>599.2913385826771</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="J58" s="17" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="K58" s="24"/>
       <c r="L58" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B59" s="12">
         <v>9</v>
@@ -3902,7 +3913,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E59" s="12">
         <v>313.05599999999998</v>
@@ -3911,581 +3922,720 @@
         <v>455.10700000000003</v>
       </c>
       <c r="G59" s="13">
-        <f t="shared" ref="G59" si="10">F59-E59</f>
+        <f t="shared" si="8"/>
         <v>142.05100000000004</v>
       </c>
       <c r="H59" s="14">
-        <f t="shared" ref="H59" si="11">G59/0.3048</f>
+        <f t="shared" si="9"/>
         <v>466.04658792650929</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="K59" s="25"/>
       <c r="L59" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="str">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="1">
+        <v>17</v>
+      </c>
+      <c r="C60" s="1">
+        <v>0</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E60" s="1">
+        <v>-29.234999999999999</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3">
+        <f t="shared" si="8"/>
+        <v>29.234999999999999</v>
+      </c>
+      <c r="H60" s="2">
+        <f t="shared" si="9"/>
+        <v>95.915354330708652</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="K60" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="L60" s="1">
+        <v>57</v>
+      </c>
+      <c r="M60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="1">
+        <v>18</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E61" s="1">
+        <v>-3.2050000000000001</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <f t="shared" si="8"/>
+        <v>3.2050000000000001</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="9"/>
+        <v>10.51509186351706</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="K61" s="28"/>
+      <c r="L61" s="1">
+        <v>58</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="str">
         <f>$A$5</f>
         <v>S01</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B62" s="1">
         <v>8</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C62" s="1">
         <f>$C$5</f>
         <v>0</v>
       </c>
-      <c r="D60" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>$D$5</f>
         <v>L0B/HTR/DIAG0/COL0/L1B</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E62" s="3">
         <f>$E$5</f>
         <v>0</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F62" s="3">
         <f>$F$5</f>
         <v>101.6</v>
       </c>
-      <c r="G60" s="3">
-        <f>$G$5</f>
+      <c r="G62" s="3">
+        <f>F62-E62</f>
         <v>101.6</v>
       </c>
-      <c r="H60" s="2">
-        <f>$H$5</f>
+      <c r="H62" s="2">
+        <f>G62/0.3048</f>
         <v>333.33333333333331</v>
       </c>
-      <c r="K60" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="L60" s="1">
-        <v>57</v>
-      </c>
-      <c r="M60" s="1">
+      <c r="K62" s="28"/>
+      <c r="L62" s="1">
+        <v>59</v>
+      </c>
+      <c r="M62" s="1">
         <f>$L$5</f>
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="str">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63" s="1">
+        <v>17</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>12.895</v>
+      </c>
+      <c r="G63" s="3">
+        <f>F63-E63</f>
+        <v>12.895</v>
+      </c>
+      <c r="H63" s="2">
+        <f>G63/0.3048</f>
+        <v>42.30643044619422</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="K63" s="28"/>
+      <c r="L63" s="1">
+        <v>60</v>
+      </c>
+      <c r="M63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B64" s="1">
+        <v>18</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E64" s="3">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>11.541</v>
+      </c>
+      <c r="G64" s="3">
+        <f>F64-E64</f>
+        <v>11.541</v>
+      </c>
+      <c r="H64" s="2">
+        <f>G64/0.3048</f>
+        <v>37.864173228346459</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="K64" s="28"/>
+      <c r="L64" s="1">
+        <v>61</v>
+      </c>
+      <c r="M64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="str">
         <f>$A$32</f>
         <v>S28</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B65" s="1">
         <v>6</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C65" s="1">
         <f>$C$32</f>
         <v>0</v>
       </c>
-      <c r="D61" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="E61" s="3">
+      <c r="D65" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E65" s="3">
         <f>$E$32</f>
         <v>2743.2</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F65" s="3">
         <f>$F$32</f>
         <v>2844.7999999999997</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G65" s="3">
         <f>$G$32</f>
         <v>101.59999999999991</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H65" s="2">
         <f>$H$32</f>
         <v>333.33333333333303</v>
       </c>
-      <c r="K61" s="31"/>
-      <c r="L61" s="1">
-        <v>58</v>
-      </c>
-      <c r="M61" s="1">
+      <c r="K65" s="28"/>
+      <c r="L65" s="1">
+        <v>62</v>
+      </c>
+      <c r="M65" s="1">
         <f>$L$32</f>
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="str">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="str">
         <f>$A$32</f>
         <v>S28</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B66" s="1">
         <v>7</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C66" s="1">
         <f>$C$32</f>
         <v>0</v>
       </c>
-      <c r="D62" s="9" t="str">
+      <c r="D66" s="9" t="str">
         <f>$D$32</f>
         <v>BYP/SPD1</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E66" s="3">
         <f>$E$32</f>
         <v>2743.2</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F66" s="3">
         <f>$F$32</f>
         <v>2844.7999999999997</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G66" s="3">
         <f>$G$32</f>
         <v>101.59999999999991</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H66" s="2">
         <f>$H$32</f>
         <v>333.33333333333303</v>
       </c>
-      <c r="K62" s="31"/>
-      <c r="L62" s="1">
-        <v>59</v>
-      </c>
-      <c r="M62" s="1">
-        <f t="shared" ref="M62:M63" si="12">$L$32</f>
+      <c r="K66" s="28"/>
+      <c r="L66" s="1">
+        <v>63</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" ref="M66:M67" si="10">$L$32</f>
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="str">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="str">
         <f>$A$32</f>
         <v>S28</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B67" s="1">
         <v>9</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C67" s="1">
         <f>$C$32</f>
         <v>0</v>
       </c>
-      <c r="D63" s="9" t="str">
+      <c r="D67" s="9" t="str">
         <f>$D$32</f>
         <v>BYP/SPD1</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E67" s="3">
         <f>$E$32</f>
         <v>2743.2</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F67" s="3">
         <f>$F$32</f>
         <v>2844.7999999999997</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G67" s="3">
         <f>$G$32</f>
         <v>101.59999999999991</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H67" s="2">
         <f>$H$32</f>
         <v>333.33333333333303</v>
       </c>
-      <c r="K63" s="31"/>
-      <c r="L63" s="1">
-        <v>60</v>
-      </c>
-      <c r="M63" s="1">
-        <f t="shared" si="12"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="1">
+        <v>64</v>
+      </c>
+      <c r="M67" s="1">
+        <f t="shared" si="10"/>
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="str">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="str">
         <f>$A$33</f>
         <v>S29</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B68" s="1">
         <v>6</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C68" s="1">
         <f>$C$33</f>
         <v>0</v>
       </c>
-      <c r="D64" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="E64" s="3">
+      <c r="D68" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="E68" s="3">
         <f>$E$33</f>
         <v>2844.7999999999997</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F68" s="3">
         <f>$F$33</f>
         <v>2946.3999999999996</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G68" s="3">
         <f>$G$33</f>
         <v>101.59999999999991</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H68" s="2">
         <f>$H$33</f>
         <v>333.33333333333303</v>
       </c>
-      <c r="K64" s="31"/>
-      <c r="L64" s="1">
-        <v>61</v>
-      </c>
-      <c r="M64" s="1">
+      <c r="K68" s="28"/>
+      <c r="L68" s="1">
+        <v>65</v>
+      </c>
+      <c r="M68" s="1">
         <f>$L$33</f>
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="str">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="str">
         <f>$A$33</f>
         <v>S29</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B69" s="1">
         <v>7</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C69" s="1">
         <f>$C$33</f>
         <v>0</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="E65" s="3">
+      <c r="D69" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="E69" s="3">
         <f>$E$33</f>
         <v>2844.7999999999997</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F69" s="3">
         <f>$F$33</f>
         <v>2946.3999999999996</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G69" s="3">
         <f>$G$33</f>
         <v>101.59999999999991</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H69" s="2">
         <f>$H$33</f>
         <v>333.33333333333303</v>
       </c>
-      <c r="K65" s="31"/>
-      <c r="L65" s="1">
-        <v>62</v>
-      </c>
-      <c r="M65" s="1">
-        <f t="shared" ref="M65:M66" si="13">$L$33</f>
+      <c r="K69" s="28"/>
+      <c r="L69" s="1">
+        <v>66</v>
+      </c>
+      <c r="M69" s="1">
+        <f t="shared" ref="M69:M70" si="11">$L$33</f>
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="str">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="str">
         <f>$A$33</f>
         <v>S29</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B70" s="1">
         <v>9</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C70" s="1">
         <f>$C$33</f>
         <v>0</v>
       </c>
-      <c r="D66" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D70" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="E70" s="3">
         <f>$E$33</f>
         <v>2844.7999999999997</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F70" s="3">
         <f>$F$33</f>
         <v>2946.3999999999996</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G70" s="3">
         <f>$G$33</f>
         <v>101.59999999999991</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H70" s="2">
         <f>$H$33</f>
         <v>333.33333333333303</v>
       </c>
-      <c r="K66" s="31"/>
-      <c r="L66" s="1">
-        <v>63</v>
-      </c>
-      <c r="M66" s="1">
-        <f t="shared" si="13"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="1">
+        <v>67</v>
+      </c>
+      <c r="M70" s="1">
+        <f t="shared" si="11"/>
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="30" t="str">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="str">
         <f>$A$34</f>
         <v>S30</v>
       </c>
-      <c r="B67" s="30">
+      <c r="B71" s="9">
         <v>6</v>
       </c>
-      <c r="C67" s="30">
+      <c r="C71" s="9">
         <f>$C$34</f>
         <v>0</v>
       </c>
-      <c r="D67" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="E67" s="28">
+      <c r="D71" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="E71" s="3">
         <f>$E$34</f>
         <v>2946.3999999999996</v>
       </c>
-      <c r="F67" s="28">
+      <c r="F71" s="3">
         <f>$F$34</f>
         <v>3050.5120000000002</v>
       </c>
-      <c r="G67" s="28">
+      <c r="G71" s="3">
         <f>$G$34</f>
         <v>104.11200000000053</v>
       </c>
-      <c r="H67" s="29">
+      <c r="H71" s="2">
         <f>$H$34</f>
         <v>341.57480314960804</v>
       </c>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="1">
-        <v>64</v>
-      </c>
-      <c r="M67" s="1">
+      <c r="K71" s="28"/>
+      <c r="L71" s="1">
+        <v>68</v>
+      </c>
+      <c r="M71" s="1">
         <f>$L$34</f>
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="30" t="str">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="9" t="str">
         <f>$A$34</f>
         <v>S30</v>
       </c>
-      <c r="B68" s="30">
+      <c r="B72" s="9">
         <v>7</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C72" s="9">
         <f>$C$34</f>
         <v>0</v>
       </c>
-      <c r="D68" s="30" t="s">
+      <c r="D72" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="E68" s="28">
+      <c r="E72" s="3">
         <f>$E$34</f>
         <v>2946.3999999999996</v>
       </c>
-      <c r="F68" s="28">
+      <c r="F72" s="3">
         <f>$F$34</f>
         <v>3050.5120000000002</v>
       </c>
-      <c r="G68" s="28">
+      <c r="G72" s="3">
         <f>$G$34</f>
         <v>104.11200000000053</v>
       </c>
-      <c r="H68" s="29">
+      <c r="H72" s="2">
         <f>$H$34</f>
         <v>341.57480314960804</v>
       </c>
-      <c r="I68" s="27"/>
-      <c r="J68" s="27"/>
-      <c r="K68" s="31"/>
-      <c r="L68" s="1">
-        <v>65</v>
-      </c>
-      <c r="M68" s="1">
+      <c r="K72" s="28"/>
+      <c r="L72" s="1">
+        <v>69</v>
+      </c>
+      <c r="M72" s="1">
         <f>$L$34</f>
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="30" t="str">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="str">
         <f>$A$34</f>
         <v>S30</v>
       </c>
-      <c r="B69" s="30">
+      <c r="B73" s="9">
         <v>9</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C73" s="9">
         <f>$C$34</f>
         <v>0</v>
       </c>
-      <c r="D69" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="E69" s="28">
+      <c r="D73" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E73" s="3">
         <f>$E$34</f>
         <v>2946.3999999999996</v>
       </c>
-      <c r="F69" s="28">
+      <c r="F73" s="3">
         <f>$F$34</f>
         <v>3050.5120000000002</v>
       </c>
-      <c r="G69" s="28">
+      <c r="G73" s="3">
         <f>$G$34</f>
         <v>104.11200000000053</v>
       </c>
-      <c r="H69" s="29">
+      <c r="H73" s="2">
         <f>$H$34</f>
         <v>341.57480314960804</v>
       </c>
-      <c r="I69" s="27"/>
-      <c r="J69" s="27"/>
-      <c r="K69" s="31"/>
-      <c r="L69" s="1">
-        <v>66</v>
-      </c>
-      <c r="M69" s="1">
+      <c r="K73" s="28"/>
+      <c r="L73" s="1">
+        <v>70</v>
+      </c>
+      <c r="M73" s="1">
         <f>$L$34</f>
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="27" t="str">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="str">
         <f>$A$35</f>
         <v>BSY</v>
       </c>
-      <c r="B70" s="27">
+      <c r="B74" s="1">
         <v>6</v>
       </c>
-      <c r="C70" s="27">
+      <c r="C74" s="1">
         <f>$C$35</f>
         <v>1</v>
       </c>
-      <c r="D70" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="E70" s="28">
+      <c r="D74" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E74" s="3">
         <v>2.512</v>
       </c>
-      <c r="F70" s="28">
+      <c r="F74" s="3">
         <v>176.02099999999999</v>
       </c>
-      <c r="G70" s="28">
-        <f>F70-E70</f>
+      <c r="G74" s="3">
+        <f>F74-E74</f>
         <v>173.50899999999999</v>
       </c>
-      <c r="H70" s="29">
-        <f>G70/0.3048</f>
+      <c r="H74" s="2">
+        <f>G74/0.3048</f>
         <v>569.25524934383191</v>
       </c>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="1">
-        <v>67</v>
-      </c>
-      <c r="M70" s="1">
+      <c r="K74" s="28"/>
+      <c r="L74" s="1">
+        <v>71</v>
+      </c>
+      <c r="M74" s="1">
         <f>$L$35</f>
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="27" t="str">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="str">
         <f>$A$35</f>
         <v>BSY</v>
       </c>
-      <c r="B71" s="27">
+      <c r="B75" s="1">
         <v>7</v>
       </c>
-      <c r="C71" s="27">
+      <c r="C75" s="1">
         <f>$C$35</f>
         <v>1</v>
       </c>
-      <c r="D71" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="E71" s="28">
+      <c r="D75" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E75" s="3">
         <v>2.512</v>
       </c>
-      <c r="F71" s="28">
+      <c r="F75" s="3">
         <v>162.65100000000001</v>
       </c>
-      <c r="G71" s="28">
-        <f>F71-E71</f>
+      <c r="G75" s="3">
+        <f>F75-E75</f>
         <v>160.13900000000001</v>
       </c>
-      <c r="H71" s="29">
-        <f>G71/0.3048</f>
+      <c r="H75" s="2">
+        <f>G75/0.3048</f>
         <v>525.39041994750653</v>
       </c>
-      <c r="I71" s="27"/>
-      <c r="J71" s="27"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="1">
-        <v>68</v>
-      </c>
-      <c r="M71" s="1">
+      <c r="K75" s="28"/>
+      <c r="L75" s="1">
+        <v>72</v>
+      </c>
+      <c r="M75" s="1">
         <f>$L$35</f>
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="str">
+    <row r="76" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="12" t="str">
         <f>$A$35</f>
         <v>BSY</v>
       </c>
-      <c r="B72" s="12">
+      <c r="B76" s="12">
         <v>9</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C76" s="12">
         <f>$C$35</f>
         <v>1</v>
       </c>
-      <c r="D72" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="E72" s="13">
+      <c r="D76" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E76" s="13">
         <v>2.512</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F76" s="13">
         <v>130.392</v>
       </c>
-      <c r="G72" s="13">
-        <f>F72-E72</f>
+      <c r="G76" s="13">
+        <f>F76-E76</f>
         <v>127.88</v>
       </c>
-      <c r="H72" s="14">
-        <f>G72/0.3048</f>
+      <c r="H76" s="14">
+        <f>G76/0.3048</f>
         <v>419.5538057742782</v>
       </c>
-      <c r="I72" s="12"/>
-      <c r="J72" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="K72" s="32"/>
-      <c r="L72" s="1">
-        <v>69</v>
-      </c>
-      <c r="M72" s="27">
+      <c r="I76" s="12"/>
+      <c r="J76" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="K76" s="29"/>
+      <c r="L76" s="1">
+        <v>73</v>
+      </c>
+      <c r="M76" s="1">
         <f>$L$35</f>
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>1</v>
-      </c>
-      <c r="B75" s="20" t="s">
-        <v>336</v>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>1</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K4:K34"/>
     <mergeCell ref="K35:K59"/>
-    <mergeCell ref="K60:K72"/>
+    <mergeCell ref="K60:K76"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup scale="61" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="G60:H60 G71" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4503,8 +4653,7 @@
     <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -4526,7 +4675,7 @@
       <c r="C1" s="10"/>
       <c r="F1" s="7"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -4536,20 +4685,20 @@
       <c r="E2" s="5"/>
       <c r="F2" s="7"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>22</v>
@@ -4560,14 +4709,14 @@
       <c r="G3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>26</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="K3" s="15"/>
     </row>
@@ -4582,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>402</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3">
         <v>2017.911482</v>
@@ -4594,15 +4743,15 @@
         <f>F4-E4</f>
         <v>17.123648000000003</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f>G4/0.3048</f>
         <v>56.179947506561689</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="K4" s="24" t="s">
         <v>28</v>
@@ -4622,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="E5" s="3">
         <f>F4</f>
@@ -4636,15 +4785,15 @@
         <f t="shared" ref="G5:G14" si="0">F5-E5</f>
         <v>98.564869999999928</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f t="shared" ref="H5:H14" si="1">G5/0.3048</f>
         <v>323.37555774278189</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="1">
@@ -4662,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" ref="E6:E14" si="2">F5</f>
@@ -4676,15 +4825,15 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="K6" s="24"/>
       <c r="L6" s="1">
@@ -4702,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="2"/>
@@ -4716,15 +4865,15 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="K7" s="24"/>
       <c r="L7" s="1">
@@ -4742,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="2"/>
@@ -4756,15 +4905,15 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="1">
@@ -4782,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="2"/>
@@ -4796,15 +4945,15 @@
         <f t="shared" si="0"/>
         <v>101.60000000000036</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f t="shared" si="1"/>
         <v>333.33333333333451</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="K9" s="24"/>
       <c r="L9" s="1">
@@ -4822,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="2"/>
@@ -4836,15 +4985,15 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="K10" s="24"/>
       <c r="L10" s="1">
@@ -4862,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="2"/>
@@ -4876,15 +5025,15 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="1">
@@ -4902,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="2"/>
@@ -4916,15 +5065,15 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="K12" s="24"/>
       <c r="L12" s="1">
@@ -4942,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="2"/>
@@ -4956,15 +5105,15 @@
         <f t="shared" si="0"/>
         <v>101.59999999999991</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f t="shared" si="1"/>
         <v>333.33333333333303</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="K13" s="24"/>
       <c r="L13" s="1">
@@ -4982,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E14" s="13">
         <f t="shared" si="2"/>
@@ -4995,15 +5144,15 @@
         <f t="shared" si="0"/>
         <v>104.11200000000053</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <f t="shared" si="1"/>
         <v>341.57480314960804</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="K14" s="25"/>
       <c r="L14" s="1">
@@ -5021,7 +5170,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>378</v>
+        <v>313</v>
       </c>
       <c r="E15" s="3">
         <v>2.512</v>
@@ -5033,18 +5182,18 @@
         <f t="shared" ref="G15:G27" si="3">F15-E15</f>
         <v>173.50899999999999</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f t="shared" ref="H15:H27" si="4">G15/0.3048</f>
         <v>569.25524934383191</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K15" s="26" t="s">
-        <v>400</v>
+        <v>29</v>
       </c>
       <c r="L15" s="1">
         <v>12</v>
@@ -5052,7 +5201,7 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
@@ -5061,7 +5210,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3">
         <f>F15</f>
@@ -5074,21 +5223,21 @@
         <f t="shared" si="3"/>
         <v>27.509000000000015</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f t="shared" si="4"/>
         <v>90.252624671916053</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="K16" s="24"/>
       <c r="L16" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B17" s="1">
         <v>10</v>
@@ -5097,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" ref="E17:E33" si="5">F16</f>
@@ -5110,7 +5259,7 @@
         <f t="shared" si="3"/>
         <v>27.749300000000005</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <f t="shared" si="4"/>
         <v>91.041010498687683</v>
       </c>
@@ -5119,9 +5268,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B18" s="1">
         <v>10</v>
@@ -5130,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="5"/>
@@ -5143,7 +5292,7 @@
         <f t="shared" si="3"/>
         <v>29.200700000000012</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f t="shared" si="4"/>
         <v>95.802821522309742</v>
       </c>
@@ -5152,9 +5301,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B19" s="1">
         <v>10</v>
@@ -5163,7 +5312,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3">
         <f t="shared" si="5"/>
@@ -5176,7 +5325,7 @@
         <f t="shared" si="3"/>
         <v>26.279999999999973</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <f t="shared" si="4"/>
         <v>86.220472440944789</v>
       </c>
@@ -5185,9 +5334,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B20" s="1">
         <v>10</v>
@@ -5196,7 +5345,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="5"/>
@@ -5209,7 +5358,7 @@
         <f t="shared" si="3"/>
         <v>27.769999999999982</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="2">
         <f t="shared" si="4"/>
         <v>91.108923884514368</v>
       </c>
@@ -5218,9 +5367,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
@@ -5229,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3">
         <f t="shared" si="5"/>
@@ -5242,7 +5391,7 @@
         <f t="shared" si="3"/>
         <v>27.740000000000009</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="2">
         <f t="shared" si="4"/>
         <v>91.010498687664068</v>
       </c>
@@ -5251,9 +5400,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B22" s="1">
         <v>10</v>
@@ -5262,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="5"/>
@@ -5275,7 +5424,7 @@
         <f t="shared" si="3"/>
         <v>29.150000000000034</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="2">
         <f t="shared" si="4"/>
         <v>95.636482939632657</v>
       </c>
@@ -5284,9 +5433,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
@@ -5295,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3">
         <f t="shared" si="5"/>
@@ -5308,7 +5457,7 @@
         <f t="shared" si="3"/>
         <v>26.339999999999975</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="2">
         <f t="shared" si="4"/>
         <v>86.417322834645589</v>
       </c>
@@ -5317,9 +5466,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B24" s="1">
         <v>10</v>
@@ -5328,7 +5477,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="5"/>
@@ -5341,7 +5490,7 @@
         <f t="shared" si="3"/>
         <v>27.769999999999982</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="2">
         <f t="shared" si="4"/>
         <v>91.108923884514368</v>
       </c>
@@ -5350,9 +5499,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B25" s="1">
         <v>10</v>
@@ -5361,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="5"/>
@@ -5374,7 +5523,7 @@
         <f t="shared" si="3"/>
         <v>27.75</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="2">
         <f t="shared" si="4"/>
         <v>91.043307086614163</v>
       </c>
@@ -5383,9 +5532,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B26" s="1">
         <v>10</v>
@@ -5394,7 +5543,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" si="5"/>
@@ -5407,7 +5556,7 @@
         <f t="shared" si="3"/>
         <v>27.75</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="2">
         <f t="shared" si="4"/>
         <v>91.043307086614163</v>
       </c>
@@ -5416,9 +5565,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B27" s="1">
         <v>10</v>
@@ -5427,7 +5576,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="5"/>
@@ -5440,21 +5589,21 @@
         <f t="shared" si="3"/>
         <v>33.710001000000034</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="2">
         <f t="shared" si="4"/>
         <v>110.59711614173239</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="K27" s="24"/>
       <c r="L27" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B28" s="1">
         <v>10</v>
@@ -5463,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>27</v>
+        <v>357</v>
       </c>
       <c r="E28" s="3">
         <f t="shared" si="5"/>
@@ -5481,16 +5630,19 @@
         <v>119.6488976377952</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N28" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B29" s="1">
         <v>10</v>
@@ -5520,10 +5672,13 @@
       <c r="L29" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N29" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B30" s="1">
         <v>10</v>
@@ -5553,10 +5708,13 @@
       <c r="L30" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N30" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B31" s="1">
         <v>10</v>
@@ -5583,16 +5741,19 @@
         <v>154.36190288713891</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="K31" s="24"/>
       <c r="L31" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N31" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1">
         <v>10</v>
@@ -5601,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E32" s="3">
         <f t="shared" si="5"/>
@@ -5614,15 +5775,15 @@
         <f t="shared" si="6"/>
         <v>15.923506999999972</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <f t="shared" ref="H32" si="7">G32/0.3048</f>
         <v>52.24247703412064</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="K32" s="24"/>
       <c r="L32" s="1">
@@ -5631,7 +5792,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B33" s="1">
         <v>10</v>
@@ -5640,7 +5801,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E33" s="3">
         <f t="shared" si="5"/>
@@ -5653,15 +5814,15 @@
         <f t="shared" si="6"/>
         <v>31.065000000000055</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="2">
         <f>G33/0.3048</f>
         <v>101.91929133858285</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="K33" s="24"/>
       <c r="L33" s="1">
@@ -5670,7 +5831,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B34" s="1">
         <v>11</v>
@@ -5679,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E34" s="3">
         <v>686.41033100000004</v>
@@ -5691,15 +5852,15 @@
         <f t="shared" si="6"/>
         <v>27.665869999999927</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="2">
         <f t="shared" ref="H34" si="8">G34/0.3048</f>
         <v>90.767290026246471</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="K34" s="24"/>
       <c r="L34" s="1">
@@ -5708,7 +5869,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B35" s="1">
         <v>12</v>
@@ -5717,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E35" s="3">
         <v>700.52800000000002</v>
@@ -5729,15 +5890,15 @@
         <f t="shared" ref="G35" si="9">F35-E35</f>
         <v>58.533928999999944</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="2">
         <f t="shared" ref="H35" si="10">G35/0.3048</f>
         <v>192.04044947506543</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="K35" s="24"/>
       <c r="L35" s="1">
@@ -5746,7 +5907,7 @@
     </row>
     <row r="36" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B36" s="12">
         <v>13</v>
@@ -5755,7 +5916,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="E36" s="13">
         <v>739.999999</v>
@@ -5767,15 +5928,15 @@
         <f t="shared" si="6"/>
         <v>18.360869999999977</v>
       </c>
-      <c r="H36" s="13">
+      <c r="H36" s="14">
         <f t="shared" ref="H36:H37" si="11">G36/0.3048</f>
         <v>60.239074803149528</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="K36" s="25"/>
       <c r="L36" s="1">
@@ -5793,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="E37" s="3">
         <v>10.456</v>
@@ -5810,13 +5971,13 @@
         <v>391.06299212598418</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="L37" s="1">
         <v>34</v>
@@ -5836,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="E38" s="3">
         <v>2018.712</v>
@@ -5853,10 +6014,10 @@
         <v>0.86942257217880592</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="K38" s="24"/>
       <c r="L38" s="1">
@@ -5877,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="E39" s="13">
         <v>2031.991</v>
@@ -5894,10 +6055,10 @@
         <v>15.695538057743127</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="K39" s="25"/>
       <c r="L39" s="1">
@@ -5912,7 +6073,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="B41" s="1"/>
       <c r="K41" s="11"/>
@@ -5922,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="K42" s="11"/>
     </row>
@@ -5999,18 +6160,19 @@
     <col min="4" max="5" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="3"/>
     <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="17.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>22</v>
@@ -6024,22 +6186,22 @@
       <c r="G1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>381</v>
+      <c r="H1" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>198</v>
+        <v>398</v>
       </c>
       <c r="D2" s="3">
         <v>517.54</v>
@@ -6055,19 +6217,19 @@
         <f>F2/0.3048</f>
         <v>8.0265485564305603</v>
       </c>
-      <c r="I2" t="s">
-        <v>380</v>
+      <c r="I2" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="D3" s="3">
         <v>519.986492</v>
@@ -6084,18 +6246,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>201</v>
+        <v>361</v>
       </c>
       <c r="D4" s="3">
         <v>524.38649199999998</v>
@@ -6112,18 +6274,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>202</v>
+        <v>362</v>
       </c>
       <c r="D5" s="3">
         <v>528.78649199999995</v>
@@ -6140,18 +6302,18 @@
         <v>14.43569553805804</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>203</v>
+        <v>363</v>
       </c>
       <c r="D6" s="3">
         <v>533.18649200000004</v>
@@ -6168,18 +6330,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>204</v>
+        <v>364</v>
       </c>
       <c r="D7" s="3">
         <v>537.58649200000002</v>
@@ -6196,18 +6358,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>205</v>
+        <v>365</v>
       </c>
       <c r="D8" s="3">
         <v>541.986492</v>
@@ -6224,18 +6386,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>206</v>
+        <v>366</v>
       </c>
       <c r="D9" s="3">
         <v>546.38649199999998</v>
@@ -6252,18 +6414,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>207</v>
+        <v>367</v>
       </c>
       <c r="D10" s="3">
         <v>550.78649199999995</v>
@@ -6280,18 +6442,18 @@
         <v>14.43569553805804</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>199</v>
+        <v>368</v>
       </c>
       <c r="D11" s="3">
         <v>555.18649200000004</v>
@@ -6308,18 +6470,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D12" s="3">
         <v>559.58649200000002</v>
@@ -6336,18 +6498,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D13" s="3">
         <v>563.986492</v>
@@ -6364,18 +6526,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D14" s="3">
         <v>568.38649199999998</v>
@@ -6392,18 +6554,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D15" s="3">
         <v>572.78649199999995</v>
@@ -6420,18 +6582,18 @@
         <v>14.43569553805804</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D16" s="3">
         <v>577.18649200000004</v>
@@ -6448,18 +6610,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="D17" s="3">
         <v>581.58649200000002</v>
@@ -6476,18 +6638,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D18" s="3">
         <v>585.986492</v>
@@ -6504,18 +6666,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D19" s="3">
         <v>590.38649199999998</v>
@@ -6532,18 +6694,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D20" s="3">
         <v>594.78649199999995</v>
@@ -6560,18 +6722,18 @@
         <v>14.43569553805804</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D21" s="3">
         <v>599.18649200000004</v>
@@ -6588,18 +6750,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D22" s="3">
         <v>603.58649200000002</v>
@@ -6616,18 +6778,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D23" s="3">
         <v>607.986492</v>
@@ -6644,18 +6806,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D24" s="3">
         <v>612.38649199999998</v>
@@ -6672,18 +6834,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D25" s="3">
         <v>616.78649199999995</v>
@@ -6700,18 +6862,18 @@
         <v>14.43569553805804</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D26" s="3">
         <v>621.18649200000004</v>
@@ -6728,18 +6890,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D27" s="3">
         <v>625.58649200000002</v>
@@ -6756,18 +6918,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="B28" s="1">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D28" s="3">
         <v>629.986492</v>
@@ -6784,18 +6946,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D29" s="3">
         <v>634.38649199999998</v>
@@ -6812,18 +6974,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D30" s="3">
         <v>638.78649199999995</v>
@@ -6840,18 +7002,18 @@
         <v>14.43569553805804</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D31" s="3">
         <v>643.18649200000004</v>
@@ -6868,18 +7030,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D32" s="3">
         <v>647.58649200000002</v>
@@ -6896,18 +7058,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="B33" s="1">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D33" s="3">
         <v>651.986492</v>
@@ -6924,18 +7086,18 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="B34" s="1">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D34" s="3">
         <v>656.38649199999998</v>
@@ -6952,21 +7114,21 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I34" t="s">
-        <v>384</v>
+        <v>188</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D35" s="3">
         <v>660.78649199999995</v>
@@ -6983,18 +7145,18 @@
         <v>14.43569553805804</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D36" s="3">
         <v>665.18649200000004</v>
@@ -7011,34 +7173,34 @@
         <v>14.435695538057667</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>22</v>
@@ -7052,84 +7214,87 @@
       <c r="G1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>381</v>
+      <c r="H1" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>249</v>
+        <v>369</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>245</v>
+        <v>369</v>
       </c>
       <c r="D2" s="3">
         <v>514.74000100000001</v>
       </c>
       <c r="E2" s="3">
-        <v>519.10765100000003</v>
+        <v>515.09498499999995</v>
       </c>
       <c r="F2" s="3">
-        <f t="shared" ref="F2:F4" si="0">E2-D2</f>
-        <v>4.367650000000026</v>
+        <f>E2-D2</f>
+        <v>0.3549839999999449</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G4" si="1">F2/0.3048</f>
-        <v>14.329560367454153</v>
+        <f>F2/0.3048</f>
+        <v>1.1646456692911578</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>382</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="B3" s="1">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="D3" s="3">
+        <f>E2</f>
+        <v>515.09498499999995</v>
+      </c>
+      <c r="E3" s="3">
         <v>519.10765100000003</v>
       </c>
-      <c r="E3" s="3">
-        <v>523.120318</v>
-      </c>
       <c r="F3" s="3">
-        <f t="shared" si="0"/>
-        <v>4.0126669999999649</v>
+        <f t="shared" ref="F3:F5" si="0">E3-D3</f>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" si="1"/>
-        <v>13.164917979002508</v>
+        <f t="shared" ref="G3:G5" si="1">F3/0.3048</f>
+        <v>13.164914698162995</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B4" s="1">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="D4" s="3">
+        <v>519.10765100000003</v>
+      </c>
+      <c r="E4" s="3">
         <v>523.120318</v>
-      </c>
-      <c r="E4" s="3">
-        <v>527.13298499999996</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
@@ -7140,164 +7305,170 @@
         <v>13.164917979002508</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="B5" s="1">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="D5" s="3">
+        <v>523.120318</v>
+      </c>
+      <c r="E5" s="3">
         <v>527.13298499999996</v>
       </c>
-      <c r="E5" s="3">
-        <v>531.14565100000004</v>
-      </c>
       <c r="F5" s="3">
-        <f>E5-D5</f>
-        <v>4.0126660000000811</v>
+        <f t="shared" si="0"/>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G5" s="2">
-        <f>F5/0.3048</f>
-        <v>13.164914698162995</v>
+        <f t="shared" si="1"/>
+        <v>13.164917979002508</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B6" s="1">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="D6" s="3">
+        <v>527.13298499999996</v>
+      </c>
+      <c r="E6" s="3">
         <v>531.14565100000004</v>
       </c>
-      <c r="E6" s="3">
-        <v>535.15831800000001</v>
-      </c>
       <c r="F6" s="3">
-        <f t="shared" ref="F6:F39" si="2">E6-D6</f>
-        <v>4.0126669999999649</v>
+        <f>E6-D6</f>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" ref="G6:G39" si="3">F6/0.3048</f>
-        <v>13.164917979002508</v>
+        <f>F6/0.3048</f>
+        <v>13.164914698162995</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="D7" s="3">
+        <v>531.14565100000004</v>
+      </c>
+      <c r="E7" s="3">
         <v>535.15831800000001</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
+        <f t="shared" ref="F7:F40" si="2">E7-D7</f>
+        <v>4.0126669999999649</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" ref="G7:G40" si="3">F7/0.3048</f>
+        <v>13.164917979002508</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" s="1">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="3">
+        <v>535.15831800000001</v>
+      </c>
+      <c r="E8" s="3">
         <v>539.17098499999997</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F8" s="3">
         <f t="shared" si="2"/>
         <v>4.0126669999999649</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G8" s="2">
         <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B8" s="1">
+      <c r="H8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="1">
         <v>10</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C9" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" s="3">
         <v>539.17098499999997</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E9" s="3">
         <v>543.18365100000005</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F9" s="3">
         <f t="shared" si="2"/>
         <v>4.0126660000000811</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G9" s="2">
         <f t="shared" si="3"/>
         <v>13.164914698162995</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B9" s="1">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" s="3">
-        <v>543.18365100000005</v>
-      </c>
-      <c r="E9" s="3">
-        <v>547.19631800000002</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="B10" s="1">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D10" s="3">
+        <v>543.18365100000005</v>
+      </c>
+      <c r="E10" s="3">
         <v>547.19631800000002</v>
-      </c>
-      <c r="E10" s="3">
-        <v>551.20898499999998</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="2"/>
@@ -7308,584 +7479,605 @@
         <v>13.164917979002508</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>372</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="D11" s="3">
+        <v>547.19631800000002</v>
+      </c>
+      <c r="E11" s="3">
         <v>551.20898499999998</v>
-      </c>
-      <c r="E11" s="3">
-        <v>555.22165099999995</v>
       </c>
       <c r="F11" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D12" s="3">
+        <v>551.20898499999998</v>
+      </c>
+      <c r="E12" s="3">
         <v>555.22165099999995</v>
-      </c>
-      <c r="E12" s="3">
-        <v>559.23431800000003</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="D13" s="3">
+        <v>555.22165099999995</v>
+      </c>
+      <c r="E13" s="3">
         <v>559.23431800000003</v>
-      </c>
-      <c r="E13" s="3">
-        <v>563.246985</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="D14" s="3">
+        <v>559.23431800000003</v>
+      </c>
+      <c r="E14" s="3">
         <v>563.246985</v>
-      </c>
-      <c r="E14" s="3">
-        <v>567.25965099999996</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="D15" s="3">
+        <v>563.246985</v>
+      </c>
+      <c r="E15" s="3">
         <v>567.25965099999996</v>
-      </c>
-      <c r="E15" s="3">
-        <v>571.27231800000004</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>208</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="D16" s="3">
+        <v>567.25965099999996</v>
+      </c>
+      <c r="E16" s="3">
         <v>571.27231800000004</v>
-      </c>
-      <c r="E16" s="3">
-        <v>575.28498500000001</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="B17" s="1">
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="D17" s="3">
+        <v>571.27231800000004</v>
+      </c>
+      <c r="E17" s="3">
         <v>575.28498500000001</v>
-      </c>
-      <c r="E17" s="3">
-        <v>579.29765099999997</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="B18" s="1">
         <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="D18" s="3">
+        <v>575.28498500000001</v>
+      </c>
+      <c r="E18" s="3">
         <v>579.29765099999997</v>
-      </c>
-      <c r="E18" s="3">
-        <v>583.31031800000005</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="B19" s="1">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="D19" s="3">
+        <v>579.29765099999997</v>
+      </c>
+      <c r="E19" s="3">
         <v>583.31031800000005</v>
-      </c>
-      <c r="E19" s="3">
-        <v>587.32298500000002</v>
       </c>
       <c r="F19" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="B20" s="1">
         <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="D20" s="3">
+        <v>583.31031800000005</v>
+      </c>
+      <c r="E20" s="3">
         <v>587.32298500000002</v>
-      </c>
-      <c r="E20" s="3">
-        <v>591.33565099999998</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="D21" s="3">
+        <v>587.32298500000002</v>
+      </c>
+      <c r="E21" s="3">
         <v>591.33565099999998</v>
-      </c>
-      <c r="E21" s="3">
-        <v>595.34831799999995</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="B22" s="1">
         <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="D22" s="3">
+        <v>591.33565099999998</v>
+      </c>
+      <c r="E22" s="3">
         <v>595.34831799999995</v>
-      </c>
-      <c r="E22" s="3">
-        <v>599.36098500000003</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="D23" s="3">
+        <v>595.34831799999995</v>
+      </c>
+      <c r="E23" s="3">
         <v>599.36098500000003</v>
-      </c>
-      <c r="E23" s="3">
-        <v>603.373651</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="B24" s="1">
         <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="D24" s="3">
+        <v>599.36098500000003</v>
+      </c>
+      <c r="E24" s="3">
         <v>603.373651</v>
-      </c>
-      <c r="E24" s="3">
-        <v>607.38631799999996</v>
       </c>
       <c r="F24" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="B25" s="1">
         <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="D25" s="3">
+        <v>603.373651</v>
+      </c>
+      <c r="E25" s="3">
         <v>607.38631799999996</v>
-      </c>
-      <c r="E25" s="3">
-        <v>611.39898500000004</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="B26" s="1">
         <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="D26" s="3">
+        <v>607.38631799999996</v>
+      </c>
+      <c r="E26" s="3">
         <v>611.39898500000004</v>
-      </c>
-      <c r="E26" s="3">
-        <v>615.41165100000001</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="B27" s="1">
         <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="D27" s="3">
+        <v>611.39898500000004</v>
+      </c>
+      <c r="E27" s="3">
         <v>615.41165100000001</v>
-      </c>
-      <c r="E27" s="3">
-        <v>619.42431799999997</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="B28" s="1">
         <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="D28" s="3">
+        <v>615.41165100000001</v>
+      </c>
+      <c r="E28" s="3">
         <v>619.42431799999997</v>
-      </c>
-      <c r="E28" s="3">
-        <v>623.43698500000005</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126670000000786</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002881</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="B29" s="1">
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="D29" s="3">
+        <v>619.42431799999997</v>
+      </c>
+      <c r="E29" s="3">
         <v>623.43698500000005</v>
-      </c>
-      <c r="E29" s="3">
-        <v>627.44965100000002</v>
       </c>
       <c r="F29" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126659999999674</v>
+        <v>4.0126670000000786</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162622</v>
+        <v>13.164917979002881</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="B30" s="1">
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D30" s="3">
+        <v>623.43698500000005</v>
+      </c>
+      <c r="E30" s="3">
         <v>627.44965100000002</v>
-      </c>
-      <c r="E30" s="3">
-        <v>631.46231799999998</v>
       </c>
       <c r="F30" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126659999999674</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162622</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B31" s="1">
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="D31" s="3">
+        <v>627.44965100000002</v>
+      </c>
+      <c r="E31" s="3">
         <v>631.46231799999998</v>
-      </c>
-      <c r="E31" s="3">
-        <v>635.47498499999995</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" si="2"/>
@@ -7896,80 +8088,83 @@
         <v>13.164917979002508</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="B32" s="1">
         <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="D32" s="3">
+        <v>631.46231799999998</v>
+      </c>
+      <c r="E32" s="3">
         <v>635.47498499999995</v>
-      </c>
-      <c r="E32" s="3">
-        <v>639.48765100000003</v>
       </c>
       <c r="F32" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126660000000811</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162995</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="B33" s="1">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="D33" s="3">
+        <v>635.47498499999995</v>
+      </c>
+      <c r="E33" s="3">
         <v>639.48765100000003</v>
-      </c>
-      <c r="E33" s="3">
-        <v>643.50031799999999</v>
       </c>
       <c r="F33" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162995</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="B34" s="1">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="D34" s="3">
+        <v>639.48765100000003</v>
+      </c>
+      <c r="E34" s="3">
         <v>643.50031799999999</v>
-      </c>
-      <c r="E34" s="3">
-        <v>647.51298499999996</v>
       </c>
       <c r="F34" s="3">
         <f t="shared" si="2"/>
@@ -7980,80 +8175,83 @@
         <v>13.164917979002508</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="B35" s="1">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="D35" s="3">
+        <v>643.50031799999999</v>
+      </c>
+      <c r="E35" s="3">
         <v>647.51298499999996</v>
-      </c>
-      <c r="E35" s="3">
-        <v>651.52565100000004</v>
       </c>
       <c r="F35" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126660000000811</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162995</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="B36" s="1">
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="D36" s="3">
+        <v>647.51298499999996</v>
+      </c>
+      <c r="E36" s="3">
         <v>651.52565100000004</v>
-      </c>
-      <c r="E36" s="3">
-        <v>655.538318</v>
       </c>
       <c r="F36" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="3"/>
-        <v>13.164917979002508</v>
+        <v>13.164914698162995</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="B37" s="1">
         <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="D37" s="3">
+        <v>651.52565100000004</v>
+      </c>
+      <c r="E37" s="3">
         <v>655.538318</v>
-      </c>
-      <c r="E37" s="3">
-        <v>659.55098499999997</v>
       </c>
       <c r="F37" s="3">
         <f t="shared" si="2"/>
@@ -8064,64 +8262,96 @@
         <v>13.164917979002508</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="B38" s="1">
         <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="D38" s="3">
+        <v>655.538318</v>
+      </c>
+      <c r="E38" s="3">
         <v>659.55098499999997</v>
-      </c>
-      <c r="E38" s="3">
-        <v>663.56365100000005</v>
       </c>
       <c r="F38" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126660000000811</v>
+        <v>4.0126669999999649</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="3"/>
-        <v>13.164914698162995</v>
+        <v>13.164917979002508</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="B39" s="1">
         <v>10</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="D39" s="3">
+        <v>659.55098499999997</v>
+      </c>
+      <c r="E39" s="3">
         <v>663.56365100000005</v>
-      </c>
-      <c r="E39" s="3">
-        <v>667.57631800000001</v>
       </c>
       <c r="F39" s="3">
         <f t="shared" si="2"/>
-        <v>4.0126669999999649</v>
+        <v>4.0126660000000811</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="3"/>
+        <v>13.164914698162995</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B40" s="1">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D40" s="3">
+        <v>663.56365100000005</v>
+      </c>
+      <c r="E40" s="3">
+        <v>667.57631800000001</v>
+      </c>
+      <c r="F40" s="3">
+        <f t="shared" si="2"/>
+        <v>4.0126669999999649</v>
+      </c>
+      <c r="G40" s="2">
+        <f t="shared" si="3"/>
         <v>13.164917979002508</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>209</v>
-      </c>
+      <c r="H40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
